--- a/files/templates/collected_data_test.xlsx
+++ b/files/templates/collected_data_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAA6657-AA26-4BC9-B94D-B07694A38C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B9C708-367B-4231-969C-6BBFF9FC540D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="management" sheetId="8" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="215">
   <si>
     <t>usm_name</t>
   </si>
@@ -692,6 +692,9 @@
   </si>
   <si>
     <t>choice</t>
+  </si>
+  <si>
+    <t>inorganic_N</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1155,10 +1158,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1167,10 +1178,13 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1185,127 +1199,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="71">
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1443,6 +1341,40 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1838,6 +1770,42 @@
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1870,6 +1838,37 @@
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1898,29 +1897,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AZ100" totalsRowShown="0" headerRowDxfId="70" headerRowBorderDxfId="69" tableBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AZ100" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65">
   <autoFilter ref="A2:AZ100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
   <tableColumns count="52">
-    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="63"/>
     <tableColumn id="3" xr3:uid="{416116E5-319A-4096-B7E5-AF8ADEF0E80A}" name="tillage_date"/>
-    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="62"/>
     <tableColumn id="5" xr3:uid="{A768ED69-1CCB-4A41-99C1-D5042177408B}" name="planting_date"/>
     <tableColumn id="6" xr3:uid="{5517C570-4D1C-46EC-9FB0-4FEA929440E1}" name="planting_depth"/>
-    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="61"/>
     <tableColumn id="8" xr3:uid="{7DEB259C-DAE3-4A1E-B476-951FEF30ABD2}" name="emergence"/>
     <tableColumn id="9" xr3:uid="{8590CC43-CF1F-45A9-A612-CE3749B53C84}" name="flowering"/>
-    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="60"/>
     <tableColumn id="11" xr3:uid="{1651DE3B-149A-4121-AFB0-BA33E8308050}" name="application_date"/>
     <tableColumn id="12" xr3:uid="{358B23A5-F859-4B79-9182-F98F3D69F461}" name="kg_N_per_ha"/>
     <tableColumn id="13" xr3:uid="{FEB67719-45D9-4389-A438-548C552EBED6}" name="fert_type"/>
     <tableColumn id="14" xr3:uid="{B9B3005C-6E63-4AA3-BE8E-646D9659B76F}" name="fert_location"/>
-    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="59"/>
     <tableColumn id="16" xr3:uid="{AA12C7D8-D645-4337-B05C-CB5F5C197AE4}" name="irrigation_type"/>
-    <tableColumn id="17" xr3:uid="{017BC113-D478-4E04-AEE6-020CA6B48738}" name="irr_efficiency" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{017BC113-D478-4E04-AEE6-020CA6B48738}" name="irr_efficiency" dataDxfId="58"/>
     <tableColumn id="51" xr3:uid="{861EB44E-9488-4000-AECA-9F2616F247A4}" name="autoirr_depth"/>
     <tableColumn id="53" xr3:uid="{6FB53672-D45A-44BE-B940-C5C46269041F}" name="autoirr_start"/>
-    <tableColumn id="52" xr3:uid="{50CA12D2-CB35-4EC1-AC10-B913B6AD68E3}" name="autoirr_end" dataDxfId="2"/>
+    <tableColumn id="52" xr3:uid="{50CA12D2-CB35-4EC1-AC10-B913B6AD68E3}" name="autoirr_end" dataDxfId="57"/>
     <tableColumn id="18" xr3:uid="{498ED556-89DC-49A5-A6C1-DF741DBED2EF}" name="irrigation_date_1"/>
     <tableColumn id="19" xr3:uid="{08BD5ABB-6859-4E1B-A6BD-260DAEDACB58}" name="amount_1"/>
     <tableColumn id="20" xr3:uid="{8628DB18-9428-459B-B5B2-46E267F6DC77}" name="irrigation_date_2"/>
@@ -1950,7 +1949,7 @@
     <tableColumn id="44" xr3:uid="{7DD1FA19-1C12-4443-9EB3-267851A488BA}" name="irrigation_date_14"/>
     <tableColumn id="45" xr3:uid="{A69E1720-4BA7-4736-9E85-A0E33013B090}" name="amount_14"/>
     <tableColumn id="46" xr3:uid="{A0DFD622-ADA5-48E2-B689-A17242FFBEEA}" name="irrigation_date_15"/>
-    <tableColumn id="47" xr3:uid="{F418CA91-8862-4EFC-BFAB-DE953401968F}" name="amount_15" dataDxfId="1"/>
+    <tableColumn id="47" xr3:uid="{F418CA91-8862-4EFC-BFAB-DE953401968F}" name="amount_15" dataDxfId="56"/>
     <tableColumn id="49" xr3:uid="{713CD6FD-5A43-47D8-A049-B2CDBB3A70A7}" name="harvest_date2"/>
     <tableColumn id="50" xr3:uid="{0534CF22-31C4-406A-8003-4D0278A8D5A3}" name="harvest_end"/>
   </tableColumns>
@@ -2009,15 +2008,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CI100" totalsRowShown="0" headerRowDxfId="61" headerRowBorderDxfId="60" tableBorderDxfId="59">
-  <autoFilter ref="A2:CI100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
-  <tableColumns count="87">
-    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="58"/>
-    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CJ100" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53">
+  <autoFilter ref="A2:CJ100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
+  <tableColumns count="88">
+    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="52"/>
+    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="51"/>
     <tableColumn id="80" xr3:uid="{0420D7E9-122C-4575-A7AC-7BBC4F58B702}" name="impermeable_lyr"/>
     <tableColumn id="82" xr3:uid="{6B1B49F0-7082-435D-B674-074AD54FF41A}" name="spacing"/>
     <tableColumn id="81" xr3:uid="{D1C9B62E-CB38-44E4-B973-A9B54A950392}" name="hydraulic_conductivity"/>
-    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="56"/>
+    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="50"/>
     <tableColumn id="2" xr3:uid="{72D785FE-A1AF-4E08-AB14-39FAD15DB9BD}" name="thickness_1"/>
     <tableColumn id="3" xr3:uid="{1838D7E8-2B3C-471C-9A0B-D70D91F18417}" name="pH"/>
     <tableColumn id="4" xr3:uid="{22C3A2D3-19B8-4556-9BAC-DEDF286C1C2C}" name="%_sand_1"/>
@@ -2026,92 +2025,93 @@
     <tableColumn id="39" xr3:uid="{E2BB7CB7-ACCE-4FF1-AF91-42C43097A8A0}" name="SOM_1"/>
     <tableColumn id="7" xr3:uid="{20FE986C-6B28-4993-A555-F2428095534E}" name="SOC_1"/>
     <tableColumn id="40" xr3:uid="{EC836542-6DD7-49C9-82D9-B724BCE18341}" name="SON_1"/>
+    <tableColumn id="71" xr3:uid="{797430C4-3320-4944-8FA7-622E4D340D6A}" name="inorganic_N"/>
     <tableColumn id="41" xr3:uid="{F7750E58-5B0E-4494-87AF-B025671824DE}" name="CN_ratio"/>
     <tableColumn id="8" xr3:uid="{0592115C-328E-42C4-B9CB-D43026D4FC27}" name="FC_1"/>
-    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="55"/>
+    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="49"/>
     <tableColumn id="9" xr3:uid="{C1383A59-387E-4667-852A-B0CF467088F3}" name="WP_1"/>
-    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="54"/>
+    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="48"/>
     <tableColumn id="10" xr3:uid="{34D0D911-5DB4-457F-88A7-76A42B57EE1A}" name="initial_NO3_1"/>
-    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="53"/>
+    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="47"/>
     <tableColumn id="53" xr3:uid="{CEF78893-60AA-4A20-A771-E76562B8EBC1}" name="initial_NH4_1"/>
-    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="52"/>
-    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="51"/>
-    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="46"/>
+    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="45"/>
+    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="44"/>
     <tableColumn id="12" xr3:uid="{FD043EB5-2678-4920-8D76-EBE8316E27AA}" name="thickness_2"/>
     <tableColumn id="13" xr3:uid="{F124AE04-B447-4F21-A0E8-7B26199C0F49}" name="%_sand_2"/>
     <tableColumn id="14" xr3:uid="{F119498A-3A35-40E3-A753-7CF13D724118}" name="%_clay_2"/>
     <tableColumn id="15" xr3:uid="{AE51522F-6903-42D4-88CE-A95BCE8C77EF}" name="BD_2"/>
     <tableColumn id="16" xr3:uid="{12076489-6AD7-4297-A729-20EF93AEE58D}" name="SOC_2"/>
     <tableColumn id="17" xr3:uid="{D6D5EFD4-69CC-4AF2-8C6B-0B430468C4C2}" name="FC_2"/>
-    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="49"/>
+    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="43"/>
     <tableColumn id="18" xr3:uid="{BBF6A61D-2092-4DF7-8C38-9024164291AE}" name="WP_2"/>
-    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="48"/>
+    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="42"/>
     <tableColumn id="19" xr3:uid="{BB4B796C-CA3E-424C-87B0-4BF33581B61B}" name="initial_NO3_2"/>
-    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="47"/>
+    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="41"/>
     <tableColumn id="55" xr3:uid="{333E59C3-3A13-4C92-9169-AC90D5E5D3EB}" name="initial_NH4_2"/>
-    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="46"/>
-    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="45"/>
-    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="44"/>
+    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="40"/>
+    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="39"/>
+    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="38"/>
     <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3"/>
     <tableColumn id="22" xr3:uid="{6C917DE4-8D95-496E-A6F1-EAB7450774EE}" name="%_sand_3"/>
     <tableColumn id="23" xr3:uid="{90DE7FE2-3A23-4294-8BD0-2D321FF71179}" name="%_clay_3"/>
     <tableColumn id="24" xr3:uid="{C874CBBB-CB06-4239-AE9B-72564A3EDC14}" name="BD_3"/>
     <tableColumn id="25" xr3:uid="{49CED3FB-E83C-4973-A99D-DAC6B3AFC7B1}" name="SOC_3"/>
     <tableColumn id="26" xr3:uid="{63FB3901-EBED-4379-9E9C-83064A8ADD01}" name="FC_3"/>
-    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="43"/>
+    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="37"/>
     <tableColumn id="27" xr3:uid="{6EEACF0E-3934-49DF-9991-42C2DB718BE0}" name="WP_3"/>
-    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="42"/>
+    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="36"/>
     <tableColumn id="28" xr3:uid="{7AAE3F1E-C60E-4E11-A023-F09548D5AA39}" name="initial_NO3_3"/>
-    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="41"/>
+    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="35"/>
     <tableColumn id="57" xr3:uid="{1D0A3587-38DB-4073-B5D4-36DA82425955}" name="initial_NH4_3"/>
-    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="40"/>
-    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="39"/>
-    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="38"/>
-    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="37"/>
+    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="34"/>
+    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="33"/>
+    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="32"/>
+    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="31"/>
     <tableColumn id="31" xr3:uid="{4C1178FA-055B-4F19-A181-638D37A24EB6}" name="%_sand_4"/>
     <tableColumn id="32" xr3:uid="{7BBFA3FD-BBE5-4B68-A551-EFDEA7062540}" name="%_clay_4"/>
     <tableColumn id="33" xr3:uid="{D0607A27-FB9E-4DA9-A7F3-7A932B2608A4}" name="BD_4"/>
     <tableColumn id="34" xr3:uid="{BD46131F-AB56-411A-8742-B77FBBE1967B}" name="SOC_4"/>
     <tableColumn id="35" xr3:uid="{EC2EEDB8-3CC6-4DEE-9309-DBA3B11A2D16}" name="FC_4"/>
-    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="36"/>
-    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="35"/>
-    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="34"/>
-    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="33"/>
-    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="32"/>
-    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="31"/>
-    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="30"/>
-    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="29"/>
-    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="28"/>
+    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="30"/>
+    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="29"/>
+    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="28"/>
+    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="27"/>
+    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="26"/>
+    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="25"/>
+    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="24"/>
+    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="23"/>
+    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="22"/>
     <tableColumn id="46" xr3:uid="{5545ADBB-3E57-4FCE-9979-330500D810A6}" name="thickness_5"/>
     <tableColumn id="49" xr3:uid="{28F4610E-A232-42D7-866E-B72AB5FC38D8}" name="%_sand_5"/>
     <tableColumn id="60" xr3:uid="{9557F7B0-0944-4CA4-8B86-630B4073480C}" name="%_clay_5"/>
     <tableColumn id="61" xr3:uid="{6977D0A0-E571-46FB-8186-DF22D992C4B6}" name="BD_5"/>
     <tableColumn id="62" xr3:uid="{762BF513-B3A9-4714-B788-A74D32CD414B}" name="SOC_5"/>
     <tableColumn id="63" xr3:uid="{F840DA58-F957-445A-8704-4823DC13AEC7}" name="FC_5"/>
-    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="27"/>
+    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="21"/>
     <tableColumn id="65" xr3:uid="{73133DDD-77CC-4B8F-AF63-0B5537B95DE3}" name="WP_5"/>
-    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="26"/>
+    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="20"/>
     <tableColumn id="67" xr3:uid="{AF697735-FE14-47A1-8029-532D47D2E5C7}" name="initial_NO3_5"/>
-    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="25"/>
-    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="24"/>
-    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="23"/>
-    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="22"/>
-    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="0"/>
-    <tableColumn id="75" xr3:uid="{5E31E895-C232-46F3-A784-EDD164AC3EC1}" name="denitrification" dataDxfId="5"/>
-    <tableColumn id="77" xr3:uid="{A0CE09FC-8A47-40DC-A973-B224FE1B7DB0}" name="nitrification" dataDxfId="4"/>
+    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="19"/>
+    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="18"/>
+    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="17"/>
+    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="16"/>
+    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="15"/>
+    <tableColumn id="75" xr3:uid="{5E31E895-C232-46F3-A784-EDD164AC3EC1}" name="denitrification" dataDxfId="14"/>
+    <tableColumn id="77" xr3:uid="{A0CE09FC-8A47-40DC-A973-B224FE1B7DB0}" name="nitrification" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:E109" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="weather_station_name" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="weather_station_name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{3D2F9127-7EC2-4140-96D1-5B59A53113F7}" name="windspeed_unit"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2119,32 +2119,32 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J100" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:J100" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A2:J100" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{C58B90D4-B75A-409B-9D58-E09932ABF65C}" name="simulation_start"/>
-    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{C4CB74A7-2660-4D67-9D08-D7802D112D6D}" name="soil_profile_name"/>
     <tableColumn id="6" xr3:uid="{EE8564A9-D685-42B6-914D-B5F77F840B11}" name="weather_station_name"/>
     <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file"/>
-    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{B3D6750F-E334-4A3F-A048-BA40F1D2EC0C}" name="cultivar_code" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{BDB57316-D9C6-4EE3-821F-F5561E0078D9}" name="first_year"/>
-    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="70">
   <autoFilter ref="A1:F30" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="69"/>
     <tableColumn id="2" xr3:uid="{A5156817-2D3F-4E14-AC57-75BA66E12293}" name="year"/>
     <tableColumn id="3" xr3:uid="{173E3383-07EB-425D-884F-01E4ECFF4626}" name="month"/>
-    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="68"/>
     <tableColumn id="6" xr3:uid="{B9B2B184-EF64-48EF-B50B-8E24249DFDCC}" name="variable 1"/>
     <tableColumn id="7" xr3:uid="{ED0F5D28-DB43-4C9B-ADB2-1706AC6D61F9}" name="variable 2"/>
   </tableColumns>
@@ -2516,68 +2516,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="64" t="s">
+      <c r="D1" s="70"/>
+      <c r="E1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="66" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="65" t="s">
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="67" t="s">
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="67"/>
-      <c r="AG1" s="67"/>
-      <c r="AH1" s="67"/>
-      <c r="AI1" s="67"/>
-      <c r="AJ1" s="67"/>
-      <c r="AK1" s="67"/>
-      <c r="AL1" s="67"/>
-      <c r="AM1" s="67"/>
-      <c r="AN1" s="67"/>
-      <c r="AO1" s="67"/>
-      <c r="AP1" s="67"/>
-      <c r="AQ1" s="67"/>
-      <c r="AR1" s="67"/>
-      <c r="AS1" s="67"/>
-      <c r="AT1" s="67"/>
-      <c r="AU1" s="67"/>
-      <c r="AV1" s="67"/>
-      <c r="AW1" s="67"/>
-      <c r="AX1" s="67"/>
-      <c r="AY1" s="64" t="s">
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AE1" s="68"/>
+      <c r="AF1" s="68"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
+      <c r="AM1" s="68"/>
+      <c r="AN1" s="68"/>
+      <c r="AO1" s="68"/>
+      <c r="AP1" s="68"/>
+      <c r="AQ1" s="68"/>
+      <c r="AR1" s="68"/>
+      <c r="AS1" s="68"/>
+      <c r="AT1" s="68"/>
+      <c r="AU1" s="68"/>
+      <c r="AV1" s="68"/>
+      <c r="AW1" s="68"/>
+      <c r="AX1" s="68"/>
+      <c r="AY1" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="AZ1" s="64"/>
+      <c r="AZ1" s="69"/>
     </row>
     <row r="2" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
@@ -2631,13 +2631,13 @@
       <c r="Q2" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="63" t="s">
         <v>202</v>
       </c>
       <c r="U2" s="11" t="s">
@@ -2727,13 +2727,13 @@
       <c r="AW2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="AX2" s="74" t="s">
+      <c r="AX2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="AY2" s="76" t="s">
+      <c r="AY2" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="AZ2" s="76" t="s">
+      <c r="AZ2" s="10" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2741,982 +2741,884 @@
       <c r="E3" s="48"/>
       <c r="M3" s="35"/>
       <c r="N3" s="35"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="81"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="65"/>
       <c r="R3" s="60"/>
-      <c r="T3" s="81"/>
+      <c r="T3" s="65"/>
       <c r="AT3"/>
-      <c r="AW3" s="79"/>
-      <c r="AX3" s="81"/>
+      <c r="AX3" s="65"/>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M4" s="35"/>
       <c r="N4" s="35"/>
-      <c r="P4" s="75"/>
+      <c r="P4" s="64"/>
       <c r="Q4" s="6"/>
       <c r="T4" s="6"/>
       <c r="AT4"/>
-      <c r="AW4" s="79"/>
       <c r="AX4" s="6"/>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M5" s="35"/>
       <c r="N5" s="35"/>
-      <c r="P5" s="75"/>
+      <c r="P5" s="64"/>
       <c r="Q5" s="6"/>
       <c r="T5" s="6"/>
       <c r="AT5"/>
-      <c r="AW5" s="79"/>
       <c r="AX5" s="6"/>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
-      <c r="P6" s="75"/>
+      <c r="P6" s="64"/>
       <c r="Q6" s="6"/>
       <c r="T6" s="6"/>
       <c r="AT6"/>
-      <c r="AW6" s="79"/>
       <c r="AX6" s="6"/>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M7" s="35"/>
       <c r="N7" s="35"/>
-      <c r="P7" s="75"/>
+      <c r="P7" s="64"/>
       <c r="Q7" s="6"/>
       <c r="T7" s="6"/>
       <c r="AT7"/>
-      <c r="AW7" s="79"/>
       <c r="AX7" s="6"/>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M8" s="35"/>
       <c r="N8" s="35"/>
-      <c r="P8" s="75"/>
+      <c r="P8" s="64"/>
       <c r="Q8" s="6"/>
       <c r="T8" s="6"/>
       <c r="AT8"/>
-      <c r="AW8" s="79"/>
       <c r="AX8" s="6"/>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M9" s="35"/>
       <c r="N9" s="35"/>
-      <c r="P9" s="75"/>
+      <c r="P9" s="64"/>
       <c r="Q9" s="6"/>
       <c r="T9" s="6"/>
       <c r="AT9"/>
-      <c r="AW9" s="79"/>
       <c r="AX9" s="6"/>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M10" s="35"/>
       <c r="N10" s="35"/>
-      <c r="P10" s="75"/>
+      <c r="P10" s="64"/>
       <c r="Q10" s="6"/>
       <c r="T10" s="6"/>
       <c r="AT10"/>
-      <c r="AW10" s="79"/>
       <c r="AX10" s="6"/>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
-      <c r="P11" s="75"/>
+      <c r="P11" s="64"/>
       <c r="Q11" s="6"/>
       <c r="T11" s="6"/>
       <c r="AT11"/>
-      <c r="AW11" s="79"/>
       <c r="AX11" s="6"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M12" s="35"/>
       <c r="N12" s="35"/>
-      <c r="P12" s="75"/>
+      <c r="P12" s="64"/>
       <c r="Q12" s="6"/>
       <c r="T12" s="6"/>
       <c r="AT12"/>
-      <c r="AW12" s="79"/>
       <c r="AX12" s="6"/>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M13" s="35"/>
       <c r="N13" s="35"/>
-      <c r="P13" s="75"/>
+      <c r="P13" s="64"/>
       <c r="Q13" s="6"/>
       <c r="T13" s="6"/>
       <c r="AT13"/>
-      <c r="AW13" s="79"/>
       <c r="AX13" s="6"/>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M14" s="35"/>
       <c r="N14" s="35"/>
-      <c r="P14" s="75"/>
+      <c r="P14" s="64"/>
       <c r="Q14" s="6"/>
       <c r="T14" s="6"/>
       <c r="AT14"/>
-      <c r="AW14" s="79"/>
       <c r="AX14" s="6"/>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
-      <c r="P15" s="75"/>
+      <c r="P15" s="64"/>
       <c r="Q15" s="6"/>
       <c r="T15" s="6"/>
       <c r="AT15"/>
-      <c r="AW15" s="79"/>
       <c r="AX15" s="6"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.3">
       <c r="M16" s="35"/>
       <c r="N16" s="35"/>
-      <c r="P16" s="75"/>
+      <c r="P16" s="64"/>
       <c r="Q16" s="6"/>
       <c r="T16" s="6"/>
       <c r="AT16"/>
-      <c r="AW16" s="79"/>
       <c r="AX16" s="6"/>
     </row>
     <row r="17" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M17" s="35"/>
       <c r="N17" s="35"/>
-      <c r="P17" s="75"/>
+      <c r="P17" s="64"/>
       <c r="Q17" s="6"/>
       <c r="T17" s="6"/>
       <c r="AT17"/>
-      <c r="AW17" s="79"/>
       <c r="AX17" s="6"/>
     </row>
     <row r="18" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M18" s="35"/>
       <c r="N18" s="35"/>
-      <c r="P18" s="75"/>
+      <c r="P18" s="64"/>
       <c r="Q18" s="6"/>
       <c r="T18" s="6"/>
       <c r="AT18"/>
-      <c r="AW18" s="79"/>
       <c r="AX18" s="6"/>
     </row>
     <row r="19" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M19" s="35"/>
       <c r="N19" s="35"/>
-      <c r="P19" s="75"/>
+      <c r="P19" s="64"/>
       <c r="Q19" s="6"/>
       <c r="T19" s="6"/>
       <c r="AT19"/>
-      <c r="AW19" s="79"/>
       <c r="AX19" s="6"/>
     </row>
     <row r="20" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M20" s="35"/>
       <c r="N20" s="35"/>
-      <c r="P20" s="75"/>
+      <c r="P20" s="64"/>
       <c r="Q20" s="6"/>
       <c r="T20" s="6"/>
       <c r="AT20"/>
-      <c r="AW20" s="79"/>
       <c r="AX20" s="6"/>
     </row>
     <row r="21" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M21" s="35"/>
       <c r="N21" s="35"/>
-      <c r="P21" s="75"/>
+      <c r="P21" s="64"/>
       <c r="Q21" s="6"/>
       <c r="T21" s="6"/>
       <c r="AT21"/>
-      <c r="AW21" s="79"/>
       <c r="AX21" s="6"/>
     </row>
     <row r="22" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M22" s="35"/>
       <c r="N22" s="35"/>
-      <c r="P22" s="75"/>
+      <c r="P22" s="64"/>
       <c r="Q22" s="6"/>
       <c r="T22" s="6"/>
       <c r="AT22"/>
-      <c r="AW22" s="79"/>
       <c r="AX22" s="6"/>
     </row>
     <row r="23" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M23" s="35"/>
       <c r="N23" s="35"/>
-      <c r="P23" s="75"/>
+      <c r="P23" s="64"/>
       <c r="Q23" s="6"/>
       <c r="T23" s="6"/>
       <c r="AT23"/>
-      <c r="AW23" s="79"/>
       <c r="AX23" s="6"/>
     </row>
     <row r="24" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M24" s="35"/>
       <c r="N24" s="35"/>
-      <c r="P24" s="75"/>
+      <c r="P24" s="64"/>
       <c r="Q24" s="6"/>
       <c r="T24" s="6"/>
       <c r="AT24"/>
-      <c r="AW24" s="79"/>
       <c r="AX24" s="6"/>
     </row>
     <row r="25" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M25" s="35"/>
       <c r="N25" s="35"/>
-      <c r="P25" s="75"/>
+      <c r="P25" s="64"/>
       <c r="Q25" s="6"/>
       <c r="T25" s="6"/>
       <c r="AT25"/>
-      <c r="AW25" s="79"/>
       <c r="AX25" s="6"/>
     </row>
     <row r="26" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M26" s="35"/>
       <c r="N26" s="35"/>
-      <c r="P26" s="75"/>
+      <c r="P26" s="64"/>
       <c r="Q26" s="6"/>
       <c r="T26" s="6"/>
       <c r="AT26"/>
-      <c r="AW26" s="79"/>
       <c r="AX26" s="6"/>
     </row>
     <row r="27" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M27" s="35"/>
       <c r="N27" s="35"/>
-      <c r="P27" s="75"/>
+      <c r="P27" s="64"/>
       <c r="Q27" s="6"/>
       <c r="T27" s="6"/>
       <c r="AT27"/>
-      <c r="AW27" s="79"/>
       <c r="AX27" s="6"/>
     </row>
     <row r="28" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M28" s="35"/>
       <c r="N28" s="35"/>
-      <c r="P28" s="75"/>
+      <c r="P28" s="64"/>
       <c r="Q28" s="6"/>
       <c r="T28" s="6"/>
       <c r="AT28"/>
-      <c r="AW28" s="79"/>
       <c r="AX28" s="6"/>
     </row>
     <row r="29" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M29" s="35"/>
       <c r="N29" s="35"/>
-      <c r="P29" s="75"/>
+      <c r="P29" s="64"/>
       <c r="Q29" s="6"/>
       <c r="T29" s="6"/>
       <c r="AT29"/>
-      <c r="AW29" s="79"/>
       <c r="AX29" s="6"/>
     </row>
     <row r="30" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M30" s="35"/>
       <c r="N30" s="35"/>
-      <c r="P30" s="75"/>
+      <c r="P30" s="64"/>
       <c r="Q30" s="6"/>
       <c r="T30" s="6"/>
       <c r="AT30"/>
-      <c r="AW30" s="79"/>
       <c r="AX30" s="6"/>
     </row>
     <row r="31" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M31" s="35"/>
       <c r="N31" s="35"/>
-      <c r="P31" s="75"/>
+      <c r="P31" s="64"/>
       <c r="Q31" s="6"/>
       <c r="T31" s="6"/>
       <c r="AT31"/>
-      <c r="AW31" s="79"/>
       <c r="AX31" s="6"/>
     </row>
     <row r="32" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M32" s="35"/>
       <c r="N32" s="35"/>
-      <c r="P32" s="75"/>
+      <c r="P32" s="64"/>
       <c r="Q32" s="6"/>
       <c r="T32" s="6"/>
       <c r="AT32"/>
-      <c r="AW32" s="79"/>
       <c r="AX32" s="6"/>
     </row>
     <row r="33" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M33" s="35"/>
       <c r="N33" s="35"/>
-      <c r="P33" s="75"/>
+      <c r="P33" s="64"/>
       <c r="Q33" s="6"/>
       <c r="T33" s="6"/>
       <c r="AT33"/>
-      <c r="AW33" s="79"/>
       <c r="AX33" s="6"/>
     </row>
     <row r="34" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M34" s="35"/>
       <c r="N34" s="35"/>
-      <c r="P34" s="75"/>
+      <c r="P34" s="64"/>
       <c r="Q34" s="6"/>
       <c r="T34" s="6"/>
       <c r="AT34"/>
-      <c r="AW34" s="79"/>
       <c r="AX34" s="6"/>
     </row>
     <row r="35" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M35" s="35"/>
       <c r="N35" s="35"/>
-      <c r="P35" s="75"/>
+      <c r="P35" s="64"/>
       <c r="Q35" s="6"/>
       <c r="T35" s="6"/>
       <c r="AT35"/>
-      <c r="AW35" s="79"/>
       <c r="AX35" s="6"/>
     </row>
     <row r="36" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M36" s="35"/>
       <c r="N36" s="35"/>
-      <c r="P36" s="75"/>
+      <c r="P36" s="64"/>
       <c r="Q36" s="6"/>
       <c r="T36" s="6"/>
       <c r="AT36"/>
-      <c r="AW36" s="79"/>
       <c r="AX36" s="6"/>
     </row>
     <row r="37" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M37" s="35"/>
       <c r="N37" s="35"/>
-      <c r="P37" s="75"/>
+      <c r="P37" s="64"/>
       <c r="Q37" s="6"/>
       <c r="T37" s="6"/>
       <c r="AT37"/>
-      <c r="AW37" s="79"/>
       <c r="AX37" s="6"/>
     </row>
     <row r="38" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M38" s="35"/>
       <c r="N38" s="35"/>
-      <c r="P38" s="75"/>
+      <c r="P38" s="64"/>
       <c r="Q38" s="6"/>
       <c r="T38" s="6"/>
       <c r="AT38"/>
-      <c r="AW38" s="79"/>
       <c r="AX38" s="6"/>
     </row>
     <row r="39" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M39" s="35"/>
       <c r="N39" s="35"/>
-      <c r="P39" s="75"/>
+      <c r="P39" s="64"/>
       <c r="Q39" s="6"/>
       <c r="T39" s="6"/>
       <c r="AT39"/>
-      <c r="AW39" s="79"/>
       <c r="AX39" s="6"/>
     </row>
     <row r="40" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M40" s="35"/>
       <c r="N40" s="35"/>
-      <c r="P40" s="75"/>
+      <c r="P40" s="64"/>
       <c r="Q40" s="6"/>
       <c r="T40" s="6"/>
       <c r="AT40"/>
-      <c r="AW40" s="79"/>
       <c r="AX40" s="6"/>
     </row>
     <row r="41" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M41" s="35"/>
       <c r="N41" s="35"/>
-      <c r="P41" s="75"/>
+      <c r="P41" s="64"/>
       <c r="Q41" s="6"/>
       <c r="T41" s="6"/>
       <c r="AT41"/>
-      <c r="AW41" s="79"/>
       <c r="AX41" s="6"/>
     </row>
     <row r="42" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M42" s="35"/>
       <c r="N42" s="35"/>
-      <c r="P42" s="75"/>
+      <c r="P42" s="64"/>
       <c r="Q42" s="6"/>
       <c r="T42" s="6"/>
       <c r="AT42"/>
-      <c r="AW42" s="79"/>
       <c r="AX42" s="6"/>
     </row>
     <row r="43" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M43" s="35"/>
       <c r="N43" s="35"/>
-      <c r="P43" s="75"/>
+      <c r="P43" s="64"/>
       <c r="Q43" s="6"/>
       <c r="T43" s="6"/>
       <c r="AT43"/>
-      <c r="AW43" s="79"/>
       <c r="AX43" s="6"/>
     </row>
     <row r="44" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M44" s="35"/>
       <c r="N44" s="35"/>
-      <c r="P44" s="75"/>
+      <c r="P44" s="64"/>
       <c r="Q44" s="6"/>
       <c r="T44" s="6"/>
       <c r="AT44"/>
-      <c r="AW44" s="79"/>
       <c r="AX44" s="6"/>
     </row>
     <row r="45" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M45" s="35"/>
       <c r="N45" s="35"/>
-      <c r="P45" s="75"/>
+      <c r="P45" s="64"/>
       <c r="Q45" s="6"/>
       <c r="T45" s="6"/>
       <c r="AT45"/>
-      <c r="AW45" s="79"/>
       <c r="AX45" s="6"/>
     </row>
     <row r="46" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M46" s="35"/>
       <c r="N46" s="35"/>
-      <c r="P46" s="75"/>
+      <c r="P46" s="64"/>
       <c r="Q46" s="6"/>
       <c r="T46" s="6"/>
       <c r="AT46"/>
-      <c r="AW46" s="79"/>
       <c r="AX46" s="6"/>
     </row>
     <row r="47" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M47" s="35"/>
       <c r="N47" s="35"/>
-      <c r="P47" s="75"/>
+      <c r="P47" s="64"/>
       <c r="Q47" s="6"/>
       <c r="T47" s="6"/>
       <c r="AT47"/>
-      <c r="AW47" s="79"/>
       <c r="AX47" s="6"/>
     </row>
     <row r="48" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M48" s="35"/>
       <c r="N48" s="35"/>
-      <c r="P48" s="75"/>
+      <c r="P48" s="64"/>
       <c r="Q48" s="6"/>
       <c r="T48" s="6"/>
       <c r="AT48"/>
-      <c r="AW48" s="79"/>
       <c r="AX48" s="6"/>
     </row>
     <row r="49" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M49" s="35"/>
       <c r="N49" s="35"/>
-      <c r="P49" s="75"/>
+      <c r="P49" s="64"/>
       <c r="Q49" s="6"/>
       <c r="T49" s="6"/>
       <c r="AT49"/>
-      <c r="AW49" s="79"/>
       <c r="AX49" s="6"/>
     </row>
     <row r="50" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M50" s="35"/>
       <c r="N50" s="35"/>
-      <c r="P50" s="75"/>
+      <c r="P50" s="64"/>
       <c r="Q50" s="6"/>
       <c r="T50" s="6"/>
       <c r="AT50"/>
-      <c r="AW50" s="79"/>
       <c r="AX50" s="6"/>
     </row>
     <row r="51" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M51" s="35"/>
       <c r="N51" s="35"/>
-      <c r="P51" s="75"/>
+      <c r="P51" s="64"/>
       <c r="Q51" s="6"/>
       <c r="T51" s="6"/>
       <c r="AT51"/>
-      <c r="AW51" s="79"/>
       <c r="AX51" s="6"/>
     </row>
     <row r="52" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M52" s="35"/>
       <c r="N52" s="35"/>
-      <c r="P52" s="75"/>
+      <c r="P52" s="64"/>
       <c r="Q52" s="6"/>
       <c r="T52" s="6"/>
       <c r="AT52"/>
-      <c r="AW52" s="79"/>
       <c r="AX52" s="6"/>
     </row>
     <row r="53" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M53" s="35"/>
       <c r="N53" s="35"/>
-      <c r="P53" s="75"/>
+      <c r="P53" s="64"/>
       <c r="Q53" s="6"/>
       <c r="T53" s="6"/>
       <c r="AT53"/>
-      <c r="AW53" s="79"/>
       <c r="AX53" s="6"/>
     </row>
     <row r="54" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M54" s="35"/>
       <c r="N54" s="35"/>
-      <c r="P54" s="75"/>
+      <c r="P54" s="64"/>
       <c r="Q54" s="6"/>
       <c r="T54" s="6"/>
       <c r="AT54"/>
-      <c r="AW54" s="79"/>
       <c r="AX54" s="6"/>
     </row>
     <row r="55" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M55" s="35"/>
       <c r="N55" s="35"/>
-      <c r="P55" s="75"/>
+      <c r="P55" s="64"/>
       <c r="Q55" s="6"/>
       <c r="T55" s="6"/>
       <c r="AT55"/>
-      <c r="AW55" s="79"/>
       <c r="AX55" s="6"/>
     </row>
     <row r="56" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M56" s="35"/>
       <c r="N56" s="35"/>
-      <c r="P56" s="75"/>
+      <c r="P56" s="64"/>
       <c r="Q56" s="6"/>
       <c r="T56" s="6"/>
       <c r="AT56"/>
-      <c r="AW56" s="79"/>
       <c r="AX56" s="6"/>
     </row>
     <row r="57" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M57" s="35"/>
       <c r="N57" s="35"/>
-      <c r="P57" s="75"/>
+      <c r="P57" s="64"/>
       <c r="Q57" s="6"/>
       <c r="T57" s="6"/>
       <c r="AT57"/>
-      <c r="AW57" s="79"/>
       <c r="AX57" s="6"/>
     </row>
     <row r="58" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M58" s="35"/>
       <c r="N58" s="35"/>
-      <c r="P58" s="75"/>
+      <c r="P58" s="64"/>
       <c r="Q58" s="6"/>
       <c r="T58" s="6"/>
       <c r="AT58"/>
-      <c r="AW58" s="79"/>
       <c r="AX58" s="6"/>
     </row>
     <row r="59" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M59" s="35"/>
       <c r="N59" s="35"/>
-      <c r="P59" s="75"/>
+      <c r="P59" s="64"/>
       <c r="Q59" s="6"/>
       <c r="T59" s="6"/>
       <c r="AT59"/>
-      <c r="AW59" s="79"/>
       <c r="AX59" s="6"/>
     </row>
     <row r="60" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M60" s="35"/>
       <c r="N60" s="35"/>
-      <c r="P60" s="75"/>
+      <c r="P60" s="64"/>
       <c r="Q60" s="6"/>
       <c r="T60" s="6"/>
       <c r="AT60"/>
-      <c r="AW60" s="79"/>
       <c r="AX60" s="6"/>
     </row>
     <row r="61" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M61" s="35"/>
       <c r="N61" s="35"/>
-      <c r="P61" s="75"/>
+      <c r="P61" s="64"/>
       <c r="Q61" s="6"/>
       <c r="T61" s="6"/>
       <c r="AT61"/>
-      <c r="AW61" s="79"/>
       <c r="AX61" s="6"/>
     </row>
     <row r="62" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M62" s="35"/>
       <c r="N62" s="35"/>
-      <c r="P62" s="75"/>
+      <c r="P62" s="64"/>
       <c r="Q62" s="6"/>
       <c r="T62" s="6"/>
       <c r="AT62"/>
-      <c r="AW62" s="79"/>
       <c r="AX62" s="6"/>
     </row>
     <row r="63" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M63" s="35"/>
       <c r="N63" s="35"/>
-      <c r="P63" s="75"/>
+      <c r="P63" s="64"/>
       <c r="Q63" s="6"/>
       <c r="T63" s="6"/>
       <c r="AT63"/>
-      <c r="AW63" s="79"/>
       <c r="AX63" s="6"/>
     </row>
     <row r="64" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M64" s="35"/>
       <c r="N64" s="35"/>
-      <c r="P64" s="75"/>
+      <c r="P64" s="64"/>
       <c r="Q64" s="6"/>
       <c r="T64" s="6"/>
       <c r="AT64"/>
-      <c r="AW64" s="79"/>
       <c r="AX64" s="6"/>
     </row>
     <row r="65" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M65" s="35"/>
       <c r="N65" s="35"/>
-      <c r="P65" s="75"/>
+      <c r="P65" s="64"/>
       <c r="Q65" s="6"/>
       <c r="T65" s="6"/>
       <c r="AT65"/>
-      <c r="AW65" s="79"/>
       <c r="AX65" s="6"/>
     </row>
     <row r="66" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M66" s="35"/>
       <c r="N66" s="35"/>
-      <c r="P66" s="75"/>
+      <c r="P66" s="64"/>
       <c r="Q66" s="6"/>
       <c r="T66" s="6"/>
       <c r="AT66"/>
-      <c r="AW66" s="79"/>
       <c r="AX66" s="6"/>
     </row>
     <row r="67" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M67" s="35"/>
       <c r="N67" s="35"/>
-      <c r="P67" s="75"/>
+      <c r="P67" s="64"/>
       <c r="Q67" s="6"/>
       <c r="T67" s="6"/>
       <c r="AT67"/>
-      <c r="AW67" s="79"/>
       <c r="AX67" s="6"/>
     </row>
     <row r="68" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M68" s="35"/>
       <c r="N68" s="35"/>
-      <c r="P68" s="75"/>
+      <c r="P68" s="64"/>
       <c r="Q68" s="6"/>
       <c r="T68" s="6"/>
       <c r="AT68"/>
-      <c r="AW68" s="79"/>
       <c r="AX68" s="6"/>
     </row>
     <row r="69" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M69" s="35"/>
       <c r="N69" s="35"/>
-      <c r="P69" s="75"/>
+      <c r="P69" s="64"/>
       <c r="Q69" s="6"/>
       <c r="T69" s="6"/>
       <c r="AT69"/>
-      <c r="AW69" s="79"/>
       <c r="AX69" s="6"/>
     </row>
     <row r="70" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M70" s="35"/>
       <c r="N70" s="35"/>
-      <c r="P70" s="75"/>
+      <c r="P70" s="64"/>
       <c r="Q70" s="6"/>
       <c r="T70" s="6"/>
       <c r="AT70"/>
-      <c r="AW70" s="79"/>
       <c r="AX70" s="6"/>
     </row>
     <row r="71" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M71" s="35"/>
       <c r="N71" s="35"/>
-      <c r="P71" s="75"/>
+      <c r="P71" s="64"/>
       <c r="Q71" s="6"/>
       <c r="T71" s="6"/>
       <c r="AT71"/>
-      <c r="AW71" s="79"/>
       <c r="AX71" s="6"/>
     </row>
     <row r="72" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M72" s="35"/>
       <c r="N72" s="35"/>
-      <c r="P72" s="75"/>
+      <c r="P72" s="64"/>
       <c r="Q72" s="6"/>
       <c r="T72" s="6"/>
       <c r="AT72"/>
-      <c r="AW72" s="79"/>
       <c r="AX72" s="6"/>
     </row>
     <row r="73" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M73" s="35"/>
       <c r="N73" s="35"/>
-      <c r="P73" s="75"/>
+      <c r="P73" s="64"/>
       <c r="Q73" s="6"/>
       <c r="T73" s="6"/>
       <c r="AT73"/>
-      <c r="AW73" s="79"/>
       <c r="AX73" s="6"/>
     </row>
     <row r="74" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M74" s="35"/>
       <c r="N74" s="35"/>
-      <c r="P74" s="75"/>
+      <c r="P74" s="64"/>
       <c r="Q74" s="6"/>
       <c r="T74" s="6"/>
       <c r="AT74"/>
-      <c r="AW74" s="79"/>
       <c r="AX74" s="6"/>
     </row>
     <row r="75" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M75" s="35"/>
       <c r="N75" s="35"/>
-      <c r="P75" s="75"/>
+      <c r="P75" s="64"/>
       <c r="Q75" s="6"/>
       <c r="T75" s="6"/>
       <c r="AT75"/>
-      <c r="AW75" s="79"/>
       <c r="AX75" s="6"/>
     </row>
     <row r="76" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M76" s="35"/>
       <c r="N76" s="35"/>
-      <c r="P76" s="75"/>
+      <c r="P76" s="64"/>
       <c r="Q76" s="6"/>
       <c r="T76" s="6"/>
       <c r="AT76"/>
-      <c r="AW76" s="79"/>
       <c r="AX76" s="6"/>
     </row>
     <row r="77" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
-      <c r="P77" s="75"/>
+      <c r="P77" s="64"/>
       <c r="Q77" s="6"/>
       <c r="T77" s="6"/>
       <c r="AT77"/>
-      <c r="AW77" s="79"/>
       <c r="AX77" s="6"/>
     </row>
     <row r="78" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
-      <c r="P78" s="75"/>
+      <c r="P78" s="64"/>
       <c r="Q78" s="6"/>
       <c r="T78" s="6"/>
       <c r="AT78"/>
-      <c r="AW78" s="79"/>
       <c r="AX78" s="6"/>
     </row>
     <row r="79" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
-      <c r="P79" s="75"/>
+      <c r="P79" s="64"/>
       <c r="Q79" s="6"/>
       <c r="T79" s="6"/>
       <c r="AT79"/>
-      <c r="AW79" s="79"/>
       <c r="AX79" s="6"/>
     </row>
     <row r="80" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M80" s="35"/>
       <c r="N80" s="35"/>
-      <c r="P80" s="75"/>
+      <c r="P80" s="64"/>
       <c r="Q80" s="6"/>
       <c r="T80" s="6"/>
       <c r="AT80"/>
-      <c r="AW80" s="79"/>
       <c r="AX80" s="6"/>
     </row>
     <row r="81" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M81" s="35"/>
       <c r="N81" s="35"/>
-      <c r="P81" s="75"/>
+      <c r="P81" s="64"/>
       <c r="Q81" s="6"/>
       <c r="T81" s="6"/>
       <c r="AT81"/>
-      <c r="AW81" s="79"/>
       <c r="AX81" s="6"/>
     </row>
     <row r="82" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M82" s="35"/>
       <c r="N82" s="35"/>
-      <c r="P82" s="75"/>
+      <c r="P82" s="64"/>
       <c r="Q82" s="6"/>
       <c r="T82" s="6"/>
       <c r="AT82"/>
-      <c r="AW82" s="79"/>
       <c r="AX82" s="6"/>
     </row>
     <row r="83" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M83" s="35"/>
       <c r="N83" s="35"/>
-      <c r="P83" s="75"/>
+      <c r="P83" s="64"/>
       <c r="Q83" s="6"/>
       <c r="T83" s="6"/>
       <c r="AT83"/>
-      <c r="AW83" s="79"/>
       <c r="AX83" s="6"/>
     </row>
     <row r="84" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M84" s="35"/>
       <c r="N84" s="35"/>
-      <c r="P84" s="75"/>
+      <c r="P84" s="64"/>
       <c r="Q84" s="6"/>
       <c r="T84" s="6"/>
       <c r="AT84"/>
-      <c r="AW84" s="79"/>
       <c r="AX84" s="6"/>
     </row>
     <row r="85" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M85" s="35"/>
       <c r="N85" s="35"/>
-      <c r="P85" s="75"/>
+      <c r="P85" s="64"/>
       <c r="Q85" s="6"/>
       <c r="T85" s="6"/>
       <c r="AT85"/>
-      <c r="AW85" s="79"/>
       <c r="AX85" s="6"/>
     </row>
     <row r="86" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M86" s="35"/>
       <c r="N86" s="35"/>
-      <c r="P86" s="75"/>
+      <c r="P86" s="64"/>
       <c r="Q86" s="6"/>
       <c r="T86" s="6"/>
       <c r="AT86"/>
-      <c r="AW86" s="79"/>
       <c r="AX86" s="6"/>
     </row>
     <row r="87" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M87" s="35"/>
       <c r="N87" s="35"/>
-      <c r="P87" s="75"/>
+      <c r="P87" s="64"/>
       <c r="Q87" s="6"/>
       <c r="T87" s="6"/>
       <c r="AT87"/>
-      <c r="AW87" s="79"/>
       <c r="AX87" s="6"/>
     </row>
     <row r="88" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M88" s="35"/>
       <c r="N88" s="35"/>
-      <c r="P88" s="75"/>
+      <c r="P88" s="64"/>
       <c r="Q88" s="6"/>
       <c r="T88" s="6"/>
       <c r="AT88"/>
-      <c r="AW88" s="79"/>
       <c r="AX88" s="6"/>
     </row>
     <row r="89" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M89" s="35"/>
       <c r="N89" s="35"/>
-      <c r="P89" s="75"/>
+      <c r="P89" s="64"/>
       <c r="Q89" s="6"/>
       <c r="T89" s="6"/>
       <c r="AT89"/>
-      <c r="AW89" s="79"/>
       <c r="AX89" s="6"/>
     </row>
     <row r="90" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M90" s="35"/>
       <c r="N90" s="35"/>
-      <c r="P90" s="75"/>
+      <c r="P90" s="64"/>
       <c r="Q90" s="6"/>
       <c r="T90" s="6"/>
       <c r="AT90"/>
-      <c r="AW90" s="79"/>
       <c r="AX90" s="6"/>
     </row>
     <row r="91" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M91" s="35"/>
       <c r="N91" s="35"/>
-      <c r="P91" s="75"/>
+      <c r="P91" s="64"/>
       <c r="Q91" s="6"/>
       <c r="T91" s="6"/>
       <c r="AT91"/>
-      <c r="AW91" s="79"/>
       <c r="AX91" s="6"/>
     </row>
     <row r="92" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M92" s="35"/>
       <c r="N92" s="35"/>
-      <c r="P92" s="75"/>
+      <c r="P92" s="64"/>
       <c r="Q92" s="6"/>
       <c r="T92" s="6"/>
       <c r="AT92"/>
-      <c r="AW92" s="79"/>
       <c r="AX92" s="6"/>
     </row>
     <row r="93" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M93" s="35"/>
       <c r="N93" s="35"/>
-      <c r="P93" s="75"/>
+      <c r="P93" s="64"/>
       <c r="Q93" s="6"/>
       <c r="T93" s="6"/>
       <c r="AT93"/>
-      <c r="AW93" s="79"/>
       <c r="AX93" s="6"/>
     </row>
     <row r="94" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M94" s="35"/>
       <c r="N94" s="35"/>
-      <c r="P94" s="75"/>
+      <c r="P94" s="64"/>
       <c r="Q94" s="6"/>
       <c r="T94" s="6"/>
       <c r="AT94"/>
-      <c r="AW94" s="79"/>
       <c r="AX94" s="6"/>
     </row>
     <row r="95" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M95" s="35"/>
       <c r="N95" s="35"/>
-      <c r="P95" s="75"/>
+      <c r="P95" s="64"/>
       <c r="Q95" s="6"/>
       <c r="T95" s="6"/>
       <c r="AT95"/>
-      <c r="AW95" s="79"/>
       <c r="AX95" s="6"/>
     </row>
     <row r="96" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M96" s="35"/>
       <c r="N96" s="35"/>
-      <c r="P96" s="75"/>
+      <c r="P96" s="64"/>
       <c r="Q96" s="6"/>
       <c r="T96" s="6"/>
       <c r="AT96"/>
-      <c r="AW96" s="79"/>
       <c r="AX96" s="6"/>
     </row>
     <row r="97" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M97" s="35"/>
       <c r="N97" s="35"/>
-      <c r="P97" s="75"/>
+      <c r="P97" s="64"/>
       <c r="Q97" s="6"/>
       <c r="T97" s="6"/>
       <c r="AT97"/>
-      <c r="AW97" s="79"/>
       <c r="AX97" s="6"/>
     </row>
     <row r="98" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M98" s="35"/>
       <c r="N98" s="35"/>
-      <c r="P98" s="75"/>
+      <c r="P98" s="64"/>
       <c r="Q98" s="6"/>
       <c r="T98" s="6"/>
       <c r="AT98"/>
-      <c r="AW98" s="79"/>
       <c r="AX98" s="6"/>
     </row>
     <row r="99" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M99" s="35"/>
       <c r="N99" s="35"/>
-      <c r="P99" s="75"/>
+      <c r="P99" s="64"/>
       <c r="Q99" s="6"/>
       <c r="T99" s="6"/>
       <c r="AT99"/>
-      <c r="AW99" s="79"/>
       <c r="AX99" s="6"/>
     </row>
     <row r="100" spans="13:50" x14ac:dyDescent="0.3">
       <c r="M100" s="35"/>
       <c r="N100" s="35"/>
-      <c r="P100" s="75"/>
+      <c r="P100" s="64"/>
       <c r="Q100" s="6"/>
       <c r="T100" s="6"/>
       <c r="AT100"/>
-      <c r="AW100" s="79"/>
       <c r="AX100" s="6"/>
     </row>
   </sheetData>
@@ -3765,7 +3667,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:CI100"/>
+  <dimension ref="A1:CJ100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" style="5" customWidth="1"/>
@@ -3773,131 +3675,132 @@
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" style="6" customWidth="1"/>
-    <col min="16" max="18" width="17.77734375" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="21" width="12.6640625" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" customWidth="1"/>
-    <col min="30" max="32" width="14.109375" customWidth="1"/>
-    <col min="33" max="33" width="16" style="6" customWidth="1"/>
-    <col min="34" max="34" width="12.6640625" customWidth="1"/>
-    <col min="35" max="35" width="11.33203125" customWidth="1"/>
-    <col min="36" max="36" width="10.6640625" customWidth="1"/>
-    <col min="45" max="47" width="14.109375" customWidth="1"/>
-    <col min="48" max="48" width="14" style="6" customWidth="1"/>
-    <col min="49" max="49" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="11.33203125" customWidth="1"/>
-    <col min="51" max="51" width="10.6640625" customWidth="1"/>
-    <col min="61" max="62" width="14.109375" customWidth="1"/>
-    <col min="63" max="63" width="14" style="6" customWidth="1"/>
-    <col min="64" max="64" width="12.44140625" customWidth="1"/>
-    <col min="76" max="76" width="8.88671875" style="5"/>
-    <col min="86" max="86" width="12.6640625" customWidth="1"/>
-    <col min="87" max="87" width="11.88671875" customWidth="1"/>
+    <col min="17" max="19" width="17.77734375" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" customWidth="1"/>
+    <col min="31" max="33" width="14.109375" customWidth="1"/>
+    <col min="34" max="34" width="16" style="6" customWidth="1"/>
+    <col min="35" max="35" width="12.6640625" customWidth="1"/>
+    <col min="36" max="36" width="11.33203125" customWidth="1"/>
+    <col min="37" max="37" width="10.6640625" customWidth="1"/>
+    <col min="46" max="48" width="14.109375" customWidth="1"/>
+    <col min="49" max="49" width="14" style="6" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="11.33203125" customWidth="1"/>
+    <col min="52" max="52" width="10.6640625" customWidth="1"/>
+    <col min="62" max="63" width="14.109375" customWidth="1"/>
+    <col min="64" max="64" width="14" style="6" customWidth="1"/>
+    <col min="65" max="65" width="12.44140625" customWidth="1"/>
+    <col min="77" max="77" width="8.88671875" style="5"/>
+    <col min="87" max="87" width="12.6640625" customWidth="1"/>
+    <col min="88" max="88" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="C1" s="68" t="s">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="C1" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="77" t="s">
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="64" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="75"/>
+      <c r="Z1" s="75"/>
+      <c r="AA1" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="AA1" s="64"/>
-      <c r="AB1" s="64"/>
-      <c r="AC1" s="64"/>
-      <c r="AD1" s="64"/>
-      <c r="AE1" s="64"/>
-      <c r="AF1" s="64"/>
-      <c r="AG1" s="64"/>
-      <c r="AH1" s="64"/>
-      <c r="AI1" s="64"/>
-      <c r="AJ1" s="64"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="64"/>
-      <c r="AN1" s="64"/>
-      <c r="AO1" s="63" t="s">
+      <c r="AB1" s="69"/>
+      <c r="AC1" s="69"/>
+      <c r="AD1" s="69"/>
+      <c r="AE1" s="69"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="69"/>
+      <c r="AH1" s="69"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AM1" s="69"/>
+      <c r="AN1" s="69"/>
+      <c r="AO1" s="69"/>
+      <c r="AP1" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="63"/>
-      <c r="AS1" s="63"/>
-      <c r="AT1" s="63"/>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="63"/>
-      <c r="AX1" s="63"/>
-      <c r="AY1" s="63"/>
-      <c r="AZ1" s="63"/>
-      <c r="BA1" s="63"/>
-      <c r="BB1" s="63"/>
-      <c r="BC1" s="63"/>
-      <c r="BD1" s="67" t="s">
+      <c r="AQ1" s="70"/>
+      <c r="AR1" s="70"/>
+      <c r="AS1" s="70"/>
+      <c r="AT1" s="70"/>
+      <c r="AU1" s="70"/>
+      <c r="AV1" s="70"/>
+      <c r="AW1" s="70"/>
+      <c r="AX1" s="70"/>
+      <c r="AY1" s="70"/>
+      <c r="AZ1" s="70"/>
+      <c r="BA1" s="70"/>
+      <c r="BB1" s="70"/>
+      <c r="BC1" s="70"/>
+      <c r="BD1" s="70"/>
+      <c r="BE1" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="BE1" s="67"/>
-      <c r="BF1" s="67"/>
-      <c r="BG1" s="67"/>
-      <c r="BH1" s="67"/>
-      <c r="BI1" s="67"/>
-      <c r="BJ1" s="67"/>
-      <c r="BK1" s="67"/>
-      <c r="BL1" s="67"/>
-      <c r="BM1" s="67"/>
-      <c r="BN1" s="67"/>
-      <c r="BO1" s="67"/>
-      <c r="BP1" s="67"/>
-      <c r="BQ1" s="67"/>
-      <c r="BR1" s="67"/>
-      <c r="BS1" s="78" t="s">
+      <c r="BF1" s="68"/>
+      <c r="BG1" s="68"/>
+      <c r="BH1" s="68"/>
+      <c r="BI1" s="68"/>
+      <c r="BJ1" s="68"/>
+      <c r="BK1" s="68"/>
+      <c r="BL1" s="68"/>
+      <c r="BM1" s="68"/>
+      <c r="BN1" s="68"/>
+      <c r="BO1" s="68"/>
+      <c r="BP1" s="68"/>
+      <c r="BQ1" s="68"/>
+      <c r="BR1" s="68"/>
+      <c r="BS1" s="68"/>
+      <c r="BT1" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="BT1" s="78"/>
-      <c r="BU1" s="78"/>
-      <c r="BV1" s="78"/>
-      <c r="BW1" s="78"/>
-      <c r="BX1" s="78"/>
-      <c r="BY1" s="78"/>
-      <c r="BZ1" s="78"/>
-      <c r="CA1" s="78"/>
-      <c r="CB1" s="78"/>
-      <c r="CC1" s="78"/>
-      <c r="CD1" s="78"/>
-      <c r="CE1" s="78"/>
-      <c r="CF1" s="78"/>
-      <c r="CG1" s="78"/>
-      <c r="CH1" s="64" t="s">
+      <c r="BU1" s="73"/>
+      <c r="BV1" s="73"/>
+      <c r="BW1" s="73"/>
+      <c r="BX1" s="73"/>
+      <c r="BY1" s="73"/>
+      <c r="BZ1" s="73"/>
+      <c r="CA1" s="73"/>
+      <c r="CB1" s="73"/>
+      <c r="CC1" s="73"/>
+      <c r="CD1" s="73"/>
+      <c r="CE1" s="73"/>
+      <c r="CF1" s="73"/>
+      <c r="CG1" s="73"/>
+      <c r="CH1" s="73"/>
+      <c r="CI1" s="69" t="s">
         <v>210</v>
       </c>
-      <c r="CI1" s="64"/>
-    </row>
-    <row r="2" spans="1:87" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="CJ1" s="69"/>
+    </row>
+    <row r="2" spans="1:88" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>5</v>
       </c>
@@ -3941,3567 +3844,3570 @@
         <v>106</v>
       </c>
       <c r="O2" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="P2" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="Q2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="R2" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="T2" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="U2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="21" t="s">
+      <c r="V2" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="W2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="X2" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Z2" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="Z2" s="28" t="s">
+      <c r="AA2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="28" t="s">
+      <c r="AB2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="28" t="s">
+      <c r="AC2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="28" t="s">
+      <c r="AD2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="AD2" s="28" t="s">
+      <c r="AE2" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AE2" s="28" t="s">
+      <c r="AF2" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="AF2" s="23" t="s">
+      <c r="AG2" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="AG2" s="28" t="s">
+      <c r="AH2" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="AH2" s="23" t="s">
+      <c r="AI2" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="AI2" s="28" t="s">
+      <c r="AJ2" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AK2" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="AK2" s="28" t="s">
+      <c r="AL2" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AL2" s="56" t="s">
+      <c r="AM2" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="AM2" s="62" t="s">
+      <c r="AN2" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="AN2" s="61" t="s">
+      <c r="AO2" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="AO2" s="29" t="s">
+      <c r="AP2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AP2" s="29" t="s">
+      <c r="AQ2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AQ2" s="29" t="s">
+      <c r="AR2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="AR2" s="29" t="s">
+      <c r="AS2" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="AS2" s="29" t="s">
+      <c r="AT2" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AT2" s="29" t="s">
+      <c r="AU2" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="AU2" s="31" t="s">
+      <c r="AV2" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="AV2" s="29" t="s">
+      <c r="AW2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="AW2" s="31" t="s">
+      <c r="AX2" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="AX2" s="29" t="s">
+      <c r="AY2" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="AY2" s="31" t="s">
+      <c r="AZ2" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AZ2" s="29" t="s">
+      <c r="BA2" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="BA2" s="55" t="s">
+      <c r="BB2" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="BB2" s="30" t="s">
+      <c r="BC2" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="BC2" s="32" t="s">
+      <c r="BD2" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="BD2" s="33" t="s">
+      <c r="BE2" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="BE2" s="33" t="s">
+      <c r="BF2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="BF2" s="33" t="s">
+      <c r="BG2" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="BG2" s="33" t="s">
+      <c r="BH2" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BI2" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="BI2" s="33" t="s">
+      <c r="BJ2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="BJ2" s="34" t="s">
+      <c r="BK2" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BL2" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BL2" s="34" t="s">
+      <c r="BM2" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="BM2" s="33" t="s">
+      <c r="BN2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="BN2" s="34" t="s">
+      <c r="BO2" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BO2" s="33" t="s">
+      <c r="BP2" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="BP2" s="53" t="s">
+      <c r="BQ2" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="BQ2" s="57" t="s">
+      <c r="BR2" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="BR2" s="58" t="s">
+      <c r="BS2" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="BS2" s="40" t="s">
+      <c r="BT2" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="BT2" s="41" t="s">
+      <c r="BU2" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="BU2" s="41" t="s">
+      <c r="BV2" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="BV2" s="41" t="s">
+      <c r="BW2" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="BW2" s="41" t="s">
+      <c r="BX2" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="BX2" s="41" t="s">
+      <c r="BY2" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="BY2" s="42" t="s">
+      <c r="BZ2" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="BZ2" s="41" t="s">
+      <c r="CA2" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="CA2" s="42" t="s">
+      <c r="CB2" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="CB2" s="41" t="s">
+      <c r="CC2" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="CC2" s="42" t="s">
+      <c r="CD2" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="CD2" s="41" t="s">
+      <c r="CE2" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="CE2" s="54" t="s">
+      <c r="CF2" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="CF2" s="41" t="s">
+      <c r="CG2" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="CG2" s="59" t="s">
+      <c r="CH2" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="CH2" s="10" t="s">
+      <c r="CI2" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="CI2" s="10" t="s">
+      <c r="CJ2" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3"/>
-      <c r="AH3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="60"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3"/>
-      <c r="AW3" s="35"/>
-      <c r="AY3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="39"/>
-      <c r="BJ3" s="35"/>
-      <c r="BK3"/>
-      <c r="BL3" s="35"/>
-      <c r="BN3" s="35"/>
-      <c r="BP3" s="35"/>
-      <c r="BR3" s="35"/>
-      <c r="BX3"/>
-      <c r="BY3" s="35"/>
-      <c r="CA3" s="35"/>
-      <c r="CC3" s="35"/>
-      <c r="CE3" s="35"/>
-      <c r="CG3" s="82"/>
-      <c r="CH3" s="35"/>
+    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3"/>
+      <c r="AI3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="60"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3"/>
+      <c r="AX3" s="35"/>
+      <c r="AZ3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BD3" s="35"/>
+      <c r="BE3" s="39"/>
+      <c r="BK3" s="35"/>
+      <c r="BL3"/>
+      <c r="BM3" s="35"/>
+      <c r="BO3" s="35"/>
+      <c r="BQ3" s="35"/>
+      <c r="BS3" s="35"/>
+      <c r="BY3"/>
+      <c r="BZ3" s="35"/>
+      <c r="CB3" s="35"/>
+      <c r="CD3" s="35"/>
+      <c r="CF3" s="35"/>
+      <c r="CH3" s="66"/>
       <c r="CI3" s="35"/>
-    </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4"/>
-      <c r="AH4" s="35"/>
-      <c r="AJ4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AN4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4"/>
-      <c r="AW4" s="35"/>
-      <c r="AY4" s="35"/>
-      <c r="BA4" s="35"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="20"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4"/>
-      <c r="BL4" s="35"/>
-      <c r="BN4" s="35"/>
-      <c r="BP4" s="35"/>
-      <c r="BR4" s="35"/>
-      <c r="BX4"/>
-      <c r="BY4" s="35"/>
-      <c r="CA4" s="35"/>
-      <c r="CC4" s="35"/>
-      <c r="CE4" s="35"/>
-      <c r="CG4" s="38"/>
-      <c r="CH4" s="35"/>
+      <c r="CJ3" s="35"/>
+    </row>
+    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4"/>
+      <c r="AI4" s="35"/>
+      <c r="AK4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4"/>
+      <c r="AX4" s="35"/>
+      <c r="AZ4" s="35"/>
+      <c r="BB4" s="35"/>
+      <c r="BD4" s="35"/>
+      <c r="BE4" s="20"/>
+      <c r="BK4" s="35"/>
+      <c r="BL4"/>
+      <c r="BM4" s="35"/>
+      <c r="BO4" s="35"/>
+      <c r="BQ4" s="35"/>
+      <c r="BS4" s="35"/>
+      <c r="BY4"/>
+      <c r="BZ4" s="35"/>
+      <c r="CB4" s="35"/>
+      <c r="CD4" s="35"/>
+      <c r="CF4" s="35"/>
+      <c r="CH4" s="38"/>
       <c r="CI4" s="35"/>
-    </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="AF5" s="35"/>
-      <c r="AG5"/>
-      <c r="AH5" s="35"/>
-      <c r="AJ5" s="35"/>
-      <c r="AL5" s="35"/>
-      <c r="AN5" s="35"/>
-      <c r="AU5" s="35"/>
-      <c r="AV5"/>
-      <c r="AW5" s="35"/>
-      <c r="AY5" s="35"/>
-      <c r="BA5" s="35"/>
-      <c r="BC5" s="35"/>
-      <c r="BD5" s="20"/>
-      <c r="BJ5" s="35"/>
-      <c r="BK5"/>
-      <c r="BL5" s="35"/>
-      <c r="BN5" s="35"/>
-      <c r="BP5" s="35"/>
-      <c r="BR5" s="35"/>
-      <c r="BX5"/>
-      <c r="BY5" s="35"/>
-      <c r="CA5" s="35"/>
-      <c r="CC5" s="35"/>
-      <c r="CE5" s="35"/>
-      <c r="CG5" s="38"/>
-      <c r="CH5" s="35"/>
+      <c r="CJ4" s="35"/>
+    </row>
+    <row r="5" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AG5" s="35"/>
+      <c r="AH5"/>
+      <c r="AI5" s="35"/>
+      <c r="AK5" s="35"/>
+      <c r="AM5" s="35"/>
+      <c r="AO5" s="35"/>
+      <c r="AV5" s="35"/>
+      <c r="AW5"/>
+      <c r="AX5" s="35"/>
+      <c r="AZ5" s="35"/>
+      <c r="BB5" s="35"/>
+      <c r="BD5" s="35"/>
+      <c r="BE5" s="20"/>
+      <c r="BK5" s="35"/>
+      <c r="BL5"/>
+      <c r="BM5" s="35"/>
+      <c r="BO5" s="35"/>
+      <c r="BQ5" s="35"/>
+      <c r="BS5" s="35"/>
+      <c r="BY5"/>
+      <c r="BZ5" s="35"/>
+      <c r="CB5" s="35"/>
+      <c r="CD5" s="35"/>
+      <c r="CF5" s="35"/>
+      <c r="CH5" s="38"/>
       <c r="CI5" s="35"/>
-    </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6"/>
-      <c r="AH6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AN6" s="35"/>
-      <c r="AU6" s="35"/>
-      <c r="AV6"/>
-      <c r="AW6" s="35"/>
-      <c r="AY6" s="35"/>
-      <c r="BA6" s="35"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="20"/>
-      <c r="BJ6" s="35"/>
-      <c r="BK6"/>
-      <c r="BL6" s="35"/>
-      <c r="BN6" s="35"/>
-      <c r="BP6" s="35"/>
-      <c r="BR6" s="35"/>
-      <c r="BX6"/>
-      <c r="BY6" s="35"/>
-      <c r="CA6" s="35"/>
-      <c r="CC6" s="35"/>
-      <c r="CE6" s="35"/>
-      <c r="CG6" s="38"/>
-      <c r="CH6" s="35"/>
+      <c r="CJ5" s="35"/>
+    </row>
+    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AG6" s="35"/>
+      <c r="AH6"/>
+      <c r="AI6" s="35"/>
+      <c r="AK6" s="35"/>
+      <c r="AM6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6"/>
+      <c r="AX6" s="35"/>
+      <c r="AZ6" s="35"/>
+      <c r="BB6" s="35"/>
+      <c r="BD6" s="35"/>
+      <c r="BE6" s="20"/>
+      <c r="BK6" s="35"/>
+      <c r="BL6"/>
+      <c r="BM6" s="35"/>
+      <c r="BO6" s="35"/>
+      <c r="BQ6" s="35"/>
+      <c r="BS6" s="35"/>
+      <c r="BY6"/>
+      <c r="BZ6" s="35"/>
+      <c r="CB6" s="35"/>
+      <c r="CD6" s="35"/>
+      <c r="CF6" s="35"/>
+      <c r="CH6" s="38"/>
       <c r="CI6" s="35"/>
-    </row>
-    <row r="7" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="AF7" s="35"/>
-      <c r="AG7"/>
-      <c r="AH7" s="35"/>
-      <c r="AJ7" s="35"/>
-      <c r="AL7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AU7" s="35"/>
-      <c r="AV7"/>
-      <c r="AW7" s="35"/>
-      <c r="AY7" s="35"/>
-      <c r="BA7" s="35"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="20"/>
-      <c r="BJ7" s="35"/>
-      <c r="BK7"/>
-      <c r="BL7" s="35"/>
-      <c r="BN7" s="35"/>
-      <c r="BP7" s="35"/>
-      <c r="BR7" s="35"/>
-      <c r="BX7"/>
-      <c r="BY7" s="35"/>
-      <c r="CA7" s="35"/>
-      <c r="CC7" s="35"/>
-      <c r="CE7" s="35"/>
-      <c r="CG7" s="38"/>
-      <c r="CH7" s="35"/>
+      <c r="CJ6" s="35"/>
+    </row>
+    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7"/>
+      <c r="AI7" s="35"/>
+      <c r="AK7" s="35"/>
+      <c r="AM7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7"/>
+      <c r="AX7" s="35"/>
+      <c r="AZ7" s="35"/>
+      <c r="BB7" s="35"/>
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="20"/>
+      <c r="BK7" s="35"/>
+      <c r="BL7"/>
+      <c r="BM7" s="35"/>
+      <c r="BO7" s="35"/>
+      <c r="BQ7" s="35"/>
+      <c r="BS7" s="35"/>
+      <c r="BY7"/>
+      <c r="BZ7" s="35"/>
+      <c r="CB7" s="35"/>
+      <c r="CD7" s="35"/>
+      <c r="CF7" s="35"/>
+      <c r="CH7" s="38"/>
       <c r="CI7" s="35"/>
-    </row>
-    <row r="8" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="AF8" s="35"/>
-      <c r="AG8"/>
-      <c r="AH8" s="35"/>
-      <c r="AJ8" s="35"/>
-      <c r="AL8" s="35"/>
-      <c r="AN8" s="35"/>
-      <c r="AU8" s="35"/>
-      <c r="AV8"/>
-      <c r="AW8" s="35"/>
-      <c r="AY8" s="35"/>
-      <c r="BA8" s="35"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="20"/>
-      <c r="BJ8" s="35"/>
-      <c r="BK8"/>
-      <c r="BL8" s="35"/>
-      <c r="BN8" s="35"/>
-      <c r="BP8" s="35"/>
-      <c r="BR8" s="35"/>
-      <c r="BX8"/>
-      <c r="BY8" s="35"/>
-      <c r="CA8" s="35"/>
-      <c r="CC8" s="35"/>
-      <c r="CE8" s="35"/>
-      <c r="CG8" s="38"/>
-      <c r="CH8" s="35"/>
+      <c r="CJ7" s="35"/>
+    </row>
+    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AG8" s="35"/>
+      <c r="AH8"/>
+      <c r="AI8" s="35"/>
+      <c r="AK8" s="35"/>
+      <c r="AM8" s="35"/>
+      <c r="AO8" s="35"/>
+      <c r="AV8" s="35"/>
+      <c r="AW8"/>
+      <c r="AX8" s="35"/>
+      <c r="AZ8" s="35"/>
+      <c r="BB8" s="35"/>
+      <c r="BD8" s="35"/>
+      <c r="BE8" s="20"/>
+      <c r="BK8" s="35"/>
+      <c r="BL8"/>
+      <c r="BM8" s="35"/>
+      <c r="BO8" s="35"/>
+      <c r="BQ8" s="35"/>
+      <c r="BS8" s="35"/>
+      <c r="BY8"/>
+      <c r="BZ8" s="35"/>
+      <c r="CB8" s="35"/>
+      <c r="CD8" s="35"/>
+      <c r="CF8" s="35"/>
+      <c r="CH8" s="38"/>
       <c r="CI8" s="35"/>
-    </row>
-    <row r="9" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9"/>
-      <c r="AH9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AL9" s="35"/>
-      <c r="AN9" s="35"/>
-      <c r="AU9" s="35"/>
-      <c r="AV9"/>
-      <c r="AW9" s="35"/>
-      <c r="AY9" s="35"/>
-      <c r="BA9" s="35"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="20"/>
-      <c r="BJ9" s="35"/>
-      <c r="BK9"/>
-      <c r="BL9" s="35"/>
-      <c r="BN9" s="35"/>
-      <c r="BP9" s="35"/>
-      <c r="BR9" s="35"/>
-      <c r="BX9"/>
-      <c r="BY9" s="35"/>
-      <c r="CA9" s="35"/>
-      <c r="CC9" s="35"/>
-      <c r="CE9" s="35"/>
-      <c r="CG9" s="38"/>
-      <c r="CH9" s="35"/>
+      <c r="CJ8" s="35"/>
+    </row>
+    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AG9" s="35"/>
+      <c r="AH9"/>
+      <c r="AI9" s="35"/>
+      <c r="AK9" s="35"/>
+      <c r="AM9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9"/>
+      <c r="AX9" s="35"/>
+      <c r="AZ9" s="35"/>
+      <c r="BB9" s="35"/>
+      <c r="BD9" s="35"/>
+      <c r="BE9" s="20"/>
+      <c r="BK9" s="35"/>
+      <c r="BL9"/>
+      <c r="BM9" s="35"/>
+      <c r="BO9" s="35"/>
+      <c r="BQ9" s="35"/>
+      <c r="BS9" s="35"/>
+      <c r="BY9"/>
+      <c r="BZ9" s="35"/>
+      <c r="CB9" s="35"/>
+      <c r="CD9" s="35"/>
+      <c r="CF9" s="35"/>
+      <c r="CH9" s="38"/>
       <c r="CI9" s="35"/>
-    </row>
-    <row r="10" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10"/>
-      <c r="AH10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AL10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10"/>
-      <c r="AW10" s="35"/>
-      <c r="AY10" s="35"/>
-      <c r="BA10" s="35"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="20"/>
-      <c r="BJ10" s="35"/>
-      <c r="BK10"/>
-      <c r="BL10" s="35"/>
-      <c r="BN10" s="35"/>
-      <c r="BP10" s="35"/>
-      <c r="BR10" s="35"/>
-      <c r="BX10"/>
-      <c r="BY10" s="35"/>
-      <c r="CA10" s="35"/>
-      <c r="CC10" s="35"/>
-      <c r="CE10" s="35"/>
-      <c r="CG10" s="38"/>
-      <c r="CH10" s="35"/>
+      <c r="CJ9" s="35"/>
+    </row>
+    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10"/>
+      <c r="AI10" s="35"/>
+      <c r="AK10" s="35"/>
+      <c r="AM10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AV10" s="35"/>
+      <c r="AW10"/>
+      <c r="AX10" s="35"/>
+      <c r="AZ10" s="35"/>
+      <c r="BB10" s="35"/>
+      <c r="BD10" s="35"/>
+      <c r="BE10" s="20"/>
+      <c r="BK10" s="35"/>
+      <c r="BL10"/>
+      <c r="BM10" s="35"/>
+      <c r="BO10" s="35"/>
+      <c r="BQ10" s="35"/>
+      <c r="BS10" s="35"/>
+      <c r="BY10"/>
+      <c r="BZ10" s="35"/>
+      <c r="CB10" s="35"/>
+      <c r="CD10" s="35"/>
+      <c r="CF10" s="35"/>
+      <c r="CH10" s="38"/>
       <c r="CI10" s="35"/>
-    </row>
-    <row r="11" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="AF11" s="35"/>
-      <c r="AG11"/>
-      <c r="AH11" s="35"/>
-      <c r="AJ11" s="35"/>
-      <c r="AL11" s="35"/>
-      <c r="AN11" s="35"/>
-      <c r="AU11" s="35"/>
-      <c r="AV11"/>
-      <c r="AW11" s="35"/>
-      <c r="AY11" s="35"/>
-      <c r="BA11" s="35"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="20"/>
-      <c r="BJ11" s="35"/>
-      <c r="BK11"/>
-      <c r="BL11" s="35"/>
-      <c r="BN11" s="35"/>
-      <c r="BP11" s="35"/>
-      <c r="BR11" s="35"/>
-      <c r="BX11"/>
-      <c r="BY11" s="35"/>
-      <c r="CA11" s="35"/>
-      <c r="CC11" s="35"/>
-      <c r="CE11" s="35"/>
-      <c r="CG11" s="38"/>
-      <c r="CH11" s="35"/>
+      <c r="CJ10" s="35"/>
+    </row>
+    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AG11" s="35"/>
+      <c r="AH11"/>
+      <c r="AI11" s="35"/>
+      <c r="AK11" s="35"/>
+      <c r="AM11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AV11" s="35"/>
+      <c r="AW11"/>
+      <c r="AX11" s="35"/>
+      <c r="AZ11" s="35"/>
+      <c r="BB11" s="35"/>
+      <c r="BD11" s="35"/>
+      <c r="BE11" s="20"/>
+      <c r="BK11" s="35"/>
+      <c r="BL11"/>
+      <c r="BM11" s="35"/>
+      <c r="BO11" s="35"/>
+      <c r="BQ11" s="35"/>
+      <c r="BS11" s="35"/>
+      <c r="BY11"/>
+      <c r="BZ11" s="35"/>
+      <c r="CB11" s="35"/>
+      <c r="CD11" s="35"/>
+      <c r="CF11" s="35"/>
+      <c r="CH11" s="38"/>
       <c r="CI11" s="35"/>
-    </row>
-    <row r="12" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="AF12" s="35"/>
-      <c r="AG12"/>
-      <c r="AH12" s="35"/>
-      <c r="AJ12" s="35"/>
-      <c r="AL12" s="35"/>
-      <c r="AN12" s="35"/>
-      <c r="AU12" s="35"/>
-      <c r="AV12"/>
-      <c r="AW12" s="35"/>
-      <c r="AY12" s="35"/>
-      <c r="BA12" s="35"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="20"/>
-      <c r="BJ12" s="35"/>
-      <c r="BK12"/>
-      <c r="BL12" s="35"/>
-      <c r="BN12" s="35"/>
-      <c r="BP12" s="35"/>
-      <c r="BR12" s="35"/>
-      <c r="BX12"/>
-      <c r="BY12" s="35"/>
-      <c r="CA12" s="35"/>
-      <c r="CC12" s="35"/>
-      <c r="CE12" s="35"/>
-      <c r="CG12" s="38"/>
-      <c r="CH12" s="35"/>
+      <c r="CJ11" s="35"/>
+    </row>
+    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AG12" s="35"/>
+      <c r="AH12"/>
+      <c r="AI12" s="35"/>
+      <c r="AK12" s="35"/>
+      <c r="AM12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12"/>
+      <c r="AX12" s="35"/>
+      <c r="AZ12" s="35"/>
+      <c r="BB12" s="35"/>
+      <c r="BD12" s="35"/>
+      <c r="BE12" s="20"/>
+      <c r="BK12" s="35"/>
+      <c r="BL12"/>
+      <c r="BM12" s="35"/>
+      <c r="BO12" s="35"/>
+      <c r="BQ12" s="35"/>
+      <c r="BS12" s="35"/>
+      <c r="BY12"/>
+      <c r="BZ12" s="35"/>
+      <c r="CB12" s="35"/>
+      <c r="CD12" s="35"/>
+      <c r="CF12" s="35"/>
+      <c r="CH12" s="38"/>
       <c r="CI12" s="35"/>
-    </row>
-    <row r="13" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13"/>
-      <c r="AH13" s="35"/>
-      <c r="AJ13" s="35"/>
-      <c r="AL13" s="35"/>
-      <c r="AN13" s="35"/>
-      <c r="AU13" s="35"/>
-      <c r="AV13"/>
-      <c r="AW13" s="35"/>
-      <c r="AY13" s="35"/>
-      <c r="BA13" s="35"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="20"/>
-      <c r="BJ13" s="35"/>
-      <c r="BK13"/>
-      <c r="BL13" s="35"/>
-      <c r="BN13" s="35"/>
-      <c r="BP13" s="35"/>
-      <c r="BR13" s="35"/>
-      <c r="BX13"/>
-      <c r="BY13" s="35"/>
-      <c r="CA13" s="35"/>
-      <c r="CC13" s="35"/>
-      <c r="CE13" s="35"/>
-      <c r="CG13" s="38"/>
-      <c r="CH13" s="35"/>
+      <c r="CJ12" s="35"/>
+    </row>
+    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AG13" s="35"/>
+      <c r="AH13"/>
+      <c r="AI13" s="35"/>
+      <c r="AK13" s="35"/>
+      <c r="AM13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AV13" s="35"/>
+      <c r="AW13"/>
+      <c r="AX13" s="35"/>
+      <c r="AZ13" s="35"/>
+      <c r="BB13" s="35"/>
+      <c r="BD13" s="35"/>
+      <c r="BE13" s="20"/>
+      <c r="BK13" s="35"/>
+      <c r="BL13"/>
+      <c r="BM13" s="35"/>
+      <c r="BO13" s="35"/>
+      <c r="BQ13" s="35"/>
+      <c r="BS13" s="35"/>
+      <c r="BY13"/>
+      <c r="BZ13" s="35"/>
+      <c r="CB13" s="35"/>
+      <c r="CD13" s="35"/>
+      <c r="CF13" s="35"/>
+      <c r="CH13" s="38"/>
       <c r="CI13" s="35"/>
-    </row>
-    <row r="14" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14"/>
-      <c r="AH14" s="35"/>
-      <c r="AJ14" s="35"/>
-      <c r="AL14" s="35"/>
-      <c r="AN14" s="35"/>
-      <c r="AU14" s="35"/>
-      <c r="AV14"/>
-      <c r="AW14" s="35"/>
-      <c r="AY14" s="35"/>
-      <c r="BA14" s="35"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="20"/>
-      <c r="BJ14" s="35"/>
-      <c r="BK14"/>
-      <c r="BL14" s="35"/>
-      <c r="BN14" s="35"/>
-      <c r="BP14" s="35"/>
-      <c r="BR14" s="35"/>
-      <c r="BX14"/>
-      <c r="BY14" s="35"/>
-      <c r="CA14" s="35"/>
-      <c r="CC14" s="35"/>
-      <c r="CE14" s="35"/>
-      <c r="CG14" s="38"/>
-      <c r="CH14" s="35"/>
+      <c r="CJ13" s="35"/>
+    </row>
+    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AG14" s="35"/>
+      <c r="AH14"/>
+      <c r="AI14" s="35"/>
+      <c r="AK14" s="35"/>
+      <c r="AM14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AV14" s="35"/>
+      <c r="AW14"/>
+      <c r="AX14" s="35"/>
+      <c r="AZ14" s="35"/>
+      <c r="BB14" s="35"/>
+      <c r="BD14" s="35"/>
+      <c r="BE14" s="20"/>
+      <c r="BK14" s="35"/>
+      <c r="BL14"/>
+      <c r="BM14" s="35"/>
+      <c r="BO14" s="35"/>
+      <c r="BQ14" s="35"/>
+      <c r="BS14" s="35"/>
+      <c r="BY14"/>
+      <c r="BZ14" s="35"/>
+      <c r="CB14" s="35"/>
+      <c r="CD14" s="35"/>
+      <c r="CF14" s="35"/>
+      <c r="CH14" s="38"/>
       <c r="CI14" s="35"/>
-    </row>
-    <row r="15" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15"/>
-      <c r="AH15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AL15" s="35"/>
-      <c r="AN15" s="35"/>
-      <c r="AU15" s="35"/>
-      <c r="AV15"/>
-      <c r="AW15" s="35"/>
-      <c r="AY15" s="35"/>
-      <c r="BA15" s="35"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="20"/>
-      <c r="BJ15" s="35"/>
-      <c r="BK15"/>
-      <c r="BL15" s="35"/>
-      <c r="BN15" s="35"/>
-      <c r="BP15" s="35"/>
-      <c r="BR15" s="35"/>
-      <c r="BX15"/>
-      <c r="BY15" s="35"/>
-      <c r="CA15" s="35"/>
-      <c r="CC15" s="35"/>
-      <c r="CE15" s="35"/>
-      <c r="CG15" s="38"/>
-      <c r="CH15" s="35"/>
+      <c r="CJ14" s="35"/>
+    </row>
+    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15"/>
+      <c r="AI15" s="35"/>
+      <c r="AK15" s="35"/>
+      <c r="AM15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AV15" s="35"/>
+      <c r="AW15"/>
+      <c r="AX15" s="35"/>
+      <c r="AZ15" s="35"/>
+      <c r="BB15" s="35"/>
+      <c r="BD15" s="35"/>
+      <c r="BE15" s="20"/>
+      <c r="BK15" s="35"/>
+      <c r="BL15"/>
+      <c r="BM15" s="35"/>
+      <c r="BO15" s="35"/>
+      <c r="BQ15" s="35"/>
+      <c r="BS15" s="35"/>
+      <c r="BY15"/>
+      <c r="BZ15" s="35"/>
+      <c r="CB15" s="35"/>
+      <c r="CD15" s="35"/>
+      <c r="CF15" s="35"/>
+      <c r="CH15" s="38"/>
       <c r="CI15" s="35"/>
-    </row>
-    <row r="16" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="Q16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16"/>
-      <c r="AH16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AL16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16"/>
-      <c r="AW16" s="35"/>
-      <c r="AY16" s="35"/>
-      <c r="BA16" s="35"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="20"/>
-      <c r="BJ16" s="35"/>
-      <c r="BK16"/>
-      <c r="BL16" s="35"/>
-      <c r="BN16" s="35"/>
-      <c r="BP16" s="35"/>
-      <c r="BR16" s="35"/>
-      <c r="BX16"/>
-      <c r="BY16" s="35"/>
-      <c r="CA16" s="35"/>
-      <c r="CC16" s="35"/>
-      <c r="CE16" s="35"/>
-      <c r="CG16" s="38"/>
-      <c r="CH16" s="35"/>
+      <c r="CJ15" s="35"/>
+    </row>
+    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="R16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16"/>
+      <c r="AI16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16"/>
+      <c r="AX16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BB16" s="35"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="20"/>
+      <c r="BK16" s="35"/>
+      <c r="BL16"/>
+      <c r="BM16" s="35"/>
+      <c r="BO16" s="35"/>
+      <c r="BQ16" s="35"/>
+      <c r="BS16" s="35"/>
+      <c r="BY16"/>
+      <c r="BZ16" s="35"/>
+      <c r="CB16" s="35"/>
+      <c r="CD16" s="35"/>
+      <c r="CF16" s="35"/>
+      <c r="CH16" s="38"/>
       <c r="CI16" s="35"/>
-    </row>
-    <row r="17" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17"/>
-      <c r="AH17" s="35"/>
-      <c r="AJ17" s="35"/>
-      <c r="AL17" s="35"/>
-      <c r="AN17" s="35"/>
-      <c r="AU17" s="35"/>
-      <c r="AV17"/>
-      <c r="AW17" s="35"/>
-      <c r="AY17" s="35"/>
-      <c r="BA17" s="35"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="20"/>
-      <c r="BJ17" s="35"/>
-      <c r="BK17"/>
-      <c r="BL17" s="35"/>
-      <c r="BN17" s="35"/>
-      <c r="BP17" s="35"/>
-      <c r="BR17" s="35"/>
-      <c r="BX17"/>
-      <c r="BY17" s="35"/>
-      <c r="CA17" s="35"/>
-      <c r="CC17" s="35"/>
-      <c r="CE17" s="35"/>
-      <c r="CG17" s="38"/>
-      <c r="CH17" s="35"/>
+      <c r="CJ16" s="35"/>
+    </row>
+    <row r="17" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17"/>
+      <c r="AI17" s="35"/>
+      <c r="AK17" s="35"/>
+      <c r="AM17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AV17" s="35"/>
+      <c r="AW17"/>
+      <c r="AX17" s="35"/>
+      <c r="AZ17" s="35"/>
+      <c r="BB17" s="35"/>
+      <c r="BD17" s="35"/>
+      <c r="BE17" s="20"/>
+      <c r="BK17" s="35"/>
+      <c r="BL17"/>
+      <c r="BM17" s="35"/>
+      <c r="BO17" s="35"/>
+      <c r="BQ17" s="35"/>
+      <c r="BS17" s="35"/>
+      <c r="BY17"/>
+      <c r="BZ17" s="35"/>
+      <c r="CB17" s="35"/>
+      <c r="CD17" s="35"/>
+      <c r="CF17" s="35"/>
+      <c r="CH17" s="38"/>
       <c r="CI17" s="35"/>
-    </row>
-    <row r="18" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18"/>
-      <c r="AH18" s="35"/>
-      <c r="AJ18" s="35"/>
-      <c r="AL18" s="35"/>
-      <c r="AN18" s="35"/>
-      <c r="AU18" s="35"/>
-      <c r="AV18"/>
-      <c r="AW18" s="35"/>
-      <c r="AY18" s="35"/>
-      <c r="BA18" s="35"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="20"/>
-      <c r="BJ18" s="35"/>
-      <c r="BK18"/>
-      <c r="BL18" s="35"/>
-      <c r="BN18" s="35"/>
-      <c r="BP18" s="35"/>
-      <c r="BR18" s="35"/>
-      <c r="BX18"/>
-      <c r="BY18" s="35"/>
-      <c r="CA18" s="35"/>
-      <c r="CC18" s="35"/>
-      <c r="CE18" s="35"/>
-      <c r="CG18" s="38"/>
-      <c r="CH18" s="35"/>
+      <c r="CJ17" s="35"/>
+    </row>
+    <row r="18" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AG18" s="35"/>
+      <c r="AH18"/>
+      <c r="AI18" s="35"/>
+      <c r="AK18" s="35"/>
+      <c r="AM18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AV18" s="35"/>
+      <c r="AW18"/>
+      <c r="AX18" s="35"/>
+      <c r="AZ18" s="35"/>
+      <c r="BB18" s="35"/>
+      <c r="BD18" s="35"/>
+      <c r="BE18" s="20"/>
+      <c r="BK18" s="35"/>
+      <c r="BL18"/>
+      <c r="BM18" s="35"/>
+      <c r="BO18" s="35"/>
+      <c r="BQ18" s="35"/>
+      <c r="BS18" s="35"/>
+      <c r="BY18"/>
+      <c r="BZ18" s="35"/>
+      <c r="CB18" s="35"/>
+      <c r="CD18" s="35"/>
+      <c r="CF18" s="35"/>
+      <c r="CH18" s="38"/>
       <c r="CI18" s="35"/>
-    </row>
-    <row r="19" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19"/>
-      <c r="AH19" s="35"/>
-      <c r="AJ19" s="35"/>
-      <c r="AL19" s="35"/>
-      <c r="AN19" s="35"/>
-      <c r="AU19" s="35"/>
-      <c r="AV19"/>
-      <c r="AW19" s="35"/>
-      <c r="AY19" s="35"/>
-      <c r="BA19" s="35"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="20"/>
-      <c r="BJ19" s="35"/>
-      <c r="BK19"/>
-      <c r="BL19" s="35"/>
-      <c r="BN19" s="35"/>
-      <c r="BP19" s="35"/>
-      <c r="BR19" s="35"/>
-      <c r="BX19"/>
-      <c r="BY19" s="35"/>
-      <c r="CA19" s="35"/>
-      <c r="CC19" s="35"/>
-      <c r="CE19" s="35"/>
-      <c r="CG19" s="38"/>
-      <c r="CH19" s="35"/>
+      <c r="CJ18" s="35"/>
+    </row>
+    <row r="19" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19"/>
+      <c r="AI19" s="35"/>
+      <c r="AK19" s="35"/>
+      <c r="AM19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AV19" s="35"/>
+      <c r="AW19"/>
+      <c r="AX19" s="35"/>
+      <c r="AZ19" s="35"/>
+      <c r="BB19" s="35"/>
+      <c r="BD19" s="35"/>
+      <c r="BE19" s="20"/>
+      <c r="BK19" s="35"/>
+      <c r="BL19"/>
+      <c r="BM19" s="35"/>
+      <c r="BO19" s="35"/>
+      <c r="BQ19" s="35"/>
+      <c r="BS19" s="35"/>
+      <c r="BY19"/>
+      <c r="BZ19" s="35"/>
+      <c r="CB19" s="35"/>
+      <c r="CD19" s="35"/>
+      <c r="CF19" s="35"/>
+      <c r="CH19" s="38"/>
       <c r="CI19" s="35"/>
-    </row>
-    <row r="20" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="U20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="AF20" s="35"/>
-      <c r="AG20"/>
-      <c r="AH20" s="35"/>
-      <c r="AJ20" s="35"/>
-      <c r="AL20" s="35"/>
-      <c r="AN20" s="35"/>
-      <c r="AU20" s="35"/>
-      <c r="AV20"/>
-      <c r="AW20" s="35"/>
-      <c r="AY20" s="35"/>
-      <c r="BA20" s="35"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="20"/>
-      <c r="BJ20" s="35"/>
-      <c r="BK20"/>
-      <c r="BL20" s="35"/>
-      <c r="BN20" s="35"/>
-      <c r="BP20" s="35"/>
-      <c r="BR20" s="35"/>
-      <c r="BX20"/>
-      <c r="BY20" s="35"/>
-      <c r="CA20" s="35"/>
-      <c r="CC20" s="35"/>
-      <c r="CE20" s="35"/>
-      <c r="CG20" s="38"/>
-      <c r="CH20" s="35"/>
+      <c r="CJ19" s="35"/>
+    </row>
+    <row r="20" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AG20" s="35"/>
+      <c r="AH20"/>
+      <c r="AI20" s="35"/>
+      <c r="AK20" s="35"/>
+      <c r="AM20" s="35"/>
+      <c r="AO20" s="35"/>
+      <c r="AV20" s="35"/>
+      <c r="AW20"/>
+      <c r="AX20" s="35"/>
+      <c r="AZ20" s="35"/>
+      <c r="BB20" s="35"/>
+      <c r="BD20" s="35"/>
+      <c r="BE20" s="20"/>
+      <c r="BK20" s="35"/>
+      <c r="BL20"/>
+      <c r="BM20" s="35"/>
+      <c r="BO20" s="35"/>
+      <c r="BQ20" s="35"/>
+      <c r="BS20" s="35"/>
+      <c r="BY20"/>
+      <c r="BZ20" s="35"/>
+      <c r="CB20" s="35"/>
+      <c r="CD20" s="35"/>
+      <c r="CF20" s="35"/>
+      <c r="CH20" s="38"/>
       <c r="CI20" s="35"/>
-    </row>
-    <row r="21" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="AF21" s="35"/>
-      <c r="AG21"/>
-      <c r="AH21" s="35"/>
-      <c r="AJ21" s="35"/>
-      <c r="AL21" s="35"/>
-      <c r="AN21" s="35"/>
-      <c r="AU21" s="35"/>
-      <c r="AV21"/>
-      <c r="AW21" s="35"/>
-      <c r="AY21" s="35"/>
-      <c r="BA21" s="35"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="20"/>
-      <c r="BJ21" s="35"/>
-      <c r="BK21"/>
-      <c r="BL21" s="35"/>
-      <c r="BN21" s="35"/>
-      <c r="BP21" s="35"/>
-      <c r="BR21" s="35"/>
-      <c r="BX21"/>
-      <c r="BY21" s="35"/>
-      <c r="CA21" s="35"/>
-      <c r="CC21" s="35"/>
-      <c r="CE21" s="35"/>
-      <c r="CG21" s="38"/>
-      <c r="CH21" s="35"/>
+      <c r="CJ20" s="35"/>
+    </row>
+    <row r="21" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21"/>
+      <c r="AI21" s="35"/>
+      <c r="AK21" s="35"/>
+      <c r="AM21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21"/>
+      <c r="AX21" s="35"/>
+      <c r="AZ21" s="35"/>
+      <c r="BB21" s="35"/>
+      <c r="BD21" s="35"/>
+      <c r="BE21" s="20"/>
+      <c r="BK21" s="35"/>
+      <c r="BL21"/>
+      <c r="BM21" s="35"/>
+      <c r="BO21" s="35"/>
+      <c r="BQ21" s="35"/>
+      <c r="BS21" s="35"/>
+      <c r="BY21"/>
+      <c r="BZ21" s="35"/>
+      <c r="CB21" s="35"/>
+      <c r="CD21" s="35"/>
+      <c r="CF21" s="35"/>
+      <c r="CH21" s="38"/>
       <c r="CI21" s="35"/>
-    </row>
-    <row r="22" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22"/>
-      <c r="AH22" s="35"/>
-      <c r="AJ22" s="35"/>
-      <c r="AL22" s="35"/>
-      <c r="AN22" s="35"/>
-      <c r="AU22" s="35"/>
-      <c r="AV22"/>
-      <c r="AW22" s="35"/>
-      <c r="AY22" s="35"/>
-      <c r="BA22" s="35"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="20"/>
-      <c r="BJ22" s="35"/>
-      <c r="BK22"/>
-      <c r="BL22" s="35"/>
-      <c r="BN22" s="35"/>
-      <c r="BP22" s="35"/>
-      <c r="BR22" s="35"/>
-      <c r="BX22"/>
-      <c r="BY22" s="35"/>
-      <c r="CA22" s="35"/>
-      <c r="CC22" s="35"/>
-      <c r="CE22" s="35"/>
-      <c r="CG22" s="38"/>
-      <c r="CH22" s="35"/>
+      <c r="CJ21" s="35"/>
+    </row>
+    <row r="22" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22"/>
+      <c r="AI22" s="35"/>
+      <c r="AK22" s="35"/>
+      <c r="AM22" s="35"/>
+      <c r="AO22" s="35"/>
+      <c r="AV22" s="35"/>
+      <c r="AW22"/>
+      <c r="AX22" s="35"/>
+      <c r="AZ22" s="35"/>
+      <c r="BB22" s="35"/>
+      <c r="BD22" s="35"/>
+      <c r="BE22" s="20"/>
+      <c r="BK22" s="35"/>
+      <c r="BL22"/>
+      <c r="BM22" s="35"/>
+      <c r="BO22" s="35"/>
+      <c r="BQ22" s="35"/>
+      <c r="BS22" s="35"/>
+      <c r="BY22"/>
+      <c r="BZ22" s="35"/>
+      <c r="CB22" s="35"/>
+      <c r="CD22" s="35"/>
+      <c r="CF22" s="35"/>
+      <c r="CH22" s="38"/>
       <c r="CI22" s="35"/>
-    </row>
-    <row r="23" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="U23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="AF23" s="35"/>
-      <c r="AG23"/>
-      <c r="AH23" s="35"/>
-      <c r="AJ23" s="35"/>
-      <c r="AL23" s="35"/>
-      <c r="AN23" s="35"/>
-      <c r="AU23" s="35"/>
-      <c r="AV23"/>
-      <c r="AW23" s="35"/>
-      <c r="AY23" s="35"/>
-      <c r="BA23" s="35"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="20"/>
-      <c r="BJ23" s="35"/>
-      <c r="BK23"/>
-      <c r="BL23" s="35"/>
-      <c r="BN23" s="35"/>
-      <c r="BP23" s="35"/>
-      <c r="BR23" s="35"/>
-      <c r="BX23"/>
-      <c r="BY23" s="35"/>
-      <c r="CA23" s="35"/>
-      <c r="CC23" s="35"/>
-      <c r="CE23" s="35"/>
-      <c r="CG23" s="38"/>
-      <c r="CH23" s="35"/>
+      <c r="CJ22" s="35"/>
+    </row>
+    <row r="23" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AG23" s="35"/>
+      <c r="AH23"/>
+      <c r="AI23" s="35"/>
+      <c r="AK23" s="35"/>
+      <c r="AM23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AV23" s="35"/>
+      <c r="AW23"/>
+      <c r="AX23" s="35"/>
+      <c r="AZ23" s="35"/>
+      <c r="BB23" s="35"/>
+      <c r="BD23" s="35"/>
+      <c r="BE23" s="20"/>
+      <c r="BK23" s="35"/>
+      <c r="BL23"/>
+      <c r="BM23" s="35"/>
+      <c r="BO23" s="35"/>
+      <c r="BQ23" s="35"/>
+      <c r="BS23" s="35"/>
+      <c r="BY23"/>
+      <c r="BZ23" s="35"/>
+      <c r="CB23" s="35"/>
+      <c r="CD23" s="35"/>
+      <c r="CF23" s="35"/>
+      <c r="CH23" s="38"/>
       <c r="CI23" s="35"/>
-    </row>
-    <row r="24" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="AF24" s="35"/>
-      <c r="AG24"/>
-      <c r="AH24" s="35"/>
-      <c r="AJ24" s="35"/>
-      <c r="AL24" s="35"/>
-      <c r="AN24" s="35"/>
-      <c r="AU24" s="35"/>
-      <c r="AV24"/>
-      <c r="AW24" s="35"/>
-      <c r="AY24" s="35"/>
-      <c r="BA24" s="35"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="20"/>
-      <c r="BJ24" s="35"/>
-      <c r="BK24"/>
-      <c r="BL24" s="35"/>
-      <c r="BN24" s="35"/>
-      <c r="BP24" s="35"/>
-      <c r="BR24" s="35"/>
-      <c r="BX24"/>
-      <c r="BY24" s="35"/>
-      <c r="CA24" s="35"/>
-      <c r="CC24" s="35"/>
-      <c r="CE24" s="35"/>
-      <c r="CG24" s="38"/>
-      <c r="CH24" s="35"/>
+      <c r="CJ23" s="35"/>
+    </row>
+    <row r="24" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AG24" s="35"/>
+      <c r="AH24"/>
+      <c r="AI24" s="35"/>
+      <c r="AK24" s="35"/>
+      <c r="AM24" s="35"/>
+      <c r="AO24" s="35"/>
+      <c r="AV24" s="35"/>
+      <c r="AW24"/>
+      <c r="AX24" s="35"/>
+      <c r="AZ24" s="35"/>
+      <c r="BB24" s="35"/>
+      <c r="BD24" s="35"/>
+      <c r="BE24" s="20"/>
+      <c r="BK24" s="35"/>
+      <c r="BL24"/>
+      <c r="BM24" s="35"/>
+      <c r="BO24" s="35"/>
+      <c r="BQ24" s="35"/>
+      <c r="BS24" s="35"/>
+      <c r="BY24"/>
+      <c r="BZ24" s="35"/>
+      <c r="CB24" s="35"/>
+      <c r="CD24" s="35"/>
+      <c r="CF24" s="35"/>
+      <c r="CH24" s="38"/>
       <c r="CI24" s="35"/>
-    </row>
-    <row r="25" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25"/>
-      <c r="AH25" s="35"/>
-      <c r="AJ25" s="35"/>
-      <c r="AL25" s="35"/>
-      <c r="AN25" s="35"/>
-      <c r="AU25" s="35"/>
-      <c r="AV25"/>
-      <c r="AW25" s="35"/>
-      <c r="AY25" s="35"/>
-      <c r="BA25" s="35"/>
-      <c r="BC25" s="35"/>
-      <c r="BD25" s="20"/>
-      <c r="BJ25" s="35"/>
-      <c r="BK25"/>
-      <c r="BL25" s="35"/>
-      <c r="BN25" s="35"/>
-      <c r="BP25" s="35"/>
-      <c r="BR25" s="35"/>
-      <c r="BX25"/>
-      <c r="BY25" s="35"/>
-      <c r="CA25" s="35"/>
-      <c r="CC25" s="35"/>
-      <c r="CE25" s="35"/>
-      <c r="CG25" s="38"/>
-      <c r="CH25" s="35"/>
+      <c r="CJ24" s="35"/>
+    </row>
+    <row r="25" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AG25" s="35"/>
+      <c r="AH25"/>
+      <c r="AI25" s="35"/>
+      <c r="AK25" s="35"/>
+      <c r="AM25" s="35"/>
+      <c r="AO25" s="35"/>
+      <c r="AV25" s="35"/>
+      <c r="AW25"/>
+      <c r="AX25" s="35"/>
+      <c r="AZ25" s="35"/>
+      <c r="BB25" s="35"/>
+      <c r="BD25" s="35"/>
+      <c r="BE25" s="20"/>
+      <c r="BK25" s="35"/>
+      <c r="BL25"/>
+      <c r="BM25" s="35"/>
+      <c r="BO25" s="35"/>
+      <c r="BQ25" s="35"/>
+      <c r="BS25" s="35"/>
+      <c r="BY25"/>
+      <c r="BZ25" s="35"/>
+      <c r="CB25" s="35"/>
+      <c r="CD25" s="35"/>
+      <c r="CF25" s="35"/>
+      <c r="CH25" s="38"/>
       <c r="CI25" s="35"/>
-    </row>
-    <row r="26" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="AF26" s="35"/>
-      <c r="AG26"/>
-      <c r="AH26" s="35"/>
-      <c r="AJ26" s="35"/>
-      <c r="AL26" s="35"/>
-      <c r="AN26" s="35"/>
-      <c r="AU26" s="35"/>
-      <c r="AV26"/>
-      <c r="AW26" s="35"/>
-      <c r="AY26" s="35"/>
-      <c r="BA26" s="35"/>
-      <c r="BC26" s="35"/>
-      <c r="BD26" s="20"/>
-      <c r="BJ26" s="35"/>
-      <c r="BK26"/>
-      <c r="BL26" s="35"/>
-      <c r="BN26" s="35"/>
-      <c r="BP26" s="35"/>
-      <c r="BR26" s="35"/>
-      <c r="BX26"/>
-      <c r="BY26" s="35"/>
-      <c r="CA26" s="35"/>
-      <c r="CC26" s="35"/>
-      <c r="CE26" s="35"/>
-      <c r="CG26" s="38"/>
-      <c r="CH26" s="35"/>
+      <c r="CJ25" s="35"/>
+    </row>
+    <row r="26" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26"/>
+      <c r="AI26" s="35"/>
+      <c r="AK26" s="35"/>
+      <c r="AM26" s="35"/>
+      <c r="AO26" s="35"/>
+      <c r="AV26" s="35"/>
+      <c r="AW26"/>
+      <c r="AX26" s="35"/>
+      <c r="AZ26" s="35"/>
+      <c r="BB26" s="35"/>
+      <c r="BD26" s="35"/>
+      <c r="BE26" s="20"/>
+      <c r="BK26" s="35"/>
+      <c r="BL26"/>
+      <c r="BM26" s="35"/>
+      <c r="BO26" s="35"/>
+      <c r="BQ26" s="35"/>
+      <c r="BS26" s="35"/>
+      <c r="BY26"/>
+      <c r="BZ26" s="35"/>
+      <c r="CB26" s="35"/>
+      <c r="CD26" s="35"/>
+      <c r="CF26" s="35"/>
+      <c r="CH26" s="38"/>
       <c r="CI26" s="35"/>
-    </row>
-    <row r="27" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="AF27" s="35"/>
-      <c r="AG27"/>
-      <c r="AH27" s="35"/>
-      <c r="AJ27" s="35"/>
-      <c r="AL27" s="35"/>
-      <c r="AN27" s="35"/>
-      <c r="AU27" s="35"/>
-      <c r="AV27"/>
-      <c r="AW27" s="35"/>
-      <c r="AY27" s="35"/>
-      <c r="BA27" s="35"/>
-      <c r="BC27" s="35"/>
-      <c r="BD27" s="20"/>
-      <c r="BJ27" s="35"/>
-      <c r="BK27"/>
-      <c r="BL27" s="35"/>
-      <c r="BN27" s="35"/>
-      <c r="BP27" s="35"/>
-      <c r="BR27" s="35"/>
-      <c r="BX27"/>
-      <c r="BY27" s="35"/>
-      <c r="CA27" s="35"/>
-      <c r="CC27" s="35"/>
-      <c r="CE27" s="35"/>
-      <c r="CG27" s="38"/>
-      <c r="CH27" s="35"/>
+      <c r="CJ26" s="35"/>
+    </row>
+    <row r="27" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AG27" s="35"/>
+      <c r="AH27"/>
+      <c r="AI27" s="35"/>
+      <c r="AK27" s="35"/>
+      <c r="AM27" s="35"/>
+      <c r="AO27" s="35"/>
+      <c r="AV27" s="35"/>
+      <c r="AW27"/>
+      <c r="AX27" s="35"/>
+      <c r="AZ27" s="35"/>
+      <c r="BB27" s="35"/>
+      <c r="BD27" s="35"/>
+      <c r="BE27" s="20"/>
+      <c r="BK27" s="35"/>
+      <c r="BL27"/>
+      <c r="BM27" s="35"/>
+      <c r="BO27" s="35"/>
+      <c r="BQ27" s="35"/>
+      <c r="BS27" s="35"/>
+      <c r="BY27"/>
+      <c r="BZ27" s="35"/>
+      <c r="CB27" s="35"/>
+      <c r="CD27" s="35"/>
+      <c r="CF27" s="35"/>
+      <c r="CH27" s="38"/>
       <c r="CI27" s="35"/>
-    </row>
-    <row r="28" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28"/>
-      <c r="AH28" s="35"/>
-      <c r="AJ28" s="35"/>
-      <c r="AL28" s="35"/>
-      <c r="AN28" s="35"/>
-      <c r="AU28" s="35"/>
-      <c r="AV28"/>
-      <c r="AW28" s="35"/>
-      <c r="AY28" s="35"/>
-      <c r="BA28" s="35"/>
-      <c r="BC28" s="35"/>
-      <c r="BD28" s="20"/>
-      <c r="BJ28" s="35"/>
-      <c r="BK28"/>
-      <c r="BL28" s="35"/>
-      <c r="BN28" s="35"/>
-      <c r="BP28" s="35"/>
-      <c r="BR28" s="35"/>
-      <c r="BX28"/>
-      <c r="BY28" s="35"/>
-      <c r="CA28" s="35"/>
-      <c r="CC28" s="35"/>
-      <c r="CE28" s="35"/>
-      <c r="CG28" s="38"/>
-      <c r="CH28" s="35"/>
+      <c r="CJ27" s="35"/>
+    </row>
+    <row r="28" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AG28" s="35"/>
+      <c r="AH28"/>
+      <c r="AI28" s="35"/>
+      <c r="AK28" s="35"/>
+      <c r="AM28" s="35"/>
+      <c r="AO28" s="35"/>
+      <c r="AV28" s="35"/>
+      <c r="AW28"/>
+      <c r="AX28" s="35"/>
+      <c r="AZ28" s="35"/>
+      <c r="BB28" s="35"/>
+      <c r="BD28" s="35"/>
+      <c r="BE28" s="20"/>
+      <c r="BK28" s="35"/>
+      <c r="BL28"/>
+      <c r="BM28" s="35"/>
+      <c r="BO28" s="35"/>
+      <c r="BQ28" s="35"/>
+      <c r="BS28" s="35"/>
+      <c r="BY28"/>
+      <c r="BZ28" s="35"/>
+      <c r="CB28" s="35"/>
+      <c r="CD28" s="35"/>
+      <c r="CF28" s="35"/>
+      <c r="CH28" s="38"/>
       <c r="CI28" s="35"/>
-    </row>
-    <row r="29" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="U29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="AF29" s="35"/>
-      <c r="AG29"/>
-      <c r="AH29" s="35"/>
-      <c r="AJ29" s="35"/>
-      <c r="AL29" s="35"/>
-      <c r="AN29" s="35"/>
-      <c r="AU29" s="35"/>
-      <c r="AV29"/>
-      <c r="AW29" s="35"/>
-      <c r="AY29" s="35"/>
-      <c r="BA29" s="35"/>
-      <c r="BC29" s="35"/>
-      <c r="BD29" s="20"/>
-      <c r="BJ29" s="35"/>
-      <c r="BK29"/>
-      <c r="BL29" s="35"/>
-      <c r="BN29" s="35"/>
-      <c r="BP29" s="35"/>
-      <c r="BR29" s="35"/>
-      <c r="BX29"/>
-      <c r="BY29" s="35"/>
-      <c r="CA29" s="35"/>
-      <c r="CC29" s="35"/>
-      <c r="CE29" s="35"/>
-      <c r="CG29" s="38"/>
-      <c r="CH29" s="35"/>
+      <c r="CJ28" s="35"/>
+    </row>
+    <row r="29" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AG29" s="35"/>
+      <c r="AH29"/>
+      <c r="AI29" s="35"/>
+      <c r="AK29" s="35"/>
+      <c r="AM29" s="35"/>
+      <c r="AO29" s="35"/>
+      <c r="AV29" s="35"/>
+      <c r="AW29"/>
+      <c r="AX29" s="35"/>
+      <c r="AZ29" s="35"/>
+      <c r="BB29" s="35"/>
+      <c r="BD29" s="35"/>
+      <c r="BE29" s="20"/>
+      <c r="BK29" s="35"/>
+      <c r="BL29"/>
+      <c r="BM29" s="35"/>
+      <c r="BO29" s="35"/>
+      <c r="BQ29" s="35"/>
+      <c r="BS29" s="35"/>
+      <c r="BY29"/>
+      <c r="BZ29" s="35"/>
+      <c r="CB29" s="35"/>
+      <c r="CD29" s="35"/>
+      <c r="CF29" s="35"/>
+      <c r="CH29" s="38"/>
       <c r="CI29" s="35"/>
-    </row>
-    <row r="30" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="AF30" s="35"/>
-      <c r="AG30"/>
-      <c r="AH30" s="35"/>
-      <c r="AJ30" s="35"/>
-      <c r="AL30" s="35"/>
-      <c r="AN30" s="35"/>
-      <c r="AU30" s="35"/>
-      <c r="AV30"/>
-      <c r="AW30" s="35"/>
-      <c r="AY30" s="35"/>
-      <c r="BA30" s="35"/>
-      <c r="BC30" s="35"/>
-      <c r="BD30" s="20"/>
-      <c r="BJ30" s="35"/>
-      <c r="BK30"/>
-      <c r="BL30" s="35"/>
-      <c r="BN30" s="35"/>
-      <c r="BP30" s="35"/>
-      <c r="BR30" s="35"/>
-      <c r="BX30"/>
-      <c r="BY30" s="35"/>
-      <c r="CA30" s="35"/>
-      <c r="CC30" s="35"/>
-      <c r="CE30" s="35"/>
-      <c r="CG30" s="38"/>
-      <c r="CH30" s="35"/>
+      <c r="CJ29" s="35"/>
+    </row>
+    <row r="30" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AG30" s="35"/>
+      <c r="AH30"/>
+      <c r="AI30" s="35"/>
+      <c r="AK30" s="35"/>
+      <c r="AM30" s="35"/>
+      <c r="AO30" s="35"/>
+      <c r="AV30" s="35"/>
+      <c r="AW30"/>
+      <c r="AX30" s="35"/>
+      <c r="AZ30" s="35"/>
+      <c r="BB30" s="35"/>
+      <c r="BD30" s="35"/>
+      <c r="BE30" s="20"/>
+      <c r="BK30" s="35"/>
+      <c r="BL30"/>
+      <c r="BM30" s="35"/>
+      <c r="BO30" s="35"/>
+      <c r="BQ30" s="35"/>
+      <c r="BS30" s="35"/>
+      <c r="BY30"/>
+      <c r="BZ30" s="35"/>
+      <c r="CB30" s="35"/>
+      <c r="CD30" s="35"/>
+      <c r="CF30" s="35"/>
+      <c r="CH30" s="38"/>
       <c r="CI30" s="35"/>
-    </row>
-    <row r="31" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="AF31" s="35"/>
-      <c r="AG31"/>
-      <c r="AH31" s="35"/>
-      <c r="AJ31" s="35"/>
-      <c r="AL31" s="35"/>
-      <c r="AN31" s="35"/>
-      <c r="AU31" s="35"/>
-      <c r="AV31"/>
-      <c r="AW31" s="35"/>
-      <c r="AY31" s="35"/>
-      <c r="BA31" s="35"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="20"/>
-      <c r="BJ31" s="35"/>
-      <c r="BK31"/>
-      <c r="BL31" s="35"/>
-      <c r="BN31" s="35"/>
-      <c r="BP31" s="35"/>
-      <c r="BR31" s="35"/>
-      <c r="BX31"/>
-      <c r="BY31" s="35"/>
-      <c r="CA31" s="35"/>
-      <c r="CC31" s="35"/>
-      <c r="CE31" s="35"/>
-      <c r="CG31" s="38"/>
-      <c r="CH31" s="35"/>
+      <c r="CJ30" s="35"/>
+    </row>
+    <row r="31" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AG31" s="35"/>
+      <c r="AH31"/>
+      <c r="AI31" s="35"/>
+      <c r="AK31" s="35"/>
+      <c r="AM31" s="35"/>
+      <c r="AO31" s="35"/>
+      <c r="AV31" s="35"/>
+      <c r="AW31"/>
+      <c r="AX31" s="35"/>
+      <c r="AZ31" s="35"/>
+      <c r="BB31" s="35"/>
+      <c r="BD31" s="35"/>
+      <c r="BE31" s="20"/>
+      <c r="BK31" s="35"/>
+      <c r="BL31"/>
+      <c r="BM31" s="35"/>
+      <c r="BO31" s="35"/>
+      <c r="BQ31" s="35"/>
+      <c r="BS31" s="35"/>
+      <c r="BY31"/>
+      <c r="BZ31" s="35"/>
+      <c r="CB31" s="35"/>
+      <c r="CD31" s="35"/>
+      <c r="CF31" s="35"/>
+      <c r="CH31" s="38"/>
       <c r="CI31" s="35"/>
-    </row>
-    <row r="32" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="U32" s="35"/>
-      <c r="W32" s="35"/>
-      <c r="Y32" s="35"/>
-      <c r="AF32" s="35"/>
-      <c r="AG32"/>
-      <c r="AH32" s="35"/>
-      <c r="AJ32" s="35"/>
-      <c r="AL32" s="35"/>
-      <c r="AN32" s="35"/>
-      <c r="AU32" s="35"/>
-      <c r="AV32"/>
-      <c r="AW32" s="35"/>
-      <c r="AY32" s="35"/>
-      <c r="BA32" s="35"/>
-      <c r="BC32" s="35"/>
-      <c r="BD32" s="20"/>
-      <c r="BJ32" s="35"/>
-      <c r="BK32"/>
-      <c r="BL32" s="35"/>
-      <c r="BN32" s="35"/>
-      <c r="BP32" s="35"/>
-      <c r="BR32" s="35"/>
-      <c r="BX32"/>
-      <c r="BY32" s="35"/>
-      <c r="CA32" s="35"/>
-      <c r="CC32" s="35"/>
-      <c r="CE32" s="35"/>
-      <c r="CG32" s="38"/>
-      <c r="CH32" s="35"/>
+      <c r="CJ31" s="35"/>
+    </row>
+    <row r="32" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="X32" s="35"/>
+      <c r="Z32" s="35"/>
+      <c r="AG32" s="35"/>
+      <c r="AH32"/>
+      <c r="AI32" s="35"/>
+      <c r="AK32" s="35"/>
+      <c r="AM32" s="35"/>
+      <c r="AO32" s="35"/>
+      <c r="AV32" s="35"/>
+      <c r="AW32"/>
+      <c r="AX32" s="35"/>
+      <c r="AZ32" s="35"/>
+      <c r="BB32" s="35"/>
+      <c r="BD32" s="35"/>
+      <c r="BE32" s="20"/>
+      <c r="BK32" s="35"/>
+      <c r="BL32"/>
+      <c r="BM32" s="35"/>
+      <c r="BO32" s="35"/>
+      <c r="BQ32" s="35"/>
+      <c r="BS32" s="35"/>
+      <c r="BY32"/>
+      <c r="BZ32" s="35"/>
+      <c r="CB32" s="35"/>
+      <c r="CD32" s="35"/>
+      <c r="CF32" s="35"/>
+      <c r="CH32" s="38"/>
       <c r="CI32" s="35"/>
-    </row>
-    <row r="33" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="U33" s="35"/>
-      <c r="W33" s="35"/>
-      <c r="Y33" s="35"/>
-      <c r="AF33" s="35"/>
-      <c r="AG33"/>
-      <c r="AH33" s="35"/>
-      <c r="AJ33" s="35"/>
-      <c r="AL33" s="35"/>
-      <c r="AN33" s="35"/>
-      <c r="AU33" s="35"/>
-      <c r="AV33"/>
-      <c r="AW33" s="35"/>
-      <c r="AY33" s="35"/>
-      <c r="BA33" s="35"/>
-      <c r="BC33" s="35"/>
-      <c r="BD33" s="20"/>
-      <c r="BJ33" s="35"/>
-      <c r="BK33"/>
-      <c r="BL33" s="35"/>
-      <c r="BN33" s="35"/>
-      <c r="BP33" s="35"/>
-      <c r="BR33" s="35"/>
-      <c r="BX33"/>
-      <c r="BY33" s="35"/>
-      <c r="CA33" s="35"/>
-      <c r="CC33" s="35"/>
-      <c r="CE33" s="35"/>
-      <c r="CG33" s="38"/>
-      <c r="CH33" s="35"/>
+      <c r="CJ32" s="35"/>
+    </row>
+    <row r="33" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="X33" s="35"/>
+      <c r="Z33" s="35"/>
+      <c r="AG33" s="35"/>
+      <c r="AH33"/>
+      <c r="AI33" s="35"/>
+      <c r="AK33" s="35"/>
+      <c r="AM33" s="35"/>
+      <c r="AO33" s="35"/>
+      <c r="AV33" s="35"/>
+      <c r="AW33"/>
+      <c r="AX33" s="35"/>
+      <c r="AZ33" s="35"/>
+      <c r="BB33" s="35"/>
+      <c r="BD33" s="35"/>
+      <c r="BE33" s="20"/>
+      <c r="BK33" s="35"/>
+      <c r="BL33"/>
+      <c r="BM33" s="35"/>
+      <c r="BO33" s="35"/>
+      <c r="BQ33" s="35"/>
+      <c r="BS33" s="35"/>
+      <c r="BY33"/>
+      <c r="BZ33" s="35"/>
+      <c r="CB33" s="35"/>
+      <c r="CD33" s="35"/>
+      <c r="CF33" s="35"/>
+      <c r="CH33" s="38"/>
       <c r="CI33" s="35"/>
-    </row>
-    <row r="34" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="W34" s="35"/>
-      <c r="Y34" s="35"/>
-      <c r="AF34" s="35"/>
-      <c r="AG34"/>
-      <c r="AH34" s="35"/>
-      <c r="AJ34" s="35"/>
-      <c r="AL34" s="35"/>
-      <c r="AN34" s="35"/>
-      <c r="AU34" s="35"/>
-      <c r="AV34"/>
-      <c r="AW34" s="35"/>
-      <c r="AY34" s="35"/>
-      <c r="BA34" s="35"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="20"/>
-      <c r="BJ34" s="35"/>
-      <c r="BK34"/>
-      <c r="BL34" s="35"/>
-      <c r="BN34" s="35"/>
-      <c r="BP34" s="35"/>
-      <c r="BR34" s="35"/>
-      <c r="BX34"/>
-      <c r="BY34" s="35"/>
-      <c r="CA34" s="35"/>
-      <c r="CC34" s="35"/>
-      <c r="CE34" s="35"/>
-      <c r="CG34" s="38"/>
-      <c r="CH34" s="35"/>
+      <c r="CJ33" s="35"/>
+    </row>
+    <row r="34" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="X34" s="35"/>
+      <c r="Z34" s="35"/>
+      <c r="AG34" s="35"/>
+      <c r="AH34"/>
+      <c r="AI34" s="35"/>
+      <c r="AK34" s="35"/>
+      <c r="AM34" s="35"/>
+      <c r="AO34" s="35"/>
+      <c r="AV34" s="35"/>
+      <c r="AW34"/>
+      <c r="AX34" s="35"/>
+      <c r="AZ34" s="35"/>
+      <c r="BB34" s="35"/>
+      <c r="BD34" s="35"/>
+      <c r="BE34" s="20"/>
+      <c r="BK34" s="35"/>
+      <c r="BL34"/>
+      <c r="BM34" s="35"/>
+      <c r="BO34" s="35"/>
+      <c r="BQ34" s="35"/>
+      <c r="BS34" s="35"/>
+      <c r="BY34"/>
+      <c r="BZ34" s="35"/>
+      <c r="CB34" s="35"/>
+      <c r="CD34" s="35"/>
+      <c r="CF34" s="35"/>
+      <c r="CH34" s="38"/>
       <c r="CI34" s="35"/>
-    </row>
-    <row r="35" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="U35" s="35"/>
-      <c r="W35" s="35"/>
-      <c r="Y35" s="35"/>
-      <c r="AF35" s="35"/>
-      <c r="AG35"/>
-      <c r="AH35" s="35"/>
-      <c r="AJ35" s="35"/>
-      <c r="AL35" s="35"/>
-      <c r="AN35" s="35"/>
-      <c r="AU35" s="35"/>
-      <c r="AV35"/>
-      <c r="AW35" s="35"/>
-      <c r="AY35" s="35"/>
-      <c r="BA35" s="35"/>
-      <c r="BC35" s="35"/>
-      <c r="BD35" s="20"/>
-      <c r="BJ35" s="35"/>
-      <c r="BK35"/>
-      <c r="BL35" s="35"/>
-      <c r="BN35" s="35"/>
-      <c r="BP35" s="35"/>
-      <c r="BR35" s="35"/>
-      <c r="BX35"/>
-      <c r="BY35" s="35"/>
-      <c r="CA35" s="35"/>
-      <c r="CC35" s="35"/>
-      <c r="CE35" s="35"/>
-      <c r="CG35" s="38"/>
-      <c r="CH35" s="35"/>
+      <c r="CJ34" s="35"/>
+    </row>
+    <row r="35" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AG35" s="35"/>
+      <c r="AH35"/>
+      <c r="AI35" s="35"/>
+      <c r="AK35" s="35"/>
+      <c r="AM35" s="35"/>
+      <c r="AO35" s="35"/>
+      <c r="AV35" s="35"/>
+      <c r="AW35"/>
+      <c r="AX35" s="35"/>
+      <c r="AZ35" s="35"/>
+      <c r="BB35" s="35"/>
+      <c r="BD35" s="35"/>
+      <c r="BE35" s="20"/>
+      <c r="BK35" s="35"/>
+      <c r="BL35"/>
+      <c r="BM35" s="35"/>
+      <c r="BO35" s="35"/>
+      <c r="BQ35" s="35"/>
+      <c r="BS35" s="35"/>
+      <c r="BY35"/>
+      <c r="BZ35" s="35"/>
+      <c r="CB35" s="35"/>
+      <c r="CD35" s="35"/>
+      <c r="CF35" s="35"/>
+      <c r="CH35" s="38"/>
       <c r="CI35" s="35"/>
-    </row>
-    <row r="36" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="AF36" s="35"/>
-      <c r="AG36"/>
-      <c r="AH36" s="35"/>
-      <c r="AJ36" s="35"/>
-      <c r="AL36" s="35"/>
-      <c r="AN36" s="35"/>
-      <c r="AU36" s="35"/>
-      <c r="AV36"/>
-      <c r="AW36" s="35"/>
-      <c r="AY36" s="35"/>
-      <c r="BA36" s="35"/>
-      <c r="BC36" s="35"/>
-      <c r="BD36" s="20"/>
-      <c r="BJ36" s="35"/>
-      <c r="BK36"/>
-      <c r="BL36" s="35"/>
-      <c r="BN36" s="35"/>
-      <c r="BP36" s="35"/>
-      <c r="BR36" s="35"/>
-      <c r="BX36"/>
-      <c r="BY36" s="35"/>
-      <c r="CA36" s="35"/>
-      <c r="CC36" s="35"/>
-      <c r="CE36" s="35"/>
-      <c r="CG36" s="38"/>
-      <c r="CH36" s="35"/>
+      <c r="CJ35" s="35"/>
+    </row>
+    <row r="36" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AG36" s="35"/>
+      <c r="AH36"/>
+      <c r="AI36" s="35"/>
+      <c r="AK36" s="35"/>
+      <c r="AM36" s="35"/>
+      <c r="AO36" s="35"/>
+      <c r="AV36" s="35"/>
+      <c r="AW36"/>
+      <c r="AX36" s="35"/>
+      <c r="AZ36" s="35"/>
+      <c r="BB36" s="35"/>
+      <c r="BD36" s="35"/>
+      <c r="BE36" s="20"/>
+      <c r="BK36" s="35"/>
+      <c r="BL36"/>
+      <c r="BM36" s="35"/>
+      <c r="BO36" s="35"/>
+      <c r="BQ36" s="35"/>
+      <c r="BS36" s="35"/>
+      <c r="BY36"/>
+      <c r="BZ36" s="35"/>
+      <c r="CB36" s="35"/>
+      <c r="CD36" s="35"/>
+      <c r="CF36" s="35"/>
+      <c r="CH36" s="38"/>
       <c r="CI36" s="35"/>
-    </row>
-    <row r="37" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q37" s="35"/>
-      <c r="S37" s="35"/>
-      <c r="U37" s="35"/>
-      <c r="W37" s="35"/>
-      <c r="Y37" s="35"/>
-      <c r="AF37" s="35"/>
-      <c r="AG37"/>
-      <c r="AH37" s="35"/>
-      <c r="AJ37" s="35"/>
-      <c r="AL37" s="35"/>
-      <c r="AN37" s="35"/>
-      <c r="AU37" s="35"/>
-      <c r="AV37"/>
-      <c r="AW37" s="35"/>
-      <c r="AY37" s="35"/>
-      <c r="BA37" s="35"/>
-      <c r="BC37" s="35"/>
-      <c r="BD37" s="20"/>
-      <c r="BJ37" s="35"/>
-      <c r="BK37"/>
-      <c r="BL37" s="35"/>
-      <c r="BN37" s="35"/>
-      <c r="BP37" s="35"/>
-      <c r="BR37" s="35"/>
-      <c r="BX37"/>
-      <c r="BY37" s="35"/>
-      <c r="CA37" s="35"/>
-      <c r="CC37" s="35"/>
-      <c r="CE37" s="35"/>
-      <c r="CG37" s="38"/>
-      <c r="CH37" s="35"/>
+      <c r="CJ36" s="35"/>
+    </row>
+    <row r="37" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="X37" s="35"/>
+      <c r="Z37" s="35"/>
+      <c r="AG37" s="35"/>
+      <c r="AH37"/>
+      <c r="AI37" s="35"/>
+      <c r="AK37" s="35"/>
+      <c r="AM37" s="35"/>
+      <c r="AO37" s="35"/>
+      <c r="AV37" s="35"/>
+      <c r="AW37"/>
+      <c r="AX37" s="35"/>
+      <c r="AZ37" s="35"/>
+      <c r="BB37" s="35"/>
+      <c r="BD37" s="35"/>
+      <c r="BE37" s="20"/>
+      <c r="BK37" s="35"/>
+      <c r="BL37"/>
+      <c r="BM37" s="35"/>
+      <c r="BO37" s="35"/>
+      <c r="BQ37" s="35"/>
+      <c r="BS37" s="35"/>
+      <c r="BY37"/>
+      <c r="BZ37" s="35"/>
+      <c r="CB37" s="35"/>
+      <c r="CD37" s="35"/>
+      <c r="CF37" s="35"/>
+      <c r="CH37" s="38"/>
       <c r="CI37" s="35"/>
-    </row>
-    <row r="38" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="U38" s="35"/>
-      <c r="W38" s="35"/>
-      <c r="Y38" s="35"/>
-      <c r="AF38" s="35"/>
-      <c r="AG38"/>
-      <c r="AH38" s="35"/>
-      <c r="AJ38" s="35"/>
-      <c r="AL38" s="35"/>
-      <c r="AN38" s="35"/>
-      <c r="AU38" s="35"/>
-      <c r="AV38"/>
-      <c r="AW38" s="35"/>
-      <c r="AY38" s="35"/>
-      <c r="BA38" s="35"/>
-      <c r="BC38" s="35"/>
-      <c r="BD38" s="20"/>
-      <c r="BJ38" s="35"/>
-      <c r="BK38"/>
-      <c r="BL38" s="35"/>
-      <c r="BN38" s="35"/>
-      <c r="BP38" s="35"/>
-      <c r="BR38" s="35"/>
-      <c r="BX38"/>
-      <c r="BY38" s="35"/>
-      <c r="CA38" s="35"/>
-      <c r="CC38" s="35"/>
-      <c r="CE38" s="35"/>
-      <c r="CG38" s="38"/>
-      <c r="CH38" s="35"/>
+      <c r="CJ37" s="35"/>
+    </row>
+    <row r="38" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AG38" s="35"/>
+      <c r="AH38"/>
+      <c r="AI38" s="35"/>
+      <c r="AK38" s="35"/>
+      <c r="AM38" s="35"/>
+      <c r="AO38" s="35"/>
+      <c r="AV38" s="35"/>
+      <c r="AW38"/>
+      <c r="AX38" s="35"/>
+      <c r="AZ38" s="35"/>
+      <c r="BB38" s="35"/>
+      <c r="BD38" s="35"/>
+      <c r="BE38" s="20"/>
+      <c r="BK38" s="35"/>
+      <c r="BL38"/>
+      <c r="BM38" s="35"/>
+      <c r="BO38" s="35"/>
+      <c r="BQ38" s="35"/>
+      <c r="BS38" s="35"/>
+      <c r="BY38"/>
+      <c r="BZ38" s="35"/>
+      <c r="CB38" s="35"/>
+      <c r="CD38" s="35"/>
+      <c r="CF38" s="35"/>
+      <c r="CH38" s="38"/>
       <c r="CI38" s="35"/>
-    </row>
-    <row r="39" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="U39" s="35"/>
-      <c r="W39" s="35"/>
-      <c r="Y39" s="35"/>
-      <c r="AF39" s="35"/>
-      <c r="AG39"/>
-      <c r="AH39" s="35"/>
-      <c r="AJ39" s="35"/>
-      <c r="AL39" s="35"/>
-      <c r="AN39" s="35"/>
-      <c r="AU39" s="35"/>
-      <c r="AV39"/>
-      <c r="AW39" s="35"/>
-      <c r="AY39" s="35"/>
-      <c r="BA39" s="35"/>
-      <c r="BC39" s="35"/>
-      <c r="BD39" s="20"/>
-      <c r="BJ39" s="35"/>
-      <c r="BK39"/>
-      <c r="BL39" s="35"/>
-      <c r="BN39" s="35"/>
-      <c r="BP39" s="35"/>
-      <c r="BR39" s="35"/>
-      <c r="BX39"/>
-      <c r="BY39" s="35"/>
-      <c r="CA39" s="35"/>
-      <c r="CC39" s="35"/>
-      <c r="CE39" s="35"/>
-      <c r="CG39" s="38"/>
-      <c r="CH39" s="35"/>
+      <c r="CJ38" s="35"/>
+    </row>
+    <row r="39" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AG39" s="35"/>
+      <c r="AH39"/>
+      <c r="AI39" s="35"/>
+      <c r="AK39" s="35"/>
+      <c r="AM39" s="35"/>
+      <c r="AO39" s="35"/>
+      <c r="AV39" s="35"/>
+      <c r="AW39"/>
+      <c r="AX39" s="35"/>
+      <c r="AZ39" s="35"/>
+      <c r="BB39" s="35"/>
+      <c r="BD39" s="35"/>
+      <c r="BE39" s="20"/>
+      <c r="BK39" s="35"/>
+      <c r="BL39"/>
+      <c r="BM39" s="35"/>
+      <c r="BO39" s="35"/>
+      <c r="BQ39" s="35"/>
+      <c r="BS39" s="35"/>
+      <c r="BY39"/>
+      <c r="BZ39" s="35"/>
+      <c r="CB39" s="35"/>
+      <c r="CD39" s="35"/>
+      <c r="CF39" s="35"/>
+      <c r="CH39" s="38"/>
       <c r="CI39" s="35"/>
-    </row>
-    <row r="40" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="U40" s="35"/>
-      <c r="W40" s="35"/>
-      <c r="Y40" s="35"/>
-      <c r="AF40" s="35"/>
-      <c r="AG40"/>
-      <c r="AH40" s="35"/>
-      <c r="AJ40" s="35"/>
-      <c r="AL40" s="35"/>
-      <c r="AN40" s="35"/>
-      <c r="AU40" s="35"/>
-      <c r="AV40"/>
-      <c r="AW40" s="35"/>
-      <c r="AY40" s="35"/>
-      <c r="BA40" s="35"/>
-      <c r="BC40" s="35"/>
-      <c r="BD40" s="20"/>
-      <c r="BJ40" s="35"/>
-      <c r="BK40"/>
-      <c r="BL40" s="35"/>
-      <c r="BN40" s="35"/>
-      <c r="BP40" s="35"/>
-      <c r="BR40" s="35"/>
-      <c r="BX40"/>
-      <c r="BY40" s="35"/>
-      <c r="CA40" s="35"/>
-      <c r="CC40" s="35"/>
-      <c r="CE40" s="35"/>
-      <c r="CG40" s="38"/>
-      <c r="CH40" s="35"/>
+      <c r="CJ39" s="35"/>
+    </row>
+    <row r="40" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="V40" s="35"/>
+      <c r="X40" s="35"/>
+      <c r="Z40" s="35"/>
+      <c r="AG40" s="35"/>
+      <c r="AH40"/>
+      <c r="AI40" s="35"/>
+      <c r="AK40" s="35"/>
+      <c r="AM40" s="35"/>
+      <c r="AO40" s="35"/>
+      <c r="AV40" s="35"/>
+      <c r="AW40"/>
+      <c r="AX40" s="35"/>
+      <c r="AZ40" s="35"/>
+      <c r="BB40" s="35"/>
+      <c r="BD40" s="35"/>
+      <c r="BE40" s="20"/>
+      <c r="BK40" s="35"/>
+      <c r="BL40"/>
+      <c r="BM40" s="35"/>
+      <c r="BO40" s="35"/>
+      <c r="BQ40" s="35"/>
+      <c r="BS40" s="35"/>
+      <c r="BY40"/>
+      <c r="BZ40" s="35"/>
+      <c r="CB40" s="35"/>
+      <c r="CD40" s="35"/>
+      <c r="CF40" s="35"/>
+      <c r="CH40" s="38"/>
       <c r="CI40" s="35"/>
-    </row>
-    <row r="41" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="U41" s="35"/>
-      <c r="W41" s="35"/>
-      <c r="Y41" s="35"/>
-      <c r="AF41" s="35"/>
-      <c r="AG41"/>
-      <c r="AH41" s="35"/>
-      <c r="AJ41" s="35"/>
-      <c r="AL41" s="35"/>
-      <c r="AN41" s="35"/>
-      <c r="AU41" s="35"/>
-      <c r="AV41"/>
-      <c r="AW41" s="35"/>
-      <c r="AY41" s="35"/>
-      <c r="BA41" s="35"/>
-      <c r="BC41" s="35"/>
-      <c r="BD41" s="20"/>
-      <c r="BJ41" s="35"/>
-      <c r="BK41"/>
-      <c r="BL41" s="35"/>
-      <c r="BN41" s="35"/>
-      <c r="BP41" s="35"/>
-      <c r="BR41" s="35"/>
-      <c r="BX41"/>
-      <c r="BY41" s="35"/>
-      <c r="CA41" s="35"/>
-      <c r="CC41" s="35"/>
-      <c r="CE41" s="35"/>
-      <c r="CG41" s="38"/>
-      <c r="CH41" s="35"/>
+      <c r="CJ40" s="35"/>
+    </row>
+    <row r="41" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="V41" s="35"/>
+      <c r="X41" s="35"/>
+      <c r="Z41" s="35"/>
+      <c r="AG41" s="35"/>
+      <c r="AH41"/>
+      <c r="AI41" s="35"/>
+      <c r="AK41" s="35"/>
+      <c r="AM41" s="35"/>
+      <c r="AO41" s="35"/>
+      <c r="AV41" s="35"/>
+      <c r="AW41"/>
+      <c r="AX41" s="35"/>
+      <c r="AZ41" s="35"/>
+      <c r="BB41" s="35"/>
+      <c r="BD41" s="35"/>
+      <c r="BE41" s="20"/>
+      <c r="BK41" s="35"/>
+      <c r="BL41"/>
+      <c r="BM41" s="35"/>
+      <c r="BO41" s="35"/>
+      <c r="BQ41" s="35"/>
+      <c r="BS41" s="35"/>
+      <c r="BY41"/>
+      <c r="BZ41" s="35"/>
+      <c r="CB41" s="35"/>
+      <c r="CD41" s="35"/>
+      <c r="CF41" s="35"/>
+      <c r="CH41" s="38"/>
       <c r="CI41" s="35"/>
-    </row>
-    <row r="42" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="U42" s="35"/>
-      <c r="W42" s="35"/>
-      <c r="Y42" s="35"/>
-      <c r="AF42" s="35"/>
-      <c r="AG42"/>
-      <c r="AH42" s="35"/>
-      <c r="AJ42" s="35"/>
-      <c r="AL42" s="35"/>
-      <c r="AN42" s="35"/>
-      <c r="AU42" s="35"/>
-      <c r="AV42"/>
-      <c r="AW42" s="35"/>
-      <c r="AY42" s="35"/>
-      <c r="BA42" s="35"/>
-      <c r="BC42" s="35"/>
-      <c r="BD42" s="20"/>
-      <c r="BJ42" s="35"/>
-      <c r="BK42"/>
-      <c r="BL42" s="35"/>
-      <c r="BN42" s="35"/>
-      <c r="BP42" s="35"/>
-      <c r="BR42" s="35"/>
-      <c r="BX42"/>
-      <c r="BY42" s="35"/>
-      <c r="CA42" s="35"/>
-      <c r="CC42" s="35"/>
-      <c r="CE42" s="35"/>
-      <c r="CG42" s="38"/>
-      <c r="CH42" s="35"/>
+      <c r="CJ41" s="35"/>
+    </row>
+    <row r="42" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="X42" s="35"/>
+      <c r="Z42" s="35"/>
+      <c r="AG42" s="35"/>
+      <c r="AH42"/>
+      <c r="AI42" s="35"/>
+      <c r="AK42" s="35"/>
+      <c r="AM42" s="35"/>
+      <c r="AO42" s="35"/>
+      <c r="AV42" s="35"/>
+      <c r="AW42"/>
+      <c r="AX42" s="35"/>
+      <c r="AZ42" s="35"/>
+      <c r="BB42" s="35"/>
+      <c r="BD42" s="35"/>
+      <c r="BE42" s="20"/>
+      <c r="BK42" s="35"/>
+      <c r="BL42"/>
+      <c r="BM42" s="35"/>
+      <c r="BO42" s="35"/>
+      <c r="BQ42" s="35"/>
+      <c r="BS42" s="35"/>
+      <c r="BY42"/>
+      <c r="BZ42" s="35"/>
+      <c r="CB42" s="35"/>
+      <c r="CD42" s="35"/>
+      <c r="CF42" s="35"/>
+      <c r="CH42" s="38"/>
       <c r="CI42" s="35"/>
-    </row>
-    <row r="43" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q43" s="35"/>
-      <c r="S43" s="35"/>
-      <c r="U43" s="35"/>
-      <c r="W43" s="35"/>
-      <c r="Y43" s="35"/>
-      <c r="AF43" s="35"/>
-      <c r="AG43"/>
-      <c r="AH43" s="35"/>
-      <c r="AJ43" s="35"/>
-      <c r="AL43" s="35"/>
-      <c r="AN43" s="35"/>
-      <c r="AU43" s="35"/>
-      <c r="AV43"/>
-      <c r="AW43" s="35"/>
-      <c r="AY43" s="35"/>
-      <c r="BA43" s="35"/>
-      <c r="BC43" s="35"/>
-      <c r="BD43" s="20"/>
-      <c r="BJ43" s="35"/>
-      <c r="BK43"/>
-      <c r="BL43" s="35"/>
-      <c r="BN43" s="35"/>
-      <c r="BP43" s="35"/>
-      <c r="BR43" s="35"/>
-      <c r="BX43"/>
-      <c r="BY43" s="35"/>
-      <c r="CA43" s="35"/>
-      <c r="CC43" s="35"/>
-      <c r="CE43" s="35"/>
-      <c r="CG43" s="38"/>
-      <c r="CH43" s="35"/>
+      <c r="CJ42" s="35"/>
+    </row>
+    <row r="43" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="X43" s="35"/>
+      <c r="Z43" s="35"/>
+      <c r="AG43" s="35"/>
+      <c r="AH43"/>
+      <c r="AI43" s="35"/>
+      <c r="AK43" s="35"/>
+      <c r="AM43" s="35"/>
+      <c r="AO43" s="35"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43"/>
+      <c r="AX43" s="35"/>
+      <c r="AZ43" s="35"/>
+      <c r="BB43" s="35"/>
+      <c r="BD43" s="35"/>
+      <c r="BE43" s="20"/>
+      <c r="BK43" s="35"/>
+      <c r="BL43"/>
+      <c r="BM43" s="35"/>
+      <c r="BO43" s="35"/>
+      <c r="BQ43" s="35"/>
+      <c r="BS43" s="35"/>
+      <c r="BY43"/>
+      <c r="BZ43" s="35"/>
+      <c r="CB43" s="35"/>
+      <c r="CD43" s="35"/>
+      <c r="CF43" s="35"/>
+      <c r="CH43" s="38"/>
       <c r="CI43" s="35"/>
-    </row>
-    <row r="44" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="W44" s="35"/>
-      <c r="Y44" s="35"/>
-      <c r="AF44" s="35"/>
-      <c r="AG44"/>
-      <c r="AH44" s="35"/>
-      <c r="AJ44" s="35"/>
-      <c r="AL44" s="35"/>
-      <c r="AN44" s="35"/>
-      <c r="AU44" s="35"/>
-      <c r="AV44"/>
-      <c r="AW44" s="35"/>
-      <c r="AY44" s="35"/>
-      <c r="BA44" s="35"/>
-      <c r="BC44" s="35"/>
-      <c r="BD44" s="20"/>
-      <c r="BJ44" s="35"/>
-      <c r="BK44"/>
-      <c r="BL44" s="35"/>
-      <c r="BN44" s="35"/>
-      <c r="BP44" s="35"/>
-      <c r="BR44" s="35"/>
-      <c r="BX44"/>
-      <c r="BY44" s="35"/>
-      <c r="CA44" s="35"/>
-      <c r="CC44" s="35"/>
-      <c r="CE44" s="35"/>
-      <c r="CG44" s="38"/>
-      <c r="CH44" s="35"/>
+      <c r="CJ43" s="35"/>
+    </row>
+    <row r="44" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="V44" s="35"/>
+      <c r="X44" s="35"/>
+      <c r="Z44" s="35"/>
+      <c r="AG44" s="35"/>
+      <c r="AH44"/>
+      <c r="AI44" s="35"/>
+      <c r="AK44" s="35"/>
+      <c r="AM44" s="35"/>
+      <c r="AO44" s="35"/>
+      <c r="AV44" s="35"/>
+      <c r="AW44"/>
+      <c r="AX44" s="35"/>
+      <c r="AZ44" s="35"/>
+      <c r="BB44" s="35"/>
+      <c r="BD44" s="35"/>
+      <c r="BE44" s="20"/>
+      <c r="BK44" s="35"/>
+      <c r="BL44"/>
+      <c r="BM44" s="35"/>
+      <c r="BO44" s="35"/>
+      <c r="BQ44" s="35"/>
+      <c r="BS44" s="35"/>
+      <c r="BY44"/>
+      <c r="BZ44" s="35"/>
+      <c r="CB44" s="35"/>
+      <c r="CD44" s="35"/>
+      <c r="CF44" s="35"/>
+      <c r="CH44" s="38"/>
       <c r="CI44" s="35"/>
-    </row>
-    <row r="45" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="U45" s="35"/>
-      <c r="W45" s="35"/>
-      <c r="Y45" s="35"/>
-      <c r="AF45" s="35"/>
-      <c r="AG45"/>
-      <c r="AH45" s="35"/>
-      <c r="AJ45" s="35"/>
-      <c r="AL45" s="35"/>
-      <c r="AN45" s="35"/>
-      <c r="AU45" s="35"/>
-      <c r="AV45"/>
-      <c r="AW45" s="35"/>
-      <c r="AY45" s="35"/>
-      <c r="BA45" s="35"/>
-      <c r="BC45" s="35"/>
-      <c r="BD45" s="20"/>
-      <c r="BJ45" s="35"/>
-      <c r="BK45"/>
-      <c r="BL45" s="35"/>
-      <c r="BN45" s="35"/>
-      <c r="BP45" s="35"/>
-      <c r="BR45" s="35"/>
-      <c r="BX45"/>
-      <c r="BY45" s="35"/>
-      <c r="CA45" s="35"/>
-      <c r="CC45" s="35"/>
-      <c r="CE45" s="35"/>
-      <c r="CG45" s="38"/>
-      <c r="CH45" s="35"/>
+      <c r="CJ44" s="35"/>
+    </row>
+    <row r="45" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="V45" s="35"/>
+      <c r="X45" s="35"/>
+      <c r="Z45" s="35"/>
+      <c r="AG45" s="35"/>
+      <c r="AH45"/>
+      <c r="AI45" s="35"/>
+      <c r="AK45" s="35"/>
+      <c r="AM45" s="35"/>
+      <c r="AO45" s="35"/>
+      <c r="AV45" s="35"/>
+      <c r="AW45"/>
+      <c r="AX45" s="35"/>
+      <c r="AZ45" s="35"/>
+      <c r="BB45" s="35"/>
+      <c r="BD45" s="35"/>
+      <c r="BE45" s="20"/>
+      <c r="BK45" s="35"/>
+      <c r="BL45"/>
+      <c r="BM45" s="35"/>
+      <c r="BO45" s="35"/>
+      <c r="BQ45" s="35"/>
+      <c r="BS45" s="35"/>
+      <c r="BY45"/>
+      <c r="BZ45" s="35"/>
+      <c r="CB45" s="35"/>
+      <c r="CD45" s="35"/>
+      <c r="CF45" s="35"/>
+      <c r="CH45" s="38"/>
       <c r="CI45" s="35"/>
-    </row>
-    <row r="46" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="W46" s="35"/>
-      <c r="Y46" s="35"/>
-      <c r="AF46" s="35"/>
-      <c r="AG46"/>
-      <c r="AH46" s="35"/>
-      <c r="AJ46" s="35"/>
-      <c r="AL46" s="35"/>
-      <c r="AN46" s="35"/>
-      <c r="AU46" s="35"/>
-      <c r="AV46"/>
-      <c r="AW46" s="35"/>
-      <c r="AY46" s="35"/>
-      <c r="BA46" s="35"/>
-      <c r="BC46" s="35"/>
-      <c r="BD46" s="20"/>
-      <c r="BJ46" s="35"/>
-      <c r="BK46"/>
-      <c r="BL46" s="35"/>
-      <c r="BN46" s="35"/>
-      <c r="BP46" s="35"/>
-      <c r="BR46" s="35"/>
-      <c r="BX46"/>
-      <c r="BY46" s="35"/>
-      <c r="CA46" s="35"/>
-      <c r="CC46" s="35"/>
-      <c r="CE46" s="35"/>
-      <c r="CG46" s="38"/>
-      <c r="CH46" s="35"/>
+      <c r="CJ45" s="35"/>
+    </row>
+    <row r="46" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="V46" s="35"/>
+      <c r="X46" s="35"/>
+      <c r="Z46" s="35"/>
+      <c r="AG46" s="35"/>
+      <c r="AH46"/>
+      <c r="AI46" s="35"/>
+      <c r="AK46" s="35"/>
+      <c r="AM46" s="35"/>
+      <c r="AO46" s="35"/>
+      <c r="AV46" s="35"/>
+      <c r="AW46"/>
+      <c r="AX46" s="35"/>
+      <c r="AZ46" s="35"/>
+      <c r="BB46" s="35"/>
+      <c r="BD46" s="35"/>
+      <c r="BE46" s="20"/>
+      <c r="BK46" s="35"/>
+      <c r="BL46"/>
+      <c r="BM46" s="35"/>
+      <c r="BO46" s="35"/>
+      <c r="BQ46" s="35"/>
+      <c r="BS46" s="35"/>
+      <c r="BY46"/>
+      <c r="BZ46" s="35"/>
+      <c r="CB46" s="35"/>
+      <c r="CD46" s="35"/>
+      <c r="CF46" s="35"/>
+      <c r="CH46" s="38"/>
       <c r="CI46" s="35"/>
-    </row>
-    <row r="47" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="W47" s="35"/>
-      <c r="Y47" s="35"/>
-      <c r="AF47" s="35"/>
-      <c r="AG47"/>
-      <c r="AH47" s="35"/>
-      <c r="AJ47" s="35"/>
-      <c r="AL47" s="35"/>
-      <c r="AN47" s="35"/>
-      <c r="AU47" s="35"/>
-      <c r="AV47"/>
-      <c r="AW47" s="35"/>
-      <c r="AY47" s="35"/>
-      <c r="BA47" s="35"/>
-      <c r="BC47" s="35"/>
-      <c r="BD47" s="20"/>
-      <c r="BJ47" s="35"/>
-      <c r="BK47"/>
-      <c r="BL47" s="35"/>
-      <c r="BN47" s="35"/>
-      <c r="BP47" s="35"/>
-      <c r="BR47" s="35"/>
-      <c r="BX47"/>
-      <c r="BY47" s="35"/>
-      <c r="CA47" s="35"/>
-      <c r="CC47" s="35"/>
-      <c r="CE47" s="35"/>
-      <c r="CG47" s="38"/>
-      <c r="CH47" s="35"/>
+      <c r="CJ46" s="35"/>
+    </row>
+    <row r="47" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="X47" s="35"/>
+      <c r="Z47" s="35"/>
+      <c r="AG47" s="35"/>
+      <c r="AH47"/>
+      <c r="AI47" s="35"/>
+      <c r="AK47" s="35"/>
+      <c r="AM47" s="35"/>
+      <c r="AO47" s="35"/>
+      <c r="AV47" s="35"/>
+      <c r="AW47"/>
+      <c r="AX47" s="35"/>
+      <c r="AZ47" s="35"/>
+      <c r="BB47" s="35"/>
+      <c r="BD47" s="35"/>
+      <c r="BE47" s="20"/>
+      <c r="BK47" s="35"/>
+      <c r="BL47"/>
+      <c r="BM47" s="35"/>
+      <c r="BO47" s="35"/>
+      <c r="BQ47" s="35"/>
+      <c r="BS47" s="35"/>
+      <c r="BY47"/>
+      <c r="BZ47" s="35"/>
+      <c r="CB47" s="35"/>
+      <c r="CD47" s="35"/>
+      <c r="CF47" s="35"/>
+      <c r="CH47" s="38"/>
       <c r="CI47" s="35"/>
-    </row>
-    <row r="48" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="U48" s="35"/>
-      <c r="W48" s="35"/>
-      <c r="Y48" s="35"/>
-      <c r="AF48" s="35"/>
-      <c r="AG48"/>
-      <c r="AH48" s="35"/>
-      <c r="AJ48" s="35"/>
-      <c r="AL48" s="35"/>
-      <c r="AN48" s="35"/>
-      <c r="AU48" s="35"/>
-      <c r="AV48"/>
-      <c r="AW48" s="35"/>
-      <c r="AY48" s="35"/>
-      <c r="BA48" s="35"/>
-      <c r="BC48" s="35"/>
-      <c r="BD48" s="20"/>
-      <c r="BJ48" s="35"/>
-      <c r="BK48"/>
-      <c r="BL48" s="35"/>
-      <c r="BN48" s="35"/>
-      <c r="BP48" s="35"/>
-      <c r="BR48" s="35"/>
-      <c r="BX48"/>
-      <c r="BY48" s="35"/>
-      <c r="CA48" s="35"/>
-      <c r="CC48" s="35"/>
-      <c r="CE48" s="35"/>
-      <c r="CG48" s="38"/>
-      <c r="CH48" s="35"/>
+      <c r="CJ47" s="35"/>
+    </row>
+    <row r="48" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="V48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AG48" s="35"/>
+      <c r="AH48"/>
+      <c r="AI48" s="35"/>
+      <c r="AK48" s="35"/>
+      <c r="AM48" s="35"/>
+      <c r="AO48" s="35"/>
+      <c r="AV48" s="35"/>
+      <c r="AW48"/>
+      <c r="AX48" s="35"/>
+      <c r="AZ48" s="35"/>
+      <c r="BB48" s="35"/>
+      <c r="BD48" s="35"/>
+      <c r="BE48" s="20"/>
+      <c r="BK48" s="35"/>
+      <c r="BL48"/>
+      <c r="BM48" s="35"/>
+      <c r="BO48" s="35"/>
+      <c r="BQ48" s="35"/>
+      <c r="BS48" s="35"/>
+      <c r="BY48"/>
+      <c r="BZ48" s="35"/>
+      <c r="CB48" s="35"/>
+      <c r="CD48" s="35"/>
+      <c r="CF48" s="35"/>
+      <c r="CH48" s="38"/>
       <c r="CI48" s="35"/>
-    </row>
-    <row r="49" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q49" s="35"/>
-      <c r="S49" s="35"/>
-      <c r="U49" s="35"/>
-      <c r="W49" s="35"/>
-      <c r="Y49" s="35"/>
-      <c r="AF49" s="35"/>
-      <c r="AG49"/>
-      <c r="AH49" s="35"/>
-      <c r="AJ49" s="35"/>
-      <c r="AL49" s="35"/>
-      <c r="AN49" s="35"/>
-      <c r="AU49" s="35"/>
-      <c r="AV49"/>
-      <c r="AW49" s="35"/>
-      <c r="AY49" s="35"/>
-      <c r="BA49" s="35"/>
-      <c r="BC49" s="35"/>
-      <c r="BD49" s="20"/>
-      <c r="BJ49" s="35"/>
-      <c r="BK49"/>
-      <c r="BL49" s="35"/>
-      <c r="BN49" s="35"/>
-      <c r="BP49" s="35"/>
-      <c r="BR49" s="35"/>
-      <c r="BX49"/>
-      <c r="BY49" s="35"/>
-      <c r="CA49" s="35"/>
-      <c r="CC49" s="35"/>
-      <c r="CE49" s="35"/>
-      <c r="CG49" s="38"/>
-      <c r="CH49" s="35"/>
+      <c r="CJ48" s="35"/>
+    </row>
+    <row r="49" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="V49" s="35"/>
+      <c r="X49" s="35"/>
+      <c r="Z49" s="35"/>
+      <c r="AG49" s="35"/>
+      <c r="AH49"/>
+      <c r="AI49" s="35"/>
+      <c r="AK49" s="35"/>
+      <c r="AM49" s="35"/>
+      <c r="AO49" s="35"/>
+      <c r="AV49" s="35"/>
+      <c r="AW49"/>
+      <c r="AX49" s="35"/>
+      <c r="AZ49" s="35"/>
+      <c r="BB49" s="35"/>
+      <c r="BD49" s="35"/>
+      <c r="BE49" s="20"/>
+      <c r="BK49" s="35"/>
+      <c r="BL49"/>
+      <c r="BM49" s="35"/>
+      <c r="BO49" s="35"/>
+      <c r="BQ49" s="35"/>
+      <c r="BS49" s="35"/>
+      <c r="BY49"/>
+      <c r="BZ49" s="35"/>
+      <c r="CB49" s="35"/>
+      <c r="CD49" s="35"/>
+      <c r="CF49" s="35"/>
+      <c r="CH49" s="38"/>
       <c r="CI49" s="35"/>
-    </row>
-    <row r="50" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="U50" s="35"/>
-      <c r="W50" s="35"/>
-      <c r="Y50" s="35"/>
-      <c r="AF50" s="35"/>
-      <c r="AG50"/>
-      <c r="AH50" s="35"/>
-      <c r="AJ50" s="35"/>
-      <c r="AL50" s="35"/>
-      <c r="AN50" s="35"/>
-      <c r="AU50" s="35"/>
-      <c r="AV50"/>
-      <c r="AW50" s="35"/>
-      <c r="AY50" s="35"/>
-      <c r="BA50" s="35"/>
-      <c r="BC50" s="35"/>
-      <c r="BD50" s="20"/>
-      <c r="BJ50" s="35"/>
-      <c r="BK50"/>
-      <c r="BL50" s="35"/>
-      <c r="BN50" s="35"/>
-      <c r="BP50" s="35"/>
-      <c r="BR50" s="35"/>
-      <c r="BX50"/>
-      <c r="BY50" s="35"/>
-      <c r="CA50" s="35"/>
-      <c r="CC50" s="35"/>
-      <c r="CE50" s="35"/>
-      <c r="CG50" s="38"/>
-      <c r="CH50" s="35"/>
+      <c r="CJ49" s="35"/>
+    </row>
+    <row r="50" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="X50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AG50" s="35"/>
+      <c r="AH50"/>
+      <c r="AI50" s="35"/>
+      <c r="AK50" s="35"/>
+      <c r="AM50" s="35"/>
+      <c r="AO50" s="35"/>
+      <c r="AV50" s="35"/>
+      <c r="AW50"/>
+      <c r="AX50" s="35"/>
+      <c r="AZ50" s="35"/>
+      <c r="BB50" s="35"/>
+      <c r="BD50" s="35"/>
+      <c r="BE50" s="20"/>
+      <c r="BK50" s="35"/>
+      <c r="BL50"/>
+      <c r="BM50" s="35"/>
+      <c r="BO50" s="35"/>
+      <c r="BQ50" s="35"/>
+      <c r="BS50" s="35"/>
+      <c r="BY50"/>
+      <c r="BZ50" s="35"/>
+      <c r="CB50" s="35"/>
+      <c r="CD50" s="35"/>
+      <c r="CF50" s="35"/>
+      <c r="CH50" s="38"/>
       <c r="CI50" s="35"/>
-    </row>
-    <row r="51" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q51" s="35"/>
-      <c r="S51" s="35"/>
-      <c r="U51" s="35"/>
-      <c r="W51" s="35"/>
-      <c r="Y51" s="35"/>
-      <c r="AF51" s="35"/>
-      <c r="AG51"/>
-      <c r="AH51" s="35"/>
-      <c r="AJ51" s="35"/>
-      <c r="AL51" s="35"/>
-      <c r="AN51" s="35"/>
-      <c r="AU51" s="35"/>
-      <c r="AV51"/>
-      <c r="AW51" s="35"/>
-      <c r="AY51" s="35"/>
-      <c r="BA51" s="35"/>
-      <c r="BC51" s="35"/>
-      <c r="BD51" s="20"/>
-      <c r="BJ51" s="35"/>
-      <c r="BK51"/>
-      <c r="BL51" s="35"/>
-      <c r="BN51" s="35"/>
-      <c r="BP51" s="35"/>
-      <c r="BR51" s="35"/>
-      <c r="BX51"/>
-      <c r="BY51" s="35"/>
-      <c r="CA51" s="35"/>
-      <c r="CC51" s="35"/>
-      <c r="CE51" s="35"/>
-      <c r="CG51" s="38"/>
-      <c r="CH51" s="35"/>
+      <c r="CJ50" s="35"/>
+    </row>
+    <row r="51" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R51" s="35"/>
+      <c r="T51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="X51" s="35"/>
+      <c r="Z51" s="35"/>
+      <c r="AG51" s="35"/>
+      <c r="AH51"/>
+      <c r="AI51" s="35"/>
+      <c r="AK51" s="35"/>
+      <c r="AM51" s="35"/>
+      <c r="AO51" s="35"/>
+      <c r="AV51" s="35"/>
+      <c r="AW51"/>
+      <c r="AX51" s="35"/>
+      <c r="AZ51" s="35"/>
+      <c r="BB51" s="35"/>
+      <c r="BD51" s="35"/>
+      <c r="BE51" s="20"/>
+      <c r="BK51" s="35"/>
+      <c r="BL51"/>
+      <c r="BM51" s="35"/>
+      <c r="BO51" s="35"/>
+      <c r="BQ51" s="35"/>
+      <c r="BS51" s="35"/>
+      <c r="BY51"/>
+      <c r="BZ51" s="35"/>
+      <c r="CB51" s="35"/>
+      <c r="CD51" s="35"/>
+      <c r="CF51" s="35"/>
+      <c r="CH51" s="38"/>
       <c r="CI51" s="35"/>
-    </row>
-    <row r="52" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q52" s="35"/>
-      <c r="S52" s="35"/>
-      <c r="U52" s="35"/>
-      <c r="W52" s="35"/>
-      <c r="Y52" s="35"/>
-      <c r="AF52" s="35"/>
-      <c r="AG52"/>
-      <c r="AH52" s="35"/>
-      <c r="AJ52" s="35"/>
-      <c r="AL52" s="35"/>
-      <c r="AN52" s="35"/>
-      <c r="AU52" s="35"/>
-      <c r="AV52"/>
-      <c r="AW52" s="35"/>
-      <c r="AY52" s="35"/>
-      <c r="BA52" s="35"/>
-      <c r="BC52" s="35"/>
-      <c r="BD52" s="20"/>
-      <c r="BJ52" s="35"/>
-      <c r="BK52"/>
-      <c r="BL52" s="35"/>
-      <c r="BN52" s="35"/>
-      <c r="BP52" s="35"/>
-      <c r="BR52" s="35"/>
-      <c r="BX52"/>
-      <c r="BY52" s="35"/>
-      <c r="CA52" s="35"/>
-      <c r="CC52" s="35"/>
-      <c r="CE52" s="35"/>
-      <c r="CG52" s="38"/>
-      <c r="CH52" s="35"/>
+      <c r="CJ51" s="35"/>
+    </row>
+    <row r="52" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="X52" s="35"/>
+      <c r="Z52" s="35"/>
+      <c r="AG52" s="35"/>
+      <c r="AH52"/>
+      <c r="AI52" s="35"/>
+      <c r="AK52" s="35"/>
+      <c r="AM52" s="35"/>
+      <c r="AO52" s="35"/>
+      <c r="AV52" s="35"/>
+      <c r="AW52"/>
+      <c r="AX52" s="35"/>
+      <c r="AZ52" s="35"/>
+      <c r="BB52" s="35"/>
+      <c r="BD52" s="35"/>
+      <c r="BE52" s="20"/>
+      <c r="BK52" s="35"/>
+      <c r="BL52"/>
+      <c r="BM52" s="35"/>
+      <c r="BO52" s="35"/>
+      <c r="BQ52" s="35"/>
+      <c r="BS52" s="35"/>
+      <c r="BY52"/>
+      <c r="BZ52" s="35"/>
+      <c r="CB52" s="35"/>
+      <c r="CD52" s="35"/>
+      <c r="CF52" s="35"/>
+      <c r="CH52" s="38"/>
       <c r="CI52" s="35"/>
-    </row>
-    <row r="53" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q53" s="35"/>
-      <c r="S53" s="35"/>
-      <c r="U53" s="35"/>
-      <c r="W53" s="35"/>
-      <c r="Y53" s="35"/>
-      <c r="AF53" s="35"/>
-      <c r="AG53"/>
-      <c r="AH53" s="35"/>
-      <c r="AJ53" s="35"/>
-      <c r="AL53" s="35"/>
-      <c r="AN53" s="35"/>
-      <c r="AU53" s="35"/>
-      <c r="AV53"/>
-      <c r="AW53" s="35"/>
-      <c r="AY53" s="35"/>
-      <c r="BA53" s="35"/>
-      <c r="BC53" s="35"/>
-      <c r="BD53" s="20"/>
-      <c r="BJ53" s="35"/>
-      <c r="BK53"/>
-      <c r="BL53" s="35"/>
-      <c r="BN53" s="35"/>
-      <c r="BP53" s="35"/>
-      <c r="BR53" s="35"/>
-      <c r="BX53"/>
-      <c r="BY53" s="35"/>
-      <c r="CA53" s="35"/>
-      <c r="CC53" s="35"/>
-      <c r="CE53" s="35"/>
-      <c r="CG53" s="38"/>
-      <c r="CH53" s="35"/>
+      <c r="CJ52" s="35"/>
+    </row>
+    <row r="53" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="V53" s="35"/>
+      <c r="X53" s="35"/>
+      <c r="Z53" s="35"/>
+      <c r="AG53" s="35"/>
+      <c r="AH53"/>
+      <c r="AI53" s="35"/>
+      <c r="AK53" s="35"/>
+      <c r="AM53" s="35"/>
+      <c r="AO53" s="35"/>
+      <c r="AV53" s="35"/>
+      <c r="AW53"/>
+      <c r="AX53" s="35"/>
+      <c r="AZ53" s="35"/>
+      <c r="BB53" s="35"/>
+      <c r="BD53" s="35"/>
+      <c r="BE53" s="20"/>
+      <c r="BK53" s="35"/>
+      <c r="BL53"/>
+      <c r="BM53" s="35"/>
+      <c r="BO53" s="35"/>
+      <c r="BQ53" s="35"/>
+      <c r="BS53" s="35"/>
+      <c r="BY53"/>
+      <c r="BZ53" s="35"/>
+      <c r="CB53" s="35"/>
+      <c r="CD53" s="35"/>
+      <c r="CF53" s="35"/>
+      <c r="CH53" s="38"/>
       <c r="CI53" s="35"/>
-    </row>
-    <row r="54" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q54" s="35"/>
-      <c r="S54" s="35"/>
-      <c r="U54" s="35"/>
-      <c r="W54" s="35"/>
-      <c r="Y54" s="35"/>
-      <c r="AF54" s="35"/>
-      <c r="AG54"/>
-      <c r="AH54" s="35"/>
-      <c r="AJ54" s="35"/>
-      <c r="AL54" s="35"/>
-      <c r="AN54" s="35"/>
-      <c r="AU54" s="35"/>
-      <c r="AV54"/>
-      <c r="AW54" s="35"/>
-      <c r="AY54" s="35"/>
-      <c r="BA54" s="35"/>
-      <c r="BC54" s="35"/>
-      <c r="BD54" s="20"/>
-      <c r="BJ54" s="35"/>
-      <c r="BK54"/>
-      <c r="BL54" s="35"/>
-      <c r="BN54" s="35"/>
-      <c r="BP54" s="35"/>
-      <c r="BR54" s="35"/>
-      <c r="BX54"/>
-      <c r="BY54" s="35"/>
-      <c r="CA54" s="35"/>
-      <c r="CC54" s="35"/>
-      <c r="CE54" s="35"/>
-      <c r="CG54" s="38"/>
-      <c r="CH54" s="35"/>
+      <c r="CJ53" s="35"/>
+    </row>
+    <row r="54" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="V54" s="35"/>
+      <c r="X54" s="35"/>
+      <c r="Z54" s="35"/>
+      <c r="AG54" s="35"/>
+      <c r="AH54"/>
+      <c r="AI54" s="35"/>
+      <c r="AK54" s="35"/>
+      <c r="AM54" s="35"/>
+      <c r="AO54" s="35"/>
+      <c r="AV54" s="35"/>
+      <c r="AW54"/>
+      <c r="AX54" s="35"/>
+      <c r="AZ54" s="35"/>
+      <c r="BB54" s="35"/>
+      <c r="BD54" s="35"/>
+      <c r="BE54" s="20"/>
+      <c r="BK54" s="35"/>
+      <c r="BL54"/>
+      <c r="BM54" s="35"/>
+      <c r="BO54" s="35"/>
+      <c r="BQ54" s="35"/>
+      <c r="BS54" s="35"/>
+      <c r="BY54"/>
+      <c r="BZ54" s="35"/>
+      <c r="CB54" s="35"/>
+      <c r="CD54" s="35"/>
+      <c r="CF54" s="35"/>
+      <c r="CH54" s="38"/>
       <c r="CI54" s="35"/>
-    </row>
-    <row r="55" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q55" s="35"/>
-      <c r="S55" s="35"/>
-      <c r="U55" s="35"/>
-      <c r="W55" s="35"/>
-      <c r="Y55" s="35"/>
-      <c r="AF55" s="35"/>
-      <c r="AG55"/>
-      <c r="AH55" s="35"/>
-      <c r="AJ55" s="35"/>
-      <c r="AL55" s="35"/>
-      <c r="AN55" s="35"/>
-      <c r="AU55" s="35"/>
-      <c r="AV55"/>
-      <c r="AW55" s="35"/>
-      <c r="AY55" s="35"/>
-      <c r="BA55" s="35"/>
-      <c r="BC55" s="35"/>
-      <c r="BD55" s="20"/>
-      <c r="BJ55" s="35"/>
-      <c r="BK55"/>
-      <c r="BL55" s="35"/>
-      <c r="BN55" s="35"/>
-      <c r="BP55" s="35"/>
-      <c r="BR55" s="35"/>
-      <c r="BX55"/>
-      <c r="BY55" s="35"/>
-      <c r="CA55" s="35"/>
-      <c r="CC55" s="35"/>
-      <c r="CE55" s="35"/>
-      <c r="CG55" s="38"/>
-      <c r="CH55" s="35"/>
+      <c r="CJ54" s="35"/>
+    </row>
+    <row r="55" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R55" s="35"/>
+      <c r="T55" s="35"/>
+      <c r="V55" s="35"/>
+      <c r="X55" s="35"/>
+      <c r="Z55" s="35"/>
+      <c r="AG55" s="35"/>
+      <c r="AH55"/>
+      <c r="AI55" s="35"/>
+      <c r="AK55" s="35"/>
+      <c r="AM55" s="35"/>
+      <c r="AO55" s="35"/>
+      <c r="AV55" s="35"/>
+      <c r="AW55"/>
+      <c r="AX55" s="35"/>
+      <c r="AZ55" s="35"/>
+      <c r="BB55" s="35"/>
+      <c r="BD55" s="35"/>
+      <c r="BE55" s="20"/>
+      <c r="BK55" s="35"/>
+      <c r="BL55"/>
+      <c r="BM55" s="35"/>
+      <c r="BO55" s="35"/>
+      <c r="BQ55" s="35"/>
+      <c r="BS55" s="35"/>
+      <c r="BY55"/>
+      <c r="BZ55" s="35"/>
+      <c r="CB55" s="35"/>
+      <c r="CD55" s="35"/>
+      <c r="CF55" s="35"/>
+      <c r="CH55" s="38"/>
       <c r="CI55" s="35"/>
-    </row>
-    <row r="56" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q56" s="35"/>
-      <c r="S56" s="35"/>
-      <c r="U56" s="35"/>
-      <c r="W56" s="35"/>
-      <c r="Y56" s="35"/>
-      <c r="AF56" s="35"/>
-      <c r="AG56"/>
-      <c r="AH56" s="35"/>
-      <c r="AJ56" s="35"/>
-      <c r="AL56" s="35"/>
-      <c r="AN56" s="35"/>
-      <c r="AU56" s="35"/>
-      <c r="AV56"/>
-      <c r="AW56" s="35"/>
-      <c r="AY56" s="35"/>
-      <c r="BA56" s="35"/>
-      <c r="BC56" s="35"/>
-      <c r="BD56" s="20"/>
-      <c r="BJ56" s="35"/>
-      <c r="BK56"/>
-      <c r="BL56" s="35"/>
-      <c r="BN56" s="35"/>
-      <c r="BP56" s="35"/>
-      <c r="BR56" s="35"/>
-      <c r="BX56"/>
-      <c r="BY56" s="35"/>
-      <c r="CA56" s="35"/>
-      <c r="CC56" s="35"/>
-      <c r="CE56" s="35"/>
-      <c r="CG56" s="38"/>
-      <c r="CH56" s="35"/>
+      <c r="CJ55" s="35"/>
+    </row>
+    <row r="56" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R56" s="35"/>
+      <c r="T56" s="35"/>
+      <c r="V56" s="35"/>
+      <c r="X56" s="35"/>
+      <c r="Z56" s="35"/>
+      <c r="AG56" s="35"/>
+      <c r="AH56"/>
+      <c r="AI56" s="35"/>
+      <c r="AK56" s="35"/>
+      <c r="AM56" s="35"/>
+      <c r="AO56" s="35"/>
+      <c r="AV56" s="35"/>
+      <c r="AW56"/>
+      <c r="AX56" s="35"/>
+      <c r="AZ56" s="35"/>
+      <c r="BB56" s="35"/>
+      <c r="BD56" s="35"/>
+      <c r="BE56" s="20"/>
+      <c r="BK56" s="35"/>
+      <c r="BL56"/>
+      <c r="BM56" s="35"/>
+      <c r="BO56" s="35"/>
+      <c r="BQ56" s="35"/>
+      <c r="BS56" s="35"/>
+      <c r="BY56"/>
+      <c r="BZ56" s="35"/>
+      <c r="CB56" s="35"/>
+      <c r="CD56" s="35"/>
+      <c r="CF56" s="35"/>
+      <c r="CH56" s="38"/>
       <c r="CI56" s="35"/>
-    </row>
-    <row r="57" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q57" s="35"/>
-      <c r="S57" s="35"/>
-      <c r="U57" s="35"/>
-      <c r="W57" s="35"/>
-      <c r="Y57" s="35"/>
-      <c r="AF57" s="35"/>
-      <c r="AG57"/>
-      <c r="AH57" s="35"/>
-      <c r="AJ57" s="35"/>
-      <c r="AL57" s="35"/>
-      <c r="AN57" s="35"/>
-      <c r="AU57" s="35"/>
-      <c r="AV57"/>
-      <c r="AW57" s="35"/>
-      <c r="AY57" s="35"/>
-      <c r="BA57" s="35"/>
-      <c r="BC57" s="35"/>
-      <c r="BD57" s="20"/>
-      <c r="BJ57" s="35"/>
-      <c r="BK57"/>
-      <c r="BL57" s="35"/>
-      <c r="BN57" s="35"/>
-      <c r="BP57" s="35"/>
-      <c r="BR57" s="35"/>
-      <c r="BX57"/>
-      <c r="BY57" s="35"/>
-      <c r="CA57" s="35"/>
-      <c r="CC57" s="35"/>
-      <c r="CE57" s="35"/>
-      <c r="CG57" s="38"/>
-      <c r="CH57" s="35"/>
+      <c r="CJ56" s="35"/>
+    </row>
+    <row r="57" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R57" s="35"/>
+      <c r="T57" s="35"/>
+      <c r="V57" s="35"/>
+      <c r="X57" s="35"/>
+      <c r="Z57" s="35"/>
+      <c r="AG57" s="35"/>
+      <c r="AH57"/>
+      <c r="AI57" s="35"/>
+      <c r="AK57" s="35"/>
+      <c r="AM57" s="35"/>
+      <c r="AO57" s="35"/>
+      <c r="AV57" s="35"/>
+      <c r="AW57"/>
+      <c r="AX57" s="35"/>
+      <c r="AZ57" s="35"/>
+      <c r="BB57" s="35"/>
+      <c r="BD57" s="35"/>
+      <c r="BE57" s="20"/>
+      <c r="BK57" s="35"/>
+      <c r="BL57"/>
+      <c r="BM57" s="35"/>
+      <c r="BO57" s="35"/>
+      <c r="BQ57" s="35"/>
+      <c r="BS57" s="35"/>
+      <c r="BY57"/>
+      <c r="BZ57" s="35"/>
+      <c r="CB57" s="35"/>
+      <c r="CD57" s="35"/>
+      <c r="CF57" s="35"/>
+      <c r="CH57" s="38"/>
       <c r="CI57" s="35"/>
-    </row>
-    <row r="58" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q58" s="35"/>
-      <c r="S58" s="35"/>
-      <c r="U58" s="35"/>
-      <c r="W58" s="35"/>
-      <c r="Y58" s="35"/>
-      <c r="AF58" s="35"/>
-      <c r="AG58"/>
-      <c r="AH58" s="35"/>
-      <c r="AJ58" s="35"/>
-      <c r="AL58" s="35"/>
-      <c r="AN58" s="35"/>
-      <c r="AU58" s="35"/>
-      <c r="AV58"/>
-      <c r="AW58" s="35"/>
-      <c r="AY58" s="35"/>
-      <c r="BA58" s="35"/>
-      <c r="BC58" s="35"/>
-      <c r="BD58" s="20"/>
-      <c r="BJ58" s="35"/>
-      <c r="BK58"/>
-      <c r="BL58" s="35"/>
-      <c r="BN58" s="35"/>
-      <c r="BP58" s="35"/>
-      <c r="BR58" s="35"/>
-      <c r="BX58"/>
-      <c r="BY58" s="35"/>
-      <c r="CA58" s="35"/>
-      <c r="CC58" s="35"/>
-      <c r="CE58" s="35"/>
-      <c r="CG58" s="38"/>
-      <c r="CH58" s="35"/>
+      <c r="CJ57" s="35"/>
+    </row>
+    <row r="58" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R58" s="35"/>
+      <c r="T58" s="35"/>
+      <c r="V58" s="35"/>
+      <c r="X58" s="35"/>
+      <c r="Z58" s="35"/>
+      <c r="AG58" s="35"/>
+      <c r="AH58"/>
+      <c r="AI58" s="35"/>
+      <c r="AK58" s="35"/>
+      <c r="AM58" s="35"/>
+      <c r="AO58" s="35"/>
+      <c r="AV58" s="35"/>
+      <c r="AW58"/>
+      <c r="AX58" s="35"/>
+      <c r="AZ58" s="35"/>
+      <c r="BB58" s="35"/>
+      <c r="BD58" s="35"/>
+      <c r="BE58" s="20"/>
+      <c r="BK58" s="35"/>
+      <c r="BL58"/>
+      <c r="BM58" s="35"/>
+      <c r="BO58" s="35"/>
+      <c r="BQ58" s="35"/>
+      <c r="BS58" s="35"/>
+      <c r="BY58"/>
+      <c r="BZ58" s="35"/>
+      <c r="CB58" s="35"/>
+      <c r="CD58" s="35"/>
+      <c r="CF58" s="35"/>
+      <c r="CH58" s="38"/>
       <c r="CI58" s="35"/>
-    </row>
-    <row r="59" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="U59" s="35"/>
-      <c r="W59" s="35"/>
-      <c r="Y59" s="35"/>
-      <c r="AF59" s="35"/>
-      <c r="AG59"/>
-      <c r="AH59" s="35"/>
-      <c r="AJ59" s="35"/>
-      <c r="AL59" s="35"/>
-      <c r="AN59" s="35"/>
-      <c r="AU59" s="35"/>
-      <c r="AV59"/>
-      <c r="AW59" s="35"/>
-      <c r="AY59" s="35"/>
-      <c r="BA59" s="35"/>
-      <c r="BC59" s="35"/>
-      <c r="BD59" s="20"/>
-      <c r="BJ59" s="35"/>
-      <c r="BK59"/>
-      <c r="BL59" s="35"/>
-      <c r="BN59" s="35"/>
-      <c r="BP59" s="35"/>
-      <c r="BR59" s="35"/>
-      <c r="BX59"/>
-      <c r="BY59" s="35"/>
-      <c r="CA59" s="35"/>
-      <c r="CC59" s="35"/>
-      <c r="CE59" s="35"/>
-      <c r="CG59" s="38"/>
-      <c r="CH59" s="35"/>
+      <c r="CJ58" s="35"/>
+    </row>
+    <row r="59" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="X59" s="35"/>
+      <c r="Z59" s="35"/>
+      <c r="AG59" s="35"/>
+      <c r="AH59"/>
+      <c r="AI59" s="35"/>
+      <c r="AK59" s="35"/>
+      <c r="AM59" s="35"/>
+      <c r="AO59" s="35"/>
+      <c r="AV59" s="35"/>
+      <c r="AW59"/>
+      <c r="AX59" s="35"/>
+      <c r="AZ59" s="35"/>
+      <c r="BB59" s="35"/>
+      <c r="BD59" s="35"/>
+      <c r="BE59" s="20"/>
+      <c r="BK59" s="35"/>
+      <c r="BL59"/>
+      <c r="BM59" s="35"/>
+      <c r="BO59" s="35"/>
+      <c r="BQ59" s="35"/>
+      <c r="BS59" s="35"/>
+      <c r="BY59"/>
+      <c r="BZ59" s="35"/>
+      <c r="CB59" s="35"/>
+      <c r="CD59" s="35"/>
+      <c r="CF59" s="35"/>
+      <c r="CH59" s="38"/>
       <c r="CI59" s="35"/>
-    </row>
-    <row r="60" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="AF60" s="35"/>
-      <c r="AG60"/>
-      <c r="AH60" s="35"/>
-      <c r="AJ60" s="35"/>
-      <c r="AL60" s="35"/>
-      <c r="AN60" s="35"/>
-      <c r="AU60" s="35"/>
-      <c r="AV60"/>
-      <c r="AW60" s="35"/>
-      <c r="AY60" s="35"/>
-      <c r="BA60" s="35"/>
-      <c r="BC60" s="35"/>
-      <c r="BD60" s="20"/>
-      <c r="BJ60" s="35"/>
-      <c r="BK60"/>
-      <c r="BL60" s="35"/>
-      <c r="BN60" s="35"/>
-      <c r="BP60" s="35"/>
-      <c r="BR60" s="35"/>
-      <c r="BX60"/>
-      <c r="BY60" s="35"/>
-      <c r="CA60" s="35"/>
-      <c r="CC60" s="35"/>
-      <c r="CE60" s="35"/>
-      <c r="CG60" s="38"/>
-      <c r="CH60" s="35"/>
+      <c r="CJ59" s="35"/>
+    </row>
+    <row r="60" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R60" s="35"/>
+      <c r="T60" s="35"/>
+      <c r="V60" s="35"/>
+      <c r="X60" s="35"/>
+      <c r="Z60" s="35"/>
+      <c r="AG60" s="35"/>
+      <c r="AH60"/>
+      <c r="AI60" s="35"/>
+      <c r="AK60" s="35"/>
+      <c r="AM60" s="35"/>
+      <c r="AO60" s="35"/>
+      <c r="AV60" s="35"/>
+      <c r="AW60"/>
+      <c r="AX60" s="35"/>
+      <c r="AZ60" s="35"/>
+      <c r="BB60" s="35"/>
+      <c r="BD60" s="35"/>
+      <c r="BE60" s="20"/>
+      <c r="BK60" s="35"/>
+      <c r="BL60"/>
+      <c r="BM60" s="35"/>
+      <c r="BO60" s="35"/>
+      <c r="BQ60" s="35"/>
+      <c r="BS60" s="35"/>
+      <c r="BY60"/>
+      <c r="BZ60" s="35"/>
+      <c r="CB60" s="35"/>
+      <c r="CD60" s="35"/>
+      <c r="CF60" s="35"/>
+      <c r="CH60" s="38"/>
       <c r="CI60" s="35"/>
-    </row>
-    <row r="61" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="U61" s="35"/>
-      <c r="W61" s="35"/>
-      <c r="Y61" s="35"/>
-      <c r="AF61" s="35"/>
-      <c r="AG61"/>
-      <c r="AH61" s="35"/>
-      <c r="AJ61" s="35"/>
-      <c r="AL61" s="35"/>
-      <c r="AN61" s="35"/>
-      <c r="AU61" s="35"/>
-      <c r="AV61"/>
-      <c r="AW61" s="35"/>
-      <c r="AY61" s="35"/>
-      <c r="BA61" s="35"/>
-      <c r="BC61" s="35"/>
-      <c r="BD61" s="20"/>
-      <c r="BJ61" s="35"/>
-      <c r="BK61"/>
-      <c r="BL61" s="35"/>
-      <c r="BN61" s="35"/>
-      <c r="BP61" s="35"/>
-      <c r="BR61" s="35"/>
-      <c r="BX61"/>
-      <c r="BY61" s="35"/>
-      <c r="CA61" s="35"/>
-      <c r="CC61" s="35"/>
-      <c r="CE61" s="35"/>
-      <c r="CG61" s="38"/>
-      <c r="CH61" s="35"/>
+      <c r="CJ60" s="35"/>
+    </row>
+    <row r="61" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R61" s="35"/>
+      <c r="T61" s="35"/>
+      <c r="V61" s="35"/>
+      <c r="X61" s="35"/>
+      <c r="Z61" s="35"/>
+      <c r="AG61" s="35"/>
+      <c r="AH61"/>
+      <c r="AI61" s="35"/>
+      <c r="AK61" s="35"/>
+      <c r="AM61" s="35"/>
+      <c r="AO61" s="35"/>
+      <c r="AV61" s="35"/>
+      <c r="AW61"/>
+      <c r="AX61" s="35"/>
+      <c r="AZ61" s="35"/>
+      <c r="BB61" s="35"/>
+      <c r="BD61" s="35"/>
+      <c r="BE61" s="20"/>
+      <c r="BK61" s="35"/>
+      <c r="BL61"/>
+      <c r="BM61" s="35"/>
+      <c r="BO61" s="35"/>
+      <c r="BQ61" s="35"/>
+      <c r="BS61" s="35"/>
+      <c r="BY61"/>
+      <c r="BZ61" s="35"/>
+      <c r="CB61" s="35"/>
+      <c r="CD61" s="35"/>
+      <c r="CF61" s="35"/>
+      <c r="CH61" s="38"/>
       <c r="CI61" s="35"/>
-    </row>
-    <row r="62" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q62" s="35"/>
-      <c r="S62" s="35"/>
-      <c r="U62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="Y62" s="35"/>
-      <c r="AF62" s="35"/>
-      <c r="AG62"/>
-      <c r="AH62" s="35"/>
-      <c r="AJ62" s="35"/>
-      <c r="AL62" s="35"/>
-      <c r="AN62" s="35"/>
-      <c r="AU62" s="35"/>
-      <c r="AV62"/>
-      <c r="AW62" s="35"/>
-      <c r="AY62" s="35"/>
-      <c r="BA62" s="35"/>
-      <c r="BC62" s="35"/>
-      <c r="BD62" s="20"/>
-      <c r="BJ62" s="35"/>
-      <c r="BK62"/>
-      <c r="BL62" s="35"/>
-      <c r="BN62" s="35"/>
-      <c r="BP62" s="35"/>
-      <c r="BR62" s="35"/>
-      <c r="BX62"/>
-      <c r="BY62" s="35"/>
-      <c r="CA62" s="35"/>
-      <c r="CC62" s="35"/>
-      <c r="CE62" s="35"/>
-      <c r="CG62" s="38"/>
-      <c r="CH62" s="35"/>
+      <c r="CJ61" s="35"/>
+    </row>
+    <row r="62" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R62" s="35"/>
+      <c r="T62" s="35"/>
+      <c r="V62" s="35"/>
+      <c r="X62" s="35"/>
+      <c r="Z62" s="35"/>
+      <c r="AG62" s="35"/>
+      <c r="AH62"/>
+      <c r="AI62" s="35"/>
+      <c r="AK62" s="35"/>
+      <c r="AM62" s="35"/>
+      <c r="AO62" s="35"/>
+      <c r="AV62" s="35"/>
+      <c r="AW62"/>
+      <c r="AX62" s="35"/>
+      <c r="AZ62" s="35"/>
+      <c r="BB62" s="35"/>
+      <c r="BD62" s="35"/>
+      <c r="BE62" s="20"/>
+      <c r="BK62" s="35"/>
+      <c r="BL62"/>
+      <c r="BM62" s="35"/>
+      <c r="BO62" s="35"/>
+      <c r="BQ62" s="35"/>
+      <c r="BS62" s="35"/>
+      <c r="BY62"/>
+      <c r="BZ62" s="35"/>
+      <c r="CB62" s="35"/>
+      <c r="CD62" s="35"/>
+      <c r="CF62" s="35"/>
+      <c r="CH62" s="38"/>
       <c r="CI62" s="35"/>
-    </row>
-    <row r="63" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q63" s="35"/>
-      <c r="S63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="W63" s="35"/>
-      <c r="Y63" s="35"/>
-      <c r="AF63" s="35"/>
-      <c r="AG63"/>
-      <c r="AH63" s="35"/>
-      <c r="AJ63" s="35"/>
-      <c r="AL63" s="35"/>
-      <c r="AN63" s="35"/>
-      <c r="AU63" s="35"/>
-      <c r="AV63"/>
-      <c r="AW63" s="35"/>
-      <c r="AY63" s="35"/>
-      <c r="BA63" s="35"/>
-      <c r="BC63" s="35"/>
-      <c r="BD63" s="20"/>
-      <c r="BJ63" s="35"/>
-      <c r="BK63"/>
-      <c r="BL63" s="35"/>
-      <c r="BN63" s="35"/>
-      <c r="BP63" s="35"/>
-      <c r="BR63" s="35"/>
-      <c r="BX63"/>
-      <c r="BY63" s="35"/>
-      <c r="CA63" s="35"/>
-      <c r="CC63" s="35"/>
-      <c r="CE63" s="35"/>
-      <c r="CG63" s="38"/>
-      <c r="CH63" s="35"/>
+      <c r="CJ62" s="35"/>
+    </row>
+    <row r="63" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="X63" s="35"/>
+      <c r="Z63" s="35"/>
+      <c r="AG63" s="35"/>
+      <c r="AH63"/>
+      <c r="AI63" s="35"/>
+      <c r="AK63" s="35"/>
+      <c r="AM63" s="35"/>
+      <c r="AO63" s="35"/>
+      <c r="AV63" s="35"/>
+      <c r="AW63"/>
+      <c r="AX63" s="35"/>
+      <c r="AZ63" s="35"/>
+      <c r="BB63" s="35"/>
+      <c r="BD63" s="35"/>
+      <c r="BE63" s="20"/>
+      <c r="BK63" s="35"/>
+      <c r="BL63"/>
+      <c r="BM63" s="35"/>
+      <c r="BO63" s="35"/>
+      <c r="BQ63" s="35"/>
+      <c r="BS63" s="35"/>
+      <c r="BY63"/>
+      <c r="BZ63" s="35"/>
+      <c r="CB63" s="35"/>
+      <c r="CD63" s="35"/>
+      <c r="CF63" s="35"/>
+      <c r="CH63" s="38"/>
       <c r="CI63" s="35"/>
-    </row>
-    <row r="64" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q64" s="35"/>
-      <c r="S64" s="35"/>
-      <c r="U64" s="35"/>
-      <c r="W64" s="35"/>
-      <c r="Y64" s="35"/>
-      <c r="AF64" s="35"/>
-      <c r="AG64"/>
-      <c r="AH64" s="35"/>
-      <c r="AJ64" s="35"/>
-      <c r="AL64" s="35"/>
-      <c r="AN64" s="35"/>
-      <c r="AU64" s="35"/>
-      <c r="AV64"/>
-      <c r="AW64" s="35"/>
-      <c r="AY64" s="35"/>
-      <c r="BA64" s="35"/>
-      <c r="BC64" s="35"/>
-      <c r="BD64" s="20"/>
-      <c r="BJ64" s="35"/>
-      <c r="BK64"/>
-      <c r="BL64" s="35"/>
-      <c r="BN64" s="35"/>
-      <c r="BP64" s="35"/>
-      <c r="BR64" s="35"/>
-      <c r="BX64"/>
-      <c r="BY64" s="35"/>
-      <c r="CA64" s="35"/>
-      <c r="CC64" s="35"/>
-      <c r="CE64" s="35"/>
-      <c r="CG64" s="38"/>
-      <c r="CH64" s="35"/>
+      <c r="CJ63" s="35"/>
+    </row>
+    <row r="64" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R64" s="35"/>
+      <c r="T64" s="35"/>
+      <c r="V64" s="35"/>
+      <c r="X64" s="35"/>
+      <c r="Z64" s="35"/>
+      <c r="AG64" s="35"/>
+      <c r="AH64"/>
+      <c r="AI64" s="35"/>
+      <c r="AK64" s="35"/>
+      <c r="AM64" s="35"/>
+      <c r="AO64" s="35"/>
+      <c r="AV64" s="35"/>
+      <c r="AW64"/>
+      <c r="AX64" s="35"/>
+      <c r="AZ64" s="35"/>
+      <c r="BB64" s="35"/>
+      <c r="BD64" s="35"/>
+      <c r="BE64" s="20"/>
+      <c r="BK64" s="35"/>
+      <c r="BL64"/>
+      <c r="BM64" s="35"/>
+      <c r="BO64" s="35"/>
+      <c r="BQ64" s="35"/>
+      <c r="BS64" s="35"/>
+      <c r="BY64"/>
+      <c r="BZ64" s="35"/>
+      <c r="CB64" s="35"/>
+      <c r="CD64" s="35"/>
+      <c r="CF64" s="35"/>
+      <c r="CH64" s="38"/>
       <c r="CI64" s="35"/>
-    </row>
-    <row r="65" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q65" s="35"/>
-      <c r="S65" s="35"/>
-      <c r="U65" s="35"/>
-      <c r="W65" s="35"/>
-      <c r="Y65" s="35"/>
-      <c r="AF65" s="35"/>
-      <c r="AG65"/>
-      <c r="AH65" s="35"/>
-      <c r="AJ65" s="35"/>
-      <c r="AL65" s="35"/>
-      <c r="AN65" s="35"/>
-      <c r="AU65" s="35"/>
-      <c r="AV65"/>
-      <c r="AW65" s="35"/>
-      <c r="AY65" s="35"/>
-      <c r="BA65" s="35"/>
-      <c r="BC65" s="35"/>
-      <c r="BD65" s="20"/>
-      <c r="BJ65" s="35"/>
-      <c r="BK65"/>
-      <c r="BL65" s="35"/>
-      <c r="BN65" s="35"/>
-      <c r="BP65" s="35"/>
-      <c r="BR65" s="35"/>
-      <c r="BX65"/>
-      <c r="BY65" s="35"/>
-      <c r="CA65" s="35"/>
-      <c r="CC65" s="35"/>
-      <c r="CE65" s="35"/>
-      <c r="CG65" s="38"/>
-      <c r="CH65" s="35"/>
+      <c r="CJ64" s="35"/>
+    </row>
+    <row r="65" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R65" s="35"/>
+      <c r="T65" s="35"/>
+      <c r="V65" s="35"/>
+      <c r="X65" s="35"/>
+      <c r="Z65" s="35"/>
+      <c r="AG65" s="35"/>
+      <c r="AH65"/>
+      <c r="AI65" s="35"/>
+      <c r="AK65" s="35"/>
+      <c r="AM65" s="35"/>
+      <c r="AO65" s="35"/>
+      <c r="AV65" s="35"/>
+      <c r="AW65"/>
+      <c r="AX65" s="35"/>
+      <c r="AZ65" s="35"/>
+      <c r="BB65" s="35"/>
+      <c r="BD65" s="35"/>
+      <c r="BE65" s="20"/>
+      <c r="BK65" s="35"/>
+      <c r="BL65"/>
+      <c r="BM65" s="35"/>
+      <c r="BO65" s="35"/>
+      <c r="BQ65" s="35"/>
+      <c r="BS65" s="35"/>
+      <c r="BY65"/>
+      <c r="BZ65" s="35"/>
+      <c r="CB65" s="35"/>
+      <c r="CD65" s="35"/>
+      <c r="CF65" s="35"/>
+      <c r="CH65" s="38"/>
       <c r="CI65" s="35"/>
-    </row>
-    <row r="66" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q66" s="35"/>
-      <c r="S66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="W66" s="35"/>
-      <c r="Y66" s="35"/>
-      <c r="AF66" s="35"/>
-      <c r="AG66"/>
-      <c r="AH66" s="35"/>
-      <c r="AJ66" s="35"/>
-      <c r="AL66" s="35"/>
-      <c r="AN66" s="35"/>
-      <c r="AU66" s="35"/>
-      <c r="AV66"/>
-      <c r="AW66" s="35"/>
-      <c r="AY66" s="35"/>
-      <c r="BA66" s="35"/>
-      <c r="BC66" s="35"/>
-      <c r="BD66" s="20"/>
-      <c r="BJ66" s="35"/>
-      <c r="BK66"/>
-      <c r="BL66" s="35"/>
-      <c r="BN66" s="35"/>
-      <c r="BP66" s="35"/>
-      <c r="BR66" s="35"/>
-      <c r="BX66"/>
-      <c r="BY66" s="35"/>
-      <c r="CA66" s="35"/>
-      <c r="CC66" s="35"/>
-      <c r="CE66" s="35"/>
-      <c r="CG66" s="38"/>
-      <c r="CH66" s="35"/>
+      <c r="CJ65" s="35"/>
+    </row>
+    <row r="66" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R66" s="35"/>
+      <c r="T66" s="35"/>
+      <c r="V66" s="35"/>
+      <c r="X66" s="35"/>
+      <c r="Z66" s="35"/>
+      <c r="AG66" s="35"/>
+      <c r="AH66"/>
+      <c r="AI66" s="35"/>
+      <c r="AK66" s="35"/>
+      <c r="AM66" s="35"/>
+      <c r="AO66" s="35"/>
+      <c r="AV66" s="35"/>
+      <c r="AW66"/>
+      <c r="AX66" s="35"/>
+      <c r="AZ66" s="35"/>
+      <c r="BB66" s="35"/>
+      <c r="BD66" s="35"/>
+      <c r="BE66" s="20"/>
+      <c r="BK66" s="35"/>
+      <c r="BL66"/>
+      <c r="BM66" s="35"/>
+      <c r="BO66" s="35"/>
+      <c r="BQ66" s="35"/>
+      <c r="BS66" s="35"/>
+      <c r="BY66"/>
+      <c r="BZ66" s="35"/>
+      <c r="CB66" s="35"/>
+      <c r="CD66" s="35"/>
+      <c r="CF66" s="35"/>
+      <c r="CH66" s="38"/>
       <c r="CI66" s="35"/>
-    </row>
-    <row r="67" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q67" s="35"/>
-      <c r="S67" s="35"/>
-      <c r="U67" s="35"/>
-      <c r="W67" s="35"/>
-      <c r="Y67" s="35"/>
-      <c r="AF67" s="35"/>
-      <c r="AG67"/>
-      <c r="AH67" s="35"/>
-      <c r="AJ67" s="35"/>
-      <c r="AL67" s="35"/>
-      <c r="AN67" s="35"/>
-      <c r="AU67" s="35"/>
-      <c r="AV67"/>
-      <c r="AW67" s="35"/>
-      <c r="AY67" s="35"/>
-      <c r="BA67" s="35"/>
-      <c r="BC67" s="35"/>
-      <c r="BD67" s="20"/>
-      <c r="BJ67" s="35"/>
-      <c r="BK67"/>
-      <c r="BL67" s="35"/>
-      <c r="BN67" s="35"/>
-      <c r="BP67" s="35"/>
-      <c r="BR67" s="35"/>
-      <c r="BX67"/>
-      <c r="BY67" s="35"/>
-      <c r="CA67" s="35"/>
-      <c r="CC67" s="35"/>
-      <c r="CE67" s="35"/>
-      <c r="CG67" s="38"/>
-      <c r="CH67" s="35"/>
+      <c r="CJ66" s="35"/>
+    </row>
+    <row r="67" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R67" s="35"/>
+      <c r="T67" s="35"/>
+      <c r="V67" s="35"/>
+      <c r="X67" s="35"/>
+      <c r="Z67" s="35"/>
+      <c r="AG67" s="35"/>
+      <c r="AH67"/>
+      <c r="AI67" s="35"/>
+      <c r="AK67" s="35"/>
+      <c r="AM67" s="35"/>
+      <c r="AO67" s="35"/>
+      <c r="AV67" s="35"/>
+      <c r="AW67"/>
+      <c r="AX67" s="35"/>
+      <c r="AZ67" s="35"/>
+      <c r="BB67" s="35"/>
+      <c r="BD67" s="35"/>
+      <c r="BE67" s="20"/>
+      <c r="BK67" s="35"/>
+      <c r="BL67"/>
+      <c r="BM67" s="35"/>
+      <c r="BO67" s="35"/>
+      <c r="BQ67" s="35"/>
+      <c r="BS67" s="35"/>
+      <c r="BY67"/>
+      <c r="BZ67" s="35"/>
+      <c r="CB67" s="35"/>
+      <c r="CD67" s="35"/>
+      <c r="CF67" s="35"/>
+      <c r="CH67" s="38"/>
       <c r="CI67" s="35"/>
-    </row>
-    <row r="68" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q68" s="35"/>
-      <c r="S68" s="35"/>
-      <c r="U68" s="35"/>
-      <c r="W68" s="35"/>
-      <c r="Y68" s="35"/>
-      <c r="AF68" s="35"/>
-      <c r="AG68"/>
-      <c r="AH68" s="35"/>
-      <c r="AJ68" s="35"/>
-      <c r="AL68" s="35"/>
-      <c r="AN68" s="35"/>
-      <c r="AU68" s="35"/>
-      <c r="AV68"/>
-      <c r="AW68" s="35"/>
-      <c r="AY68" s="35"/>
-      <c r="BA68" s="35"/>
-      <c r="BC68" s="35"/>
-      <c r="BD68" s="20"/>
-      <c r="BJ68" s="35"/>
-      <c r="BK68"/>
-      <c r="BL68" s="35"/>
-      <c r="BN68" s="35"/>
-      <c r="BP68" s="35"/>
-      <c r="BR68" s="35"/>
-      <c r="BX68"/>
-      <c r="BY68" s="35"/>
-      <c r="CA68" s="35"/>
-      <c r="CC68" s="35"/>
-      <c r="CE68" s="35"/>
-      <c r="CG68" s="38"/>
-      <c r="CH68" s="35"/>
+      <c r="CJ67" s="35"/>
+    </row>
+    <row r="68" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R68" s="35"/>
+      <c r="T68" s="35"/>
+      <c r="V68" s="35"/>
+      <c r="X68" s="35"/>
+      <c r="Z68" s="35"/>
+      <c r="AG68" s="35"/>
+      <c r="AH68"/>
+      <c r="AI68" s="35"/>
+      <c r="AK68" s="35"/>
+      <c r="AM68" s="35"/>
+      <c r="AO68" s="35"/>
+      <c r="AV68" s="35"/>
+      <c r="AW68"/>
+      <c r="AX68" s="35"/>
+      <c r="AZ68" s="35"/>
+      <c r="BB68" s="35"/>
+      <c r="BD68" s="35"/>
+      <c r="BE68" s="20"/>
+      <c r="BK68" s="35"/>
+      <c r="BL68"/>
+      <c r="BM68" s="35"/>
+      <c r="BO68" s="35"/>
+      <c r="BQ68" s="35"/>
+      <c r="BS68" s="35"/>
+      <c r="BY68"/>
+      <c r="BZ68" s="35"/>
+      <c r="CB68" s="35"/>
+      <c r="CD68" s="35"/>
+      <c r="CF68" s="35"/>
+      <c r="CH68" s="38"/>
       <c r="CI68" s="35"/>
-    </row>
-    <row r="69" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q69" s="35"/>
-      <c r="S69" s="35"/>
-      <c r="U69" s="35"/>
-      <c r="W69" s="35"/>
-      <c r="Y69" s="35"/>
-      <c r="AF69" s="35"/>
-      <c r="AG69"/>
-      <c r="AH69" s="35"/>
-      <c r="AJ69" s="35"/>
-      <c r="AL69" s="35"/>
-      <c r="AN69" s="35"/>
-      <c r="AU69" s="35"/>
-      <c r="AV69"/>
-      <c r="AW69" s="35"/>
-      <c r="AY69" s="35"/>
-      <c r="BA69" s="35"/>
-      <c r="BC69" s="35"/>
-      <c r="BD69" s="20"/>
-      <c r="BJ69" s="35"/>
-      <c r="BK69"/>
-      <c r="BL69" s="35"/>
-      <c r="BN69" s="35"/>
-      <c r="BP69" s="35"/>
-      <c r="BR69" s="35"/>
-      <c r="BX69"/>
-      <c r="BY69" s="35"/>
-      <c r="CA69" s="35"/>
-      <c r="CC69" s="35"/>
-      <c r="CE69" s="35"/>
-      <c r="CG69" s="38"/>
-      <c r="CH69" s="35"/>
+      <c r="CJ68" s="35"/>
+    </row>
+    <row r="69" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R69" s="35"/>
+      <c r="T69" s="35"/>
+      <c r="V69" s="35"/>
+      <c r="X69" s="35"/>
+      <c r="Z69" s="35"/>
+      <c r="AG69" s="35"/>
+      <c r="AH69"/>
+      <c r="AI69" s="35"/>
+      <c r="AK69" s="35"/>
+      <c r="AM69" s="35"/>
+      <c r="AO69" s="35"/>
+      <c r="AV69" s="35"/>
+      <c r="AW69"/>
+      <c r="AX69" s="35"/>
+      <c r="AZ69" s="35"/>
+      <c r="BB69" s="35"/>
+      <c r="BD69" s="35"/>
+      <c r="BE69" s="20"/>
+      <c r="BK69" s="35"/>
+      <c r="BL69"/>
+      <c r="BM69" s="35"/>
+      <c r="BO69" s="35"/>
+      <c r="BQ69" s="35"/>
+      <c r="BS69" s="35"/>
+      <c r="BY69"/>
+      <c r="BZ69" s="35"/>
+      <c r="CB69" s="35"/>
+      <c r="CD69" s="35"/>
+      <c r="CF69" s="35"/>
+      <c r="CH69" s="38"/>
       <c r="CI69" s="35"/>
-    </row>
-    <row r="70" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q70" s="35"/>
-      <c r="S70" s="35"/>
-      <c r="U70" s="35"/>
-      <c r="W70" s="35"/>
-      <c r="Y70" s="35"/>
-      <c r="AF70" s="35"/>
-      <c r="AG70"/>
-      <c r="AH70" s="35"/>
-      <c r="AJ70" s="35"/>
-      <c r="AL70" s="35"/>
-      <c r="AN70" s="35"/>
-      <c r="AU70" s="35"/>
-      <c r="AV70"/>
-      <c r="AW70" s="35"/>
-      <c r="AY70" s="35"/>
-      <c r="BA70" s="35"/>
-      <c r="BC70" s="35"/>
-      <c r="BD70" s="20"/>
-      <c r="BJ70" s="35"/>
-      <c r="BK70"/>
-      <c r="BL70" s="35"/>
-      <c r="BN70" s="35"/>
-      <c r="BP70" s="35"/>
-      <c r="BR70" s="35"/>
-      <c r="BX70"/>
-      <c r="BY70" s="35"/>
-      <c r="CA70" s="35"/>
-      <c r="CC70" s="35"/>
-      <c r="CE70" s="35"/>
-      <c r="CG70" s="38"/>
-      <c r="CH70" s="35"/>
+      <c r="CJ69" s="35"/>
+    </row>
+    <row r="70" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R70" s="35"/>
+      <c r="T70" s="35"/>
+      <c r="V70" s="35"/>
+      <c r="X70" s="35"/>
+      <c r="Z70" s="35"/>
+      <c r="AG70" s="35"/>
+      <c r="AH70"/>
+      <c r="AI70" s="35"/>
+      <c r="AK70" s="35"/>
+      <c r="AM70" s="35"/>
+      <c r="AO70" s="35"/>
+      <c r="AV70" s="35"/>
+      <c r="AW70"/>
+      <c r="AX70" s="35"/>
+      <c r="AZ70" s="35"/>
+      <c r="BB70" s="35"/>
+      <c r="BD70" s="35"/>
+      <c r="BE70" s="20"/>
+      <c r="BK70" s="35"/>
+      <c r="BL70"/>
+      <c r="BM70" s="35"/>
+      <c r="BO70" s="35"/>
+      <c r="BQ70" s="35"/>
+      <c r="BS70" s="35"/>
+      <c r="BY70"/>
+      <c r="BZ70" s="35"/>
+      <c r="CB70" s="35"/>
+      <c r="CD70" s="35"/>
+      <c r="CF70" s="35"/>
+      <c r="CH70" s="38"/>
       <c r="CI70" s="35"/>
-    </row>
-    <row r="71" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q71" s="35"/>
-      <c r="S71" s="35"/>
-      <c r="U71" s="35"/>
-      <c r="W71" s="35"/>
-      <c r="Y71" s="35"/>
-      <c r="AF71" s="35"/>
-      <c r="AG71"/>
-      <c r="AH71" s="35"/>
-      <c r="AJ71" s="35"/>
-      <c r="AL71" s="35"/>
-      <c r="AN71" s="35"/>
-      <c r="AU71" s="35"/>
-      <c r="AV71"/>
-      <c r="AW71" s="35"/>
-      <c r="AY71" s="35"/>
-      <c r="BA71" s="35"/>
-      <c r="BC71" s="35"/>
-      <c r="BD71" s="20"/>
-      <c r="BJ71" s="35"/>
-      <c r="BK71"/>
-      <c r="BL71" s="35"/>
-      <c r="BN71" s="35"/>
-      <c r="BP71" s="35"/>
-      <c r="BR71" s="35"/>
-      <c r="BX71"/>
-      <c r="BY71" s="35"/>
-      <c r="CA71" s="35"/>
-      <c r="CC71" s="35"/>
-      <c r="CE71" s="35"/>
-      <c r="CG71" s="38"/>
-      <c r="CH71" s="35"/>
+      <c r="CJ70" s="35"/>
+    </row>
+    <row r="71" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R71" s="35"/>
+      <c r="T71" s="35"/>
+      <c r="V71" s="35"/>
+      <c r="X71" s="35"/>
+      <c r="Z71" s="35"/>
+      <c r="AG71" s="35"/>
+      <c r="AH71"/>
+      <c r="AI71" s="35"/>
+      <c r="AK71" s="35"/>
+      <c r="AM71" s="35"/>
+      <c r="AO71" s="35"/>
+      <c r="AV71" s="35"/>
+      <c r="AW71"/>
+      <c r="AX71" s="35"/>
+      <c r="AZ71" s="35"/>
+      <c r="BB71" s="35"/>
+      <c r="BD71" s="35"/>
+      <c r="BE71" s="20"/>
+      <c r="BK71" s="35"/>
+      <c r="BL71"/>
+      <c r="BM71" s="35"/>
+      <c r="BO71" s="35"/>
+      <c r="BQ71" s="35"/>
+      <c r="BS71" s="35"/>
+      <c r="BY71"/>
+      <c r="BZ71" s="35"/>
+      <c r="CB71" s="35"/>
+      <c r="CD71" s="35"/>
+      <c r="CF71" s="35"/>
+      <c r="CH71" s="38"/>
       <c r="CI71" s="35"/>
-    </row>
-    <row r="72" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q72" s="35"/>
-      <c r="S72" s="35"/>
-      <c r="U72" s="35"/>
-      <c r="W72" s="35"/>
-      <c r="Y72" s="35"/>
-      <c r="AF72" s="35"/>
-      <c r="AG72"/>
-      <c r="AH72" s="35"/>
-      <c r="AJ72" s="35"/>
-      <c r="AL72" s="35"/>
-      <c r="AN72" s="35"/>
-      <c r="AU72" s="35"/>
-      <c r="AV72"/>
-      <c r="AW72" s="35"/>
-      <c r="AY72" s="35"/>
-      <c r="BA72" s="35"/>
-      <c r="BC72" s="35"/>
-      <c r="BD72" s="20"/>
-      <c r="BJ72" s="35"/>
-      <c r="BK72"/>
-      <c r="BL72" s="35"/>
-      <c r="BN72" s="35"/>
-      <c r="BP72" s="35"/>
-      <c r="BR72" s="35"/>
-      <c r="BX72"/>
-      <c r="BY72" s="35"/>
-      <c r="CA72" s="35"/>
-      <c r="CC72" s="35"/>
-      <c r="CE72" s="35"/>
-      <c r="CG72" s="38"/>
-      <c r="CH72" s="35"/>
+      <c r="CJ71" s="35"/>
+    </row>
+    <row r="72" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R72" s="35"/>
+      <c r="T72" s="35"/>
+      <c r="V72" s="35"/>
+      <c r="X72" s="35"/>
+      <c r="Z72" s="35"/>
+      <c r="AG72" s="35"/>
+      <c r="AH72"/>
+      <c r="AI72" s="35"/>
+      <c r="AK72" s="35"/>
+      <c r="AM72" s="35"/>
+      <c r="AO72" s="35"/>
+      <c r="AV72" s="35"/>
+      <c r="AW72"/>
+      <c r="AX72" s="35"/>
+      <c r="AZ72" s="35"/>
+      <c r="BB72" s="35"/>
+      <c r="BD72" s="35"/>
+      <c r="BE72" s="20"/>
+      <c r="BK72" s="35"/>
+      <c r="BL72"/>
+      <c r="BM72" s="35"/>
+      <c r="BO72" s="35"/>
+      <c r="BQ72" s="35"/>
+      <c r="BS72" s="35"/>
+      <c r="BY72"/>
+      <c r="BZ72" s="35"/>
+      <c r="CB72" s="35"/>
+      <c r="CD72" s="35"/>
+      <c r="CF72" s="35"/>
+      <c r="CH72" s="38"/>
       <c r="CI72" s="35"/>
-    </row>
-    <row r="73" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q73" s="35"/>
-      <c r="S73" s="35"/>
-      <c r="U73" s="35"/>
-      <c r="W73" s="35"/>
-      <c r="Y73" s="35"/>
-      <c r="AF73" s="35"/>
-      <c r="AG73"/>
-      <c r="AH73" s="35"/>
-      <c r="AJ73" s="35"/>
-      <c r="AL73" s="35"/>
-      <c r="AN73" s="35"/>
-      <c r="AU73" s="35"/>
-      <c r="AV73"/>
-      <c r="AW73" s="35"/>
-      <c r="AY73" s="35"/>
-      <c r="BA73" s="35"/>
-      <c r="BC73" s="35"/>
-      <c r="BD73" s="20"/>
-      <c r="BJ73" s="35"/>
-      <c r="BK73"/>
-      <c r="BL73" s="35"/>
-      <c r="BN73" s="35"/>
-      <c r="BP73" s="35"/>
-      <c r="BR73" s="35"/>
-      <c r="BX73"/>
-      <c r="BY73" s="35"/>
-      <c r="CA73" s="35"/>
-      <c r="CC73" s="35"/>
-      <c r="CE73" s="35"/>
-      <c r="CG73" s="38"/>
-      <c r="CH73" s="35"/>
+      <c r="CJ72" s="35"/>
+    </row>
+    <row r="73" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R73" s="35"/>
+      <c r="T73" s="35"/>
+      <c r="V73" s="35"/>
+      <c r="X73" s="35"/>
+      <c r="Z73" s="35"/>
+      <c r="AG73" s="35"/>
+      <c r="AH73"/>
+      <c r="AI73" s="35"/>
+      <c r="AK73" s="35"/>
+      <c r="AM73" s="35"/>
+      <c r="AO73" s="35"/>
+      <c r="AV73" s="35"/>
+      <c r="AW73"/>
+      <c r="AX73" s="35"/>
+      <c r="AZ73" s="35"/>
+      <c r="BB73" s="35"/>
+      <c r="BD73" s="35"/>
+      <c r="BE73" s="20"/>
+      <c r="BK73" s="35"/>
+      <c r="BL73"/>
+      <c r="BM73" s="35"/>
+      <c r="BO73" s="35"/>
+      <c r="BQ73" s="35"/>
+      <c r="BS73" s="35"/>
+      <c r="BY73"/>
+      <c r="BZ73" s="35"/>
+      <c r="CB73" s="35"/>
+      <c r="CD73" s="35"/>
+      <c r="CF73" s="35"/>
+      <c r="CH73" s="38"/>
       <c r="CI73" s="35"/>
-    </row>
-    <row r="74" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q74" s="35"/>
-      <c r="S74" s="35"/>
-      <c r="U74" s="35"/>
-      <c r="W74" s="35"/>
-      <c r="Y74" s="35"/>
-      <c r="AF74" s="35"/>
-      <c r="AG74"/>
-      <c r="AH74" s="35"/>
-      <c r="AJ74" s="35"/>
-      <c r="AL74" s="35"/>
-      <c r="AN74" s="35"/>
-      <c r="AU74" s="35"/>
-      <c r="AV74"/>
-      <c r="AW74" s="35"/>
-      <c r="AY74" s="35"/>
-      <c r="BA74" s="35"/>
-      <c r="BC74" s="35"/>
-      <c r="BD74" s="20"/>
-      <c r="BJ74" s="35"/>
-      <c r="BK74"/>
-      <c r="BL74" s="35"/>
-      <c r="BN74" s="35"/>
-      <c r="BP74" s="35"/>
-      <c r="BR74" s="35"/>
-      <c r="BX74"/>
-      <c r="BY74" s="35"/>
-      <c r="CA74" s="35"/>
-      <c r="CC74" s="35"/>
-      <c r="CE74" s="35"/>
-      <c r="CG74" s="38"/>
-      <c r="CH74" s="35"/>
+      <c r="CJ73" s="35"/>
+    </row>
+    <row r="74" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R74" s="35"/>
+      <c r="T74" s="35"/>
+      <c r="V74" s="35"/>
+      <c r="X74" s="35"/>
+      <c r="Z74" s="35"/>
+      <c r="AG74" s="35"/>
+      <c r="AH74"/>
+      <c r="AI74" s="35"/>
+      <c r="AK74" s="35"/>
+      <c r="AM74" s="35"/>
+      <c r="AO74" s="35"/>
+      <c r="AV74" s="35"/>
+      <c r="AW74"/>
+      <c r="AX74" s="35"/>
+      <c r="AZ74" s="35"/>
+      <c r="BB74" s="35"/>
+      <c r="BD74" s="35"/>
+      <c r="BE74" s="20"/>
+      <c r="BK74" s="35"/>
+      <c r="BL74"/>
+      <c r="BM74" s="35"/>
+      <c r="BO74" s="35"/>
+      <c r="BQ74" s="35"/>
+      <c r="BS74" s="35"/>
+      <c r="BY74"/>
+      <c r="BZ74" s="35"/>
+      <c r="CB74" s="35"/>
+      <c r="CD74" s="35"/>
+      <c r="CF74" s="35"/>
+      <c r="CH74" s="38"/>
       <c r="CI74" s="35"/>
-    </row>
-    <row r="75" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q75" s="35"/>
-      <c r="S75" s="35"/>
-      <c r="U75" s="35"/>
-      <c r="W75" s="35"/>
-      <c r="Y75" s="35"/>
-      <c r="AF75" s="35"/>
-      <c r="AG75"/>
-      <c r="AH75" s="35"/>
-      <c r="AJ75" s="35"/>
-      <c r="AL75" s="35"/>
-      <c r="AN75" s="35"/>
-      <c r="AU75" s="35"/>
-      <c r="AV75"/>
-      <c r="AW75" s="35"/>
-      <c r="AY75" s="35"/>
-      <c r="BA75" s="35"/>
-      <c r="BC75" s="35"/>
-      <c r="BD75" s="20"/>
-      <c r="BJ75" s="35"/>
-      <c r="BK75"/>
-      <c r="BL75" s="35"/>
-      <c r="BN75" s="35"/>
-      <c r="BP75" s="35"/>
-      <c r="BR75" s="35"/>
-      <c r="BX75"/>
-      <c r="BY75" s="35"/>
-      <c r="CA75" s="35"/>
-      <c r="CC75" s="35"/>
-      <c r="CE75" s="35"/>
-      <c r="CG75" s="38"/>
-      <c r="CH75" s="35"/>
+      <c r="CJ74" s="35"/>
+    </row>
+    <row r="75" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R75" s="35"/>
+      <c r="T75" s="35"/>
+      <c r="V75" s="35"/>
+      <c r="X75" s="35"/>
+      <c r="Z75" s="35"/>
+      <c r="AG75" s="35"/>
+      <c r="AH75"/>
+      <c r="AI75" s="35"/>
+      <c r="AK75" s="35"/>
+      <c r="AM75" s="35"/>
+      <c r="AO75" s="35"/>
+      <c r="AV75" s="35"/>
+      <c r="AW75"/>
+      <c r="AX75" s="35"/>
+      <c r="AZ75" s="35"/>
+      <c r="BB75" s="35"/>
+      <c r="BD75" s="35"/>
+      <c r="BE75" s="20"/>
+      <c r="BK75" s="35"/>
+      <c r="BL75"/>
+      <c r="BM75" s="35"/>
+      <c r="BO75" s="35"/>
+      <c r="BQ75" s="35"/>
+      <c r="BS75" s="35"/>
+      <c r="BY75"/>
+      <c r="BZ75" s="35"/>
+      <c r="CB75" s="35"/>
+      <c r="CD75" s="35"/>
+      <c r="CF75" s="35"/>
+      <c r="CH75" s="38"/>
       <c r="CI75" s="35"/>
-    </row>
-    <row r="76" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q76" s="35"/>
-      <c r="S76" s="35"/>
-      <c r="U76" s="35"/>
-      <c r="W76" s="35"/>
-      <c r="Y76" s="35"/>
-      <c r="AF76" s="35"/>
-      <c r="AG76"/>
-      <c r="AH76" s="35"/>
-      <c r="AJ76" s="35"/>
-      <c r="AL76" s="35"/>
-      <c r="AN76" s="35"/>
-      <c r="AU76" s="35"/>
-      <c r="AV76"/>
-      <c r="AW76" s="35"/>
-      <c r="AY76" s="35"/>
-      <c r="BA76" s="35"/>
-      <c r="BC76" s="35"/>
-      <c r="BD76" s="20"/>
-      <c r="BJ76" s="35"/>
-      <c r="BK76"/>
-      <c r="BL76" s="35"/>
-      <c r="BN76" s="35"/>
-      <c r="BP76" s="35"/>
-      <c r="BR76" s="35"/>
-      <c r="BX76"/>
-      <c r="BY76" s="35"/>
-      <c r="CA76" s="35"/>
-      <c r="CC76" s="35"/>
-      <c r="CE76" s="35"/>
-      <c r="CG76" s="38"/>
-      <c r="CH76" s="35"/>
+      <c r="CJ75" s="35"/>
+    </row>
+    <row r="76" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R76" s="35"/>
+      <c r="T76" s="35"/>
+      <c r="V76" s="35"/>
+      <c r="X76" s="35"/>
+      <c r="Z76" s="35"/>
+      <c r="AG76" s="35"/>
+      <c r="AH76"/>
+      <c r="AI76" s="35"/>
+      <c r="AK76" s="35"/>
+      <c r="AM76" s="35"/>
+      <c r="AO76" s="35"/>
+      <c r="AV76" s="35"/>
+      <c r="AW76"/>
+      <c r="AX76" s="35"/>
+      <c r="AZ76" s="35"/>
+      <c r="BB76" s="35"/>
+      <c r="BD76" s="35"/>
+      <c r="BE76" s="20"/>
+      <c r="BK76" s="35"/>
+      <c r="BL76"/>
+      <c r="BM76" s="35"/>
+      <c r="BO76" s="35"/>
+      <c r="BQ76" s="35"/>
+      <c r="BS76" s="35"/>
+      <c r="BY76"/>
+      <c r="BZ76" s="35"/>
+      <c r="CB76" s="35"/>
+      <c r="CD76" s="35"/>
+      <c r="CF76" s="35"/>
+      <c r="CH76" s="38"/>
       <c r="CI76" s="35"/>
-    </row>
-    <row r="77" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q77" s="35"/>
-      <c r="S77" s="35"/>
-      <c r="U77" s="35"/>
-      <c r="W77" s="35"/>
-      <c r="Y77" s="35"/>
-      <c r="AF77" s="35"/>
-      <c r="AG77"/>
-      <c r="AH77" s="35"/>
-      <c r="AJ77" s="35"/>
-      <c r="AL77" s="35"/>
-      <c r="AN77" s="35"/>
-      <c r="AU77" s="35"/>
-      <c r="AV77"/>
-      <c r="AW77" s="35"/>
-      <c r="AY77" s="35"/>
-      <c r="BA77" s="35"/>
-      <c r="BC77" s="35"/>
-      <c r="BD77" s="20"/>
-      <c r="BJ77" s="35"/>
-      <c r="BK77"/>
-      <c r="BL77" s="35"/>
-      <c r="BN77" s="35"/>
-      <c r="BP77" s="35"/>
-      <c r="BR77" s="35"/>
-      <c r="BX77"/>
-      <c r="BY77" s="35"/>
-      <c r="CA77" s="35"/>
-      <c r="CC77" s="35"/>
-      <c r="CE77" s="35"/>
-      <c r="CG77" s="38"/>
-      <c r="CH77" s="35"/>
+      <c r="CJ76" s="35"/>
+    </row>
+    <row r="77" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R77" s="35"/>
+      <c r="T77" s="35"/>
+      <c r="V77" s="35"/>
+      <c r="X77" s="35"/>
+      <c r="Z77" s="35"/>
+      <c r="AG77" s="35"/>
+      <c r="AH77"/>
+      <c r="AI77" s="35"/>
+      <c r="AK77" s="35"/>
+      <c r="AM77" s="35"/>
+      <c r="AO77" s="35"/>
+      <c r="AV77" s="35"/>
+      <c r="AW77"/>
+      <c r="AX77" s="35"/>
+      <c r="AZ77" s="35"/>
+      <c r="BB77" s="35"/>
+      <c r="BD77" s="35"/>
+      <c r="BE77" s="20"/>
+      <c r="BK77" s="35"/>
+      <c r="BL77"/>
+      <c r="BM77" s="35"/>
+      <c r="BO77" s="35"/>
+      <c r="BQ77" s="35"/>
+      <c r="BS77" s="35"/>
+      <c r="BY77"/>
+      <c r="BZ77" s="35"/>
+      <c r="CB77" s="35"/>
+      <c r="CD77" s="35"/>
+      <c r="CF77" s="35"/>
+      <c r="CH77" s="38"/>
       <c r="CI77" s="35"/>
-    </row>
-    <row r="78" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q78" s="35"/>
-      <c r="S78" s="35"/>
-      <c r="U78" s="35"/>
-      <c r="W78" s="35"/>
-      <c r="Y78" s="35"/>
-      <c r="AF78" s="35"/>
-      <c r="AG78"/>
-      <c r="AH78" s="35"/>
-      <c r="AJ78" s="35"/>
-      <c r="AL78" s="35"/>
-      <c r="AN78" s="35"/>
-      <c r="AU78" s="35"/>
-      <c r="AV78"/>
-      <c r="AW78" s="35"/>
-      <c r="AY78" s="35"/>
-      <c r="BA78" s="35"/>
-      <c r="BC78" s="35"/>
-      <c r="BD78" s="20"/>
-      <c r="BJ78" s="35"/>
-      <c r="BK78"/>
-      <c r="BL78" s="35"/>
-      <c r="BN78" s="35"/>
-      <c r="BP78" s="35"/>
-      <c r="BR78" s="35"/>
-      <c r="BX78"/>
-      <c r="BY78" s="35"/>
-      <c r="CA78" s="35"/>
-      <c r="CC78" s="35"/>
-      <c r="CE78" s="35"/>
-      <c r="CG78" s="38"/>
-      <c r="CH78" s="35"/>
+      <c r="CJ77" s="35"/>
+    </row>
+    <row r="78" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R78" s="35"/>
+      <c r="T78" s="35"/>
+      <c r="V78" s="35"/>
+      <c r="X78" s="35"/>
+      <c r="Z78" s="35"/>
+      <c r="AG78" s="35"/>
+      <c r="AH78"/>
+      <c r="AI78" s="35"/>
+      <c r="AK78" s="35"/>
+      <c r="AM78" s="35"/>
+      <c r="AO78" s="35"/>
+      <c r="AV78" s="35"/>
+      <c r="AW78"/>
+      <c r="AX78" s="35"/>
+      <c r="AZ78" s="35"/>
+      <c r="BB78" s="35"/>
+      <c r="BD78" s="35"/>
+      <c r="BE78" s="20"/>
+      <c r="BK78" s="35"/>
+      <c r="BL78"/>
+      <c r="BM78" s="35"/>
+      <c r="BO78" s="35"/>
+      <c r="BQ78" s="35"/>
+      <c r="BS78" s="35"/>
+      <c r="BY78"/>
+      <c r="BZ78" s="35"/>
+      <c r="CB78" s="35"/>
+      <c r="CD78" s="35"/>
+      <c r="CF78" s="35"/>
+      <c r="CH78" s="38"/>
       <c r="CI78" s="35"/>
-    </row>
-    <row r="79" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q79" s="35"/>
-      <c r="S79" s="35"/>
-      <c r="U79" s="35"/>
-      <c r="W79" s="35"/>
-      <c r="Y79" s="35"/>
-      <c r="AF79" s="35"/>
-      <c r="AG79"/>
-      <c r="AH79" s="35"/>
-      <c r="AJ79" s="35"/>
-      <c r="AL79" s="35"/>
-      <c r="AN79" s="35"/>
-      <c r="AU79" s="35"/>
-      <c r="AV79"/>
-      <c r="AW79" s="35"/>
-      <c r="AY79" s="35"/>
-      <c r="BA79" s="35"/>
-      <c r="BC79" s="35"/>
-      <c r="BD79" s="20"/>
-      <c r="BJ79" s="35"/>
-      <c r="BK79"/>
-      <c r="BL79" s="35"/>
-      <c r="BN79" s="35"/>
-      <c r="BP79" s="35"/>
-      <c r="BR79" s="35"/>
-      <c r="BX79"/>
-      <c r="BY79" s="35"/>
-      <c r="CA79" s="35"/>
-      <c r="CC79" s="35"/>
-      <c r="CE79" s="35"/>
-      <c r="CG79" s="38"/>
-      <c r="CH79" s="35"/>
+      <c r="CJ78" s="35"/>
+    </row>
+    <row r="79" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R79" s="35"/>
+      <c r="T79" s="35"/>
+      <c r="V79" s="35"/>
+      <c r="X79" s="35"/>
+      <c r="Z79" s="35"/>
+      <c r="AG79" s="35"/>
+      <c r="AH79"/>
+      <c r="AI79" s="35"/>
+      <c r="AK79" s="35"/>
+      <c r="AM79" s="35"/>
+      <c r="AO79" s="35"/>
+      <c r="AV79" s="35"/>
+      <c r="AW79"/>
+      <c r="AX79" s="35"/>
+      <c r="AZ79" s="35"/>
+      <c r="BB79" s="35"/>
+      <c r="BD79" s="35"/>
+      <c r="BE79" s="20"/>
+      <c r="BK79" s="35"/>
+      <c r="BL79"/>
+      <c r="BM79" s="35"/>
+      <c r="BO79" s="35"/>
+      <c r="BQ79" s="35"/>
+      <c r="BS79" s="35"/>
+      <c r="BY79"/>
+      <c r="BZ79" s="35"/>
+      <c r="CB79" s="35"/>
+      <c r="CD79" s="35"/>
+      <c r="CF79" s="35"/>
+      <c r="CH79" s="38"/>
       <c r="CI79" s="35"/>
-    </row>
-    <row r="80" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q80" s="35"/>
-      <c r="S80" s="35"/>
-      <c r="U80" s="35"/>
-      <c r="W80" s="35"/>
-      <c r="Y80" s="35"/>
-      <c r="AF80" s="35"/>
-      <c r="AG80"/>
-      <c r="AH80" s="35"/>
-      <c r="AJ80" s="35"/>
-      <c r="AL80" s="35"/>
-      <c r="AN80" s="35"/>
-      <c r="AU80" s="35"/>
-      <c r="AV80"/>
-      <c r="AW80" s="35"/>
-      <c r="AY80" s="35"/>
-      <c r="BA80" s="35"/>
-      <c r="BC80" s="35"/>
-      <c r="BD80" s="20"/>
-      <c r="BJ80" s="35"/>
-      <c r="BK80"/>
-      <c r="BL80" s="35"/>
-      <c r="BN80" s="35"/>
-      <c r="BP80" s="35"/>
-      <c r="BR80" s="35"/>
-      <c r="BX80"/>
-      <c r="BY80" s="35"/>
-      <c r="CA80" s="35"/>
-      <c r="CC80" s="35"/>
-      <c r="CE80" s="35"/>
-      <c r="CG80" s="38"/>
-      <c r="CH80" s="35"/>
+      <c r="CJ79" s="35"/>
+    </row>
+    <row r="80" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R80" s="35"/>
+      <c r="T80" s="35"/>
+      <c r="V80" s="35"/>
+      <c r="X80" s="35"/>
+      <c r="Z80" s="35"/>
+      <c r="AG80" s="35"/>
+      <c r="AH80"/>
+      <c r="AI80" s="35"/>
+      <c r="AK80" s="35"/>
+      <c r="AM80" s="35"/>
+      <c r="AO80" s="35"/>
+      <c r="AV80" s="35"/>
+      <c r="AW80"/>
+      <c r="AX80" s="35"/>
+      <c r="AZ80" s="35"/>
+      <c r="BB80" s="35"/>
+      <c r="BD80" s="35"/>
+      <c r="BE80" s="20"/>
+      <c r="BK80" s="35"/>
+      <c r="BL80"/>
+      <c r="BM80" s="35"/>
+      <c r="BO80" s="35"/>
+      <c r="BQ80" s="35"/>
+      <c r="BS80" s="35"/>
+      <c r="BY80"/>
+      <c r="BZ80" s="35"/>
+      <c r="CB80" s="35"/>
+      <c r="CD80" s="35"/>
+      <c r="CF80" s="35"/>
+      <c r="CH80" s="38"/>
       <c r="CI80" s="35"/>
-    </row>
-    <row r="81" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q81" s="35"/>
-      <c r="S81" s="35"/>
-      <c r="U81" s="35"/>
-      <c r="W81" s="35"/>
-      <c r="Y81" s="35"/>
-      <c r="AF81" s="35"/>
-      <c r="AG81"/>
-      <c r="AH81" s="35"/>
-      <c r="AJ81" s="35"/>
-      <c r="AL81" s="35"/>
-      <c r="AN81" s="35"/>
-      <c r="AU81" s="35"/>
-      <c r="AV81"/>
-      <c r="AW81" s="35"/>
-      <c r="AY81" s="35"/>
-      <c r="BA81" s="35"/>
-      <c r="BC81" s="35"/>
-      <c r="BD81" s="20"/>
-      <c r="BJ81" s="35"/>
-      <c r="BK81"/>
-      <c r="BL81" s="35"/>
-      <c r="BN81" s="35"/>
-      <c r="BP81" s="35"/>
-      <c r="BR81" s="35"/>
-      <c r="BX81"/>
-      <c r="BY81" s="35"/>
-      <c r="CA81" s="35"/>
-      <c r="CC81" s="35"/>
-      <c r="CE81" s="35"/>
-      <c r="CG81" s="38"/>
-      <c r="CH81" s="35"/>
+      <c r="CJ80" s="35"/>
+    </row>
+    <row r="81" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R81" s="35"/>
+      <c r="T81" s="35"/>
+      <c r="V81" s="35"/>
+      <c r="X81" s="35"/>
+      <c r="Z81" s="35"/>
+      <c r="AG81" s="35"/>
+      <c r="AH81"/>
+      <c r="AI81" s="35"/>
+      <c r="AK81" s="35"/>
+      <c r="AM81" s="35"/>
+      <c r="AO81" s="35"/>
+      <c r="AV81" s="35"/>
+      <c r="AW81"/>
+      <c r="AX81" s="35"/>
+      <c r="AZ81" s="35"/>
+      <c r="BB81" s="35"/>
+      <c r="BD81" s="35"/>
+      <c r="BE81" s="20"/>
+      <c r="BK81" s="35"/>
+      <c r="BL81"/>
+      <c r="BM81" s="35"/>
+      <c r="BO81" s="35"/>
+      <c r="BQ81" s="35"/>
+      <c r="BS81" s="35"/>
+      <c r="BY81"/>
+      <c r="BZ81" s="35"/>
+      <c r="CB81" s="35"/>
+      <c r="CD81" s="35"/>
+      <c r="CF81" s="35"/>
+      <c r="CH81" s="38"/>
       <c r="CI81" s="35"/>
-    </row>
-    <row r="82" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q82" s="35"/>
-      <c r="S82" s="35"/>
-      <c r="U82" s="35"/>
-      <c r="W82" s="35"/>
-      <c r="Y82" s="35"/>
-      <c r="AF82" s="35"/>
-      <c r="AG82"/>
-      <c r="AH82" s="35"/>
-      <c r="AJ82" s="35"/>
-      <c r="AL82" s="35"/>
-      <c r="AN82" s="35"/>
-      <c r="AU82" s="35"/>
-      <c r="AV82"/>
-      <c r="AW82" s="35"/>
-      <c r="AY82" s="35"/>
-      <c r="BA82" s="35"/>
-      <c r="BC82" s="35"/>
-      <c r="BD82" s="20"/>
-      <c r="BJ82" s="35"/>
-      <c r="BK82"/>
-      <c r="BL82" s="35"/>
-      <c r="BN82" s="35"/>
-      <c r="BP82" s="35"/>
-      <c r="BR82" s="35"/>
-      <c r="BX82"/>
-      <c r="BY82" s="35"/>
-      <c r="CA82" s="35"/>
-      <c r="CC82" s="35"/>
-      <c r="CE82" s="35"/>
-      <c r="CG82" s="38"/>
-      <c r="CH82" s="35"/>
+      <c r="CJ81" s="35"/>
+    </row>
+    <row r="82" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R82" s="35"/>
+      <c r="T82" s="35"/>
+      <c r="V82" s="35"/>
+      <c r="X82" s="35"/>
+      <c r="Z82" s="35"/>
+      <c r="AG82" s="35"/>
+      <c r="AH82"/>
+      <c r="AI82" s="35"/>
+      <c r="AK82" s="35"/>
+      <c r="AM82" s="35"/>
+      <c r="AO82" s="35"/>
+      <c r="AV82" s="35"/>
+      <c r="AW82"/>
+      <c r="AX82" s="35"/>
+      <c r="AZ82" s="35"/>
+      <c r="BB82" s="35"/>
+      <c r="BD82" s="35"/>
+      <c r="BE82" s="20"/>
+      <c r="BK82" s="35"/>
+      <c r="BL82"/>
+      <c r="BM82" s="35"/>
+      <c r="BO82" s="35"/>
+      <c r="BQ82" s="35"/>
+      <c r="BS82" s="35"/>
+      <c r="BY82"/>
+      <c r="BZ82" s="35"/>
+      <c r="CB82" s="35"/>
+      <c r="CD82" s="35"/>
+      <c r="CF82" s="35"/>
+      <c r="CH82" s="38"/>
       <c r="CI82" s="35"/>
-    </row>
-    <row r="83" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q83" s="35"/>
-      <c r="S83" s="35"/>
-      <c r="U83" s="35"/>
-      <c r="W83" s="35"/>
-      <c r="Y83" s="35"/>
-      <c r="AF83" s="35"/>
-      <c r="AG83"/>
-      <c r="AH83" s="35"/>
-      <c r="AJ83" s="35"/>
-      <c r="AL83" s="35"/>
-      <c r="AN83" s="35"/>
-      <c r="AU83" s="35"/>
-      <c r="AV83"/>
-      <c r="AW83" s="35"/>
-      <c r="AY83" s="35"/>
-      <c r="BA83" s="35"/>
-      <c r="BC83" s="35"/>
-      <c r="BD83" s="20"/>
-      <c r="BJ83" s="35"/>
-      <c r="BK83"/>
-      <c r="BL83" s="35"/>
-      <c r="BN83" s="35"/>
-      <c r="BP83" s="35"/>
-      <c r="BR83" s="35"/>
-      <c r="BX83"/>
-      <c r="BY83" s="35"/>
-      <c r="CA83" s="35"/>
-      <c r="CC83" s="35"/>
-      <c r="CE83" s="35"/>
-      <c r="CG83" s="38"/>
-      <c r="CH83" s="35"/>
+      <c r="CJ82" s="35"/>
+    </row>
+    <row r="83" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R83" s="35"/>
+      <c r="T83" s="35"/>
+      <c r="V83" s="35"/>
+      <c r="X83" s="35"/>
+      <c r="Z83" s="35"/>
+      <c r="AG83" s="35"/>
+      <c r="AH83"/>
+      <c r="AI83" s="35"/>
+      <c r="AK83" s="35"/>
+      <c r="AM83" s="35"/>
+      <c r="AO83" s="35"/>
+      <c r="AV83" s="35"/>
+      <c r="AW83"/>
+      <c r="AX83" s="35"/>
+      <c r="AZ83" s="35"/>
+      <c r="BB83" s="35"/>
+      <c r="BD83" s="35"/>
+      <c r="BE83" s="20"/>
+      <c r="BK83" s="35"/>
+      <c r="BL83"/>
+      <c r="BM83" s="35"/>
+      <c r="BO83" s="35"/>
+      <c r="BQ83" s="35"/>
+      <c r="BS83" s="35"/>
+      <c r="BY83"/>
+      <c r="BZ83" s="35"/>
+      <c r="CB83" s="35"/>
+      <c r="CD83" s="35"/>
+      <c r="CF83" s="35"/>
+      <c r="CH83" s="38"/>
       <c r="CI83" s="35"/>
-    </row>
-    <row r="84" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q84" s="35"/>
-      <c r="S84" s="35"/>
-      <c r="U84" s="35"/>
-      <c r="W84" s="35"/>
-      <c r="Y84" s="35"/>
-      <c r="AF84" s="35"/>
-      <c r="AG84"/>
-      <c r="AH84" s="35"/>
-      <c r="AJ84" s="35"/>
-      <c r="AL84" s="35"/>
-      <c r="AN84" s="35"/>
-      <c r="AU84" s="35"/>
-      <c r="AV84"/>
-      <c r="AW84" s="35"/>
-      <c r="AY84" s="35"/>
-      <c r="BA84" s="35"/>
-      <c r="BC84" s="35"/>
-      <c r="BD84" s="20"/>
-      <c r="BJ84" s="35"/>
-      <c r="BK84"/>
-      <c r="BL84" s="35"/>
-      <c r="BN84" s="35"/>
-      <c r="BP84" s="35"/>
-      <c r="BR84" s="35"/>
-      <c r="BX84"/>
-      <c r="BY84" s="35"/>
-      <c r="CA84" s="35"/>
-      <c r="CC84" s="35"/>
-      <c r="CE84" s="35"/>
-      <c r="CG84" s="38"/>
-      <c r="CH84" s="35"/>
+      <c r="CJ83" s="35"/>
+    </row>
+    <row r="84" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R84" s="35"/>
+      <c r="T84" s="35"/>
+      <c r="V84" s="35"/>
+      <c r="X84" s="35"/>
+      <c r="Z84" s="35"/>
+      <c r="AG84" s="35"/>
+      <c r="AH84"/>
+      <c r="AI84" s="35"/>
+      <c r="AK84" s="35"/>
+      <c r="AM84" s="35"/>
+      <c r="AO84" s="35"/>
+      <c r="AV84" s="35"/>
+      <c r="AW84"/>
+      <c r="AX84" s="35"/>
+      <c r="AZ84" s="35"/>
+      <c r="BB84" s="35"/>
+      <c r="BD84" s="35"/>
+      <c r="BE84" s="20"/>
+      <c r="BK84" s="35"/>
+      <c r="BL84"/>
+      <c r="BM84" s="35"/>
+      <c r="BO84" s="35"/>
+      <c r="BQ84" s="35"/>
+      <c r="BS84" s="35"/>
+      <c r="BY84"/>
+      <c r="BZ84" s="35"/>
+      <c r="CB84" s="35"/>
+      <c r="CD84" s="35"/>
+      <c r="CF84" s="35"/>
+      <c r="CH84" s="38"/>
       <c r="CI84" s="35"/>
-    </row>
-    <row r="85" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q85" s="35"/>
-      <c r="S85" s="35"/>
-      <c r="U85" s="35"/>
-      <c r="W85" s="35"/>
-      <c r="Y85" s="35"/>
-      <c r="AF85" s="35"/>
-      <c r="AG85"/>
-      <c r="AH85" s="35"/>
-      <c r="AJ85" s="35"/>
-      <c r="AL85" s="35"/>
-      <c r="AN85" s="35"/>
-      <c r="AU85" s="35"/>
-      <c r="AV85"/>
-      <c r="AW85" s="35"/>
-      <c r="AY85" s="35"/>
-      <c r="BA85" s="35"/>
-      <c r="BC85" s="35"/>
-      <c r="BD85" s="20"/>
-      <c r="BJ85" s="35"/>
-      <c r="BK85"/>
-      <c r="BL85" s="35"/>
-      <c r="BN85" s="35"/>
-      <c r="BP85" s="35"/>
-      <c r="BR85" s="35"/>
-      <c r="BX85"/>
-      <c r="BY85" s="35"/>
-      <c r="CA85" s="35"/>
-      <c r="CC85" s="35"/>
-      <c r="CE85" s="35"/>
-      <c r="CG85" s="38"/>
-      <c r="CH85" s="35"/>
+      <c r="CJ84" s="35"/>
+    </row>
+    <row r="85" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R85" s="35"/>
+      <c r="T85" s="35"/>
+      <c r="V85" s="35"/>
+      <c r="X85" s="35"/>
+      <c r="Z85" s="35"/>
+      <c r="AG85" s="35"/>
+      <c r="AH85"/>
+      <c r="AI85" s="35"/>
+      <c r="AK85" s="35"/>
+      <c r="AM85" s="35"/>
+      <c r="AO85" s="35"/>
+      <c r="AV85" s="35"/>
+      <c r="AW85"/>
+      <c r="AX85" s="35"/>
+      <c r="AZ85" s="35"/>
+      <c r="BB85" s="35"/>
+      <c r="BD85" s="35"/>
+      <c r="BE85" s="20"/>
+      <c r="BK85" s="35"/>
+      <c r="BL85"/>
+      <c r="BM85" s="35"/>
+      <c r="BO85" s="35"/>
+      <c r="BQ85" s="35"/>
+      <c r="BS85" s="35"/>
+      <c r="BY85"/>
+      <c r="BZ85" s="35"/>
+      <c r="CB85" s="35"/>
+      <c r="CD85" s="35"/>
+      <c r="CF85" s="35"/>
+      <c r="CH85" s="38"/>
       <c r="CI85" s="35"/>
-    </row>
-    <row r="86" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q86" s="35"/>
-      <c r="S86" s="35"/>
-      <c r="U86" s="35"/>
-      <c r="W86" s="35"/>
-      <c r="Y86" s="35"/>
-      <c r="AF86" s="35"/>
-      <c r="AG86"/>
-      <c r="AH86" s="35"/>
-      <c r="AJ86" s="35"/>
-      <c r="AL86" s="35"/>
-      <c r="AN86" s="35"/>
-      <c r="AU86" s="35"/>
-      <c r="AV86"/>
-      <c r="AW86" s="35"/>
-      <c r="AY86" s="35"/>
-      <c r="BA86" s="35"/>
-      <c r="BC86" s="35"/>
-      <c r="BD86" s="20"/>
-      <c r="BJ86" s="35"/>
-      <c r="BK86"/>
-      <c r="BL86" s="35"/>
-      <c r="BN86" s="35"/>
-      <c r="BP86" s="35"/>
-      <c r="BR86" s="35"/>
-      <c r="BX86"/>
-      <c r="BY86" s="35"/>
-      <c r="CA86" s="35"/>
-      <c r="CC86" s="35"/>
-      <c r="CE86" s="35"/>
-      <c r="CG86" s="38"/>
-      <c r="CH86" s="35"/>
+      <c r="CJ85" s="35"/>
+    </row>
+    <row r="86" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R86" s="35"/>
+      <c r="T86" s="35"/>
+      <c r="V86" s="35"/>
+      <c r="X86" s="35"/>
+      <c r="Z86" s="35"/>
+      <c r="AG86" s="35"/>
+      <c r="AH86"/>
+      <c r="AI86" s="35"/>
+      <c r="AK86" s="35"/>
+      <c r="AM86" s="35"/>
+      <c r="AO86" s="35"/>
+      <c r="AV86" s="35"/>
+      <c r="AW86"/>
+      <c r="AX86" s="35"/>
+      <c r="AZ86" s="35"/>
+      <c r="BB86" s="35"/>
+      <c r="BD86" s="35"/>
+      <c r="BE86" s="20"/>
+      <c r="BK86" s="35"/>
+      <c r="BL86"/>
+      <c r="BM86" s="35"/>
+      <c r="BO86" s="35"/>
+      <c r="BQ86" s="35"/>
+      <c r="BS86" s="35"/>
+      <c r="BY86"/>
+      <c r="BZ86" s="35"/>
+      <c r="CB86" s="35"/>
+      <c r="CD86" s="35"/>
+      <c r="CF86" s="35"/>
+      <c r="CH86" s="38"/>
       <c r="CI86" s="35"/>
-    </row>
-    <row r="87" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q87" s="35"/>
-      <c r="S87" s="35"/>
-      <c r="U87" s="35"/>
-      <c r="W87" s="35"/>
-      <c r="Y87" s="35"/>
-      <c r="AF87" s="35"/>
-      <c r="AG87"/>
-      <c r="AH87" s="35"/>
-      <c r="AJ87" s="35"/>
-      <c r="AL87" s="35"/>
-      <c r="AN87" s="35"/>
-      <c r="AU87" s="35"/>
-      <c r="AV87"/>
-      <c r="AW87" s="35"/>
-      <c r="AY87" s="35"/>
-      <c r="BA87" s="35"/>
-      <c r="BC87" s="35"/>
-      <c r="BD87" s="20"/>
-      <c r="BJ87" s="35"/>
-      <c r="BK87"/>
-      <c r="BL87" s="35"/>
-      <c r="BN87" s="35"/>
-      <c r="BP87" s="35"/>
-      <c r="BR87" s="35"/>
-      <c r="BX87"/>
-      <c r="BY87" s="35"/>
-      <c r="CA87" s="35"/>
-      <c r="CC87" s="35"/>
-      <c r="CE87" s="35"/>
-      <c r="CG87" s="38"/>
-      <c r="CH87" s="35"/>
+      <c r="CJ86" s="35"/>
+    </row>
+    <row r="87" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R87" s="35"/>
+      <c r="T87" s="35"/>
+      <c r="V87" s="35"/>
+      <c r="X87" s="35"/>
+      <c r="Z87" s="35"/>
+      <c r="AG87" s="35"/>
+      <c r="AH87"/>
+      <c r="AI87" s="35"/>
+      <c r="AK87" s="35"/>
+      <c r="AM87" s="35"/>
+      <c r="AO87" s="35"/>
+      <c r="AV87" s="35"/>
+      <c r="AW87"/>
+      <c r="AX87" s="35"/>
+      <c r="AZ87" s="35"/>
+      <c r="BB87" s="35"/>
+      <c r="BD87" s="35"/>
+      <c r="BE87" s="20"/>
+      <c r="BK87" s="35"/>
+      <c r="BL87"/>
+      <c r="BM87" s="35"/>
+      <c r="BO87" s="35"/>
+      <c r="BQ87" s="35"/>
+      <c r="BS87" s="35"/>
+      <c r="BY87"/>
+      <c r="BZ87" s="35"/>
+      <c r="CB87" s="35"/>
+      <c r="CD87" s="35"/>
+      <c r="CF87" s="35"/>
+      <c r="CH87" s="38"/>
       <c r="CI87" s="35"/>
-    </row>
-    <row r="88" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q88" s="35"/>
-      <c r="S88" s="35"/>
-      <c r="U88" s="35"/>
-      <c r="W88" s="35"/>
-      <c r="Y88" s="35"/>
-      <c r="AF88" s="35"/>
-      <c r="AG88"/>
-      <c r="AH88" s="35"/>
-      <c r="AJ88" s="35"/>
-      <c r="AL88" s="35"/>
-      <c r="AN88" s="35"/>
-      <c r="AU88" s="35"/>
-      <c r="AV88"/>
-      <c r="AW88" s="35"/>
-      <c r="AY88" s="35"/>
-      <c r="BA88" s="35"/>
-      <c r="BC88" s="35"/>
-      <c r="BD88" s="20"/>
-      <c r="BJ88" s="35"/>
-      <c r="BK88"/>
-      <c r="BL88" s="35"/>
-      <c r="BN88" s="35"/>
-      <c r="BP88" s="35"/>
-      <c r="BR88" s="35"/>
-      <c r="BX88"/>
-      <c r="BY88" s="35"/>
-      <c r="CA88" s="35"/>
-      <c r="CC88" s="35"/>
-      <c r="CE88" s="35"/>
-      <c r="CG88" s="38"/>
-      <c r="CH88" s="35"/>
+      <c r="CJ87" s="35"/>
+    </row>
+    <row r="88" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R88" s="35"/>
+      <c r="T88" s="35"/>
+      <c r="V88" s="35"/>
+      <c r="X88" s="35"/>
+      <c r="Z88" s="35"/>
+      <c r="AG88" s="35"/>
+      <c r="AH88"/>
+      <c r="AI88" s="35"/>
+      <c r="AK88" s="35"/>
+      <c r="AM88" s="35"/>
+      <c r="AO88" s="35"/>
+      <c r="AV88" s="35"/>
+      <c r="AW88"/>
+      <c r="AX88" s="35"/>
+      <c r="AZ88" s="35"/>
+      <c r="BB88" s="35"/>
+      <c r="BD88" s="35"/>
+      <c r="BE88" s="20"/>
+      <c r="BK88" s="35"/>
+      <c r="BL88"/>
+      <c r="BM88" s="35"/>
+      <c r="BO88" s="35"/>
+      <c r="BQ88" s="35"/>
+      <c r="BS88" s="35"/>
+      <c r="BY88"/>
+      <c r="BZ88" s="35"/>
+      <c r="CB88" s="35"/>
+      <c r="CD88" s="35"/>
+      <c r="CF88" s="35"/>
+      <c r="CH88" s="38"/>
       <c r="CI88" s="35"/>
-    </row>
-    <row r="89" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q89" s="35"/>
-      <c r="S89" s="35"/>
-      <c r="U89" s="35"/>
-      <c r="W89" s="35"/>
-      <c r="Y89" s="35"/>
-      <c r="AF89" s="35"/>
-      <c r="AG89"/>
-      <c r="AH89" s="35"/>
-      <c r="AJ89" s="35"/>
-      <c r="AL89" s="35"/>
-      <c r="AN89" s="35"/>
-      <c r="AU89" s="35"/>
-      <c r="AV89"/>
-      <c r="AW89" s="35"/>
-      <c r="AY89" s="35"/>
-      <c r="BA89" s="35"/>
-      <c r="BC89" s="35"/>
-      <c r="BD89" s="20"/>
-      <c r="BJ89" s="35"/>
-      <c r="BK89"/>
-      <c r="BL89" s="35"/>
-      <c r="BN89" s="35"/>
-      <c r="BP89" s="35"/>
-      <c r="BR89" s="35"/>
-      <c r="BX89"/>
-      <c r="BY89" s="35"/>
-      <c r="CA89" s="35"/>
-      <c r="CC89" s="35"/>
-      <c r="CE89" s="35"/>
-      <c r="CG89" s="38"/>
-      <c r="CH89" s="35"/>
+      <c r="CJ88" s="35"/>
+    </row>
+    <row r="89" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R89" s="35"/>
+      <c r="T89" s="35"/>
+      <c r="V89" s="35"/>
+      <c r="X89" s="35"/>
+      <c r="Z89" s="35"/>
+      <c r="AG89" s="35"/>
+      <c r="AH89"/>
+      <c r="AI89" s="35"/>
+      <c r="AK89" s="35"/>
+      <c r="AM89" s="35"/>
+      <c r="AO89" s="35"/>
+      <c r="AV89" s="35"/>
+      <c r="AW89"/>
+      <c r="AX89" s="35"/>
+      <c r="AZ89" s="35"/>
+      <c r="BB89" s="35"/>
+      <c r="BD89" s="35"/>
+      <c r="BE89" s="20"/>
+      <c r="BK89" s="35"/>
+      <c r="BL89"/>
+      <c r="BM89" s="35"/>
+      <c r="BO89" s="35"/>
+      <c r="BQ89" s="35"/>
+      <c r="BS89" s="35"/>
+      <c r="BY89"/>
+      <c r="BZ89" s="35"/>
+      <c r="CB89" s="35"/>
+      <c r="CD89" s="35"/>
+      <c r="CF89" s="35"/>
+      <c r="CH89" s="38"/>
       <c r="CI89" s="35"/>
-    </row>
-    <row r="90" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q90" s="35"/>
-      <c r="S90" s="35"/>
-      <c r="U90" s="35"/>
-      <c r="W90" s="35"/>
-      <c r="Y90" s="35"/>
-      <c r="AF90" s="35"/>
-      <c r="AG90"/>
-      <c r="AH90" s="35"/>
-      <c r="AJ90" s="35"/>
-      <c r="AL90" s="35"/>
-      <c r="AN90" s="35"/>
-      <c r="AU90" s="35"/>
-      <c r="AV90"/>
-      <c r="AW90" s="35"/>
-      <c r="AY90" s="35"/>
-      <c r="BA90" s="35"/>
-      <c r="BC90" s="35"/>
-      <c r="BD90" s="20"/>
-      <c r="BJ90" s="35"/>
-      <c r="BK90"/>
-      <c r="BL90" s="35"/>
-      <c r="BN90" s="35"/>
-      <c r="BP90" s="35"/>
-      <c r="BR90" s="35"/>
-      <c r="BX90"/>
-      <c r="BY90" s="35"/>
-      <c r="CA90" s="35"/>
-      <c r="CC90" s="35"/>
-      <c r="CE90" s="35"/>
-      <c r="CG90" s="38"/>
-      <c r="CH90" s="35"/>
+      <c r="CJ89" s="35"/>
+    </row>
+    <row r="90" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R90" s="35"/>
+      <c r="T90" s="35"/>
+      <c r="V90" s="35"/>
+      <c r="X90" s="35"/>
+      <c r="Z90" s="35"/>
+      <c r="AG90" s="35"/>
+      <c r="AH90"/>
+      <c r="AI90" s="35"/>
+      <c r="AK90" s="35"/>
+      <c r="AM90" s="35"/>
+      <c r="AO90" s="35"/>
+      <c r="AV90" s="35"/>
+      <c r="AW90"/>
+      <c r="AX90" s="35"/>
+      <c r="AZ90" s="35"/>
+      <c r="BB90" s="35"/>
+      <c r="BD90" s="35"/>
+      <c r="BE90" s="20"/>
+      <c r="BK90" s="35"/>
+      <c r="BL90"/>
+      <c r="BM90" s="35"/>
+      <c r="BO90" s="35"/>
+      <c r="BQ90" s="35"/>
+      <c r="BS90" s="35"/>
+      <c r="BY90"/>
+      <c r="BZ90" s="35"/>
+      <c r="CB90" s="35"/>
+      <c r="CD90" s="35"/>
+      <c r="CF90" s="35"/>
+      <c r="CH90" s="38"/>
       <c r="CI90" s="35"/>
-    </row>
-    <row r="91" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q91" s="35"/>
-      <c r="S91" s="35"/>
-      <c r="U91" s="35"/>
-      <c r="W91" s="35"/>
-      <c r="Y91" s="35"/>
-      <c r="AF91" s="35"/>
-      <c r="AG91"/>
-      <c r="AH91" s="35"/>
-      <c r="AJ91" s="35"/>
-      <c r="AL91" s="35"/>
-      <c r="AN91" s="35"/>
-      <c r="AU91" s="35"/>
-      <c r="AV91"/>
-      <c r="AW91" s="35"/>
-      <c r="AY91" s="35"/>
-      <c r="BA91" s="35"/>
-      <c r="BC91" s="35"/>
-      <c r="BD91" s="20"/>
-      <c r="BJ91" s="35"/>
-      <c r="BK91"/>
-      <c r="BL91" s="35"/>
-      <c r="BN91" s="35"/>
-      <c r="BP91" s="35"/>
-      <c r="BR91" s="35"/>
-      <c r="BX91"/>
-      <c r="BY91" s="35"/>
-      <c r="CA91" s="35"/>
-      <c r="CC91" s="35"/>
-      <c r="CE91" s="35"/>
-      <c r="CG91" s="38"/>
-      <c r="CH91" s="35"/>
+      <c r="CJ90" s="35"/>
+    </row>
+    <row r="91" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R91" s="35"/>
+      <c r="T91" s="35"/>
+      <c r="V91" s="35"/>
+      <c r="X91" s="35"/>
+      <c r="Z91" s="35"/>
+      <c r="AG91" s="35"/>
+      <c r="AH91"/>
+      <c r="AI91" s="35"/>
+      <c r="AK91" s="35"/>
+      <c r="AM91" s="35"/>
+      <c r="AO91" s="35"/>
+      <c r="AV91" s="35"/>
+      <c r="AW91"/>
+      <c r="AX91" s="35"/>
+      <c r="AZ91" s="35"/>
+      <c r="BB91" s="35"/>
+      <c r="BD91" s="35"/>
+      <c r="BE91" s="20"/>
+      <c r="BK91" s="35"/>
+      <c r="BL91"/>
+      <c r="BM91" s="35"/>
+      <c r="BO91" s="35"/>
+      <c r="BQ91" s="35"/>
+      <c r="BS91" s="35"/>
+      <c r="BY91"/>
+      <c r="BZ91" s="35"/>
+      <c r="CB91" s="35"/>
+      <c r="CD91" s="35"/>
+      <c r="CF91" s="35"/>
+      <c r="CH91" s="38"/>
       <c r="CI91" s="35"/>
-    </row>
-    <row r="92" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q92" s="35"/>
-      <c r="S92" s="35"/>
-      <c r="U92" s="35"/>
-      <c r="W92" s="35"/>
-      <c r="Y92" s="35"/>
-      <c r="AF92" s="35"/>
-      <c r="AG92"/>
-      <c r="AH92" s="35"/>
-      <c r="AJ92" s="35"/>
-      <c r="AL92" s="35"/>
-      <c r="AN92" s="35"/>
-      <c r="AU92" s="35"/>
-      <c r="AV92"/>
-      <c r="AW92" s="35"/>
-      <c r="AY92" s="35"/>
-      <c r="BA92" s="35"/>
-      <c r="BC92" s="35"/>
-      <c r="BD92" s="20"/>
-      <c r="BJ92" s="35"/>
-      <c r="BK92"/>
-      <c r="BL92" s="35"/>
-      <c r="BN92" s="35"/>
-      <c r="BP92" s="35"/>
-      <c r="BR92" s="35"/>
-      <c r="BX92"/>
-      <c r="BY92" s="35"/>
-      <c r="CA92" s="35"/>
-      <c r="CC92" s="35"/>
-      <c r="CE92" s="35"/>
-      <c r="CG92" s="38"/>
-      <c r="CH92" s="35"/>
+      <c r="CJ91" s="35"/>
+    </row>
+    <row r="92" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R92" s="35"/>
+      <c r="T92" s="35"/>
+      <c r="V92" s="35"/>
+      <c r="X92" s="35"/>
+      <c r="Z92" s="35"/>
+      <c r="AG92" s="35"/>
+      <c r="AH92"/>
+      <c r="AI92" s="35"/>
+      <c r="AK92" s="35"/>
+      <c r="AM92" s="35"/>
+      <c r="AO92" s="35"/>
+      <c r="AV92" s="35"/>
+      <c r="AW92"/>
+      <c r="AX92" s="35"/>
+      <c r="AZ92" s="35"/>
+      <c r="BB92" s="35"/>
+      <c r="BD92" s="35"/>
+      <c r="BE92" s="20"/>
+      <c r="BK92" s="35"/>
+      <c r="BL92"/>
+      <c r="BM92" s="35"/>
+      <c r="BO92" s="35"/>
+      <c r="BQ92" s="35"/>
+      <c r="BS92" s="35"/>
+      <c r="BY92"/>
+      <c r="BZ92" s="35"/>
+      <c r="CB92" s="35"/>
+      <c r="CD92" s="35"/>
+      <c r="CF92" s="35"/>
+      <c r="CH92" s="38"/>
       <c r="CI92" s="35"/>
-    </row>
-    <row r="93" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q93" s="35"/>
-      <c r="S93" s="35"/>
-      <c r="U93" s="35"/>
-      <c r="W93" s="35"/>
-      <c r="Y93" s="35"/>
-      <c r="AF93" s="35"/>
-      <c r="AG93"/>
-      <c r="AH93" s="35"/>
-      <c r="AJ93" s="35"/>
-      <c r="AL93" s="35"/>
-      <c r="AN93" s="35"/>
-      <c r="AU93" s="35"/>
-      <c r="AV93"/>
-      <c r="AW93" s="35"/>
-      <c r="AY93" s="35"/>
-      <c r="BA93" s="35"/>
-      <c r="BC93" s="35"/>
-      <c r="BD93" s="20"/>
-      <c r="BJ93" s="35"/>
-      <c r="BK93"/>
-      <c r="BL93" s="35"/>
-      <c r="BN93" s="35"/>
-      <c r="BP93" s="35"/>
-      <c r="BR93" s="35"/>
-      <c r="BX93"/>
-      <c r="BY93" s="35"/>
-      <c r="CA93" s="35"/>
-      <c r="CC93" s="35"/>
-      <c r="CE93" s="35"/>
-      <c r="CG93" s="38"/>
-      <c r="CH93" s="35"/>
+      <c r="CJ92" s="35"/>
+    </row>
+    <row r="93" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R93" s="35"/>
+      <c r="T93" s="35"/>
+      <c r="V93" s="35"/>
+      <c r="X93" s="35"/>
+      <c r="Z93" s="35"/>
+      <c r="AG93" s="35"/>
+      <c r="AH93"/>
+      <c r="AI93" s="35"/>
+      <c r="AK93" s="35"/>
+      <c r="AM93" s="35"/>
+      <c r="AO93" s="35"/>
+      <c r="AV93" s="35"/>
+      <c r="AW93"/>
+      <c r="AX93" s="35"/>
+      <c r="AZ93" s="35"/>
+      <c r="BB93" s="35"/>
+      <c r="BD93" s="35"/>
+      <c r="BE93" s="20"/>
+      <c r="BK93" s="35"/>
+      <c r="BL93"/>
+      <c r="BM93" s="35"/>
+      <c r="BO93" s="35"/>
+      <c r="BQ93" s="35"/>
+      <c r="BS93" s="35"/>
+      <c r="BY93"/>
+      <c r="BZ93" s="35"/>
+      <c r="CB93" s="35"/>
+      <c r="CD93" s="35"/>
+      <c r="CF93" s="35"/>
+      <c r="CH93" s="38"/>
       <c r="CI93" s="35"/>
-    </row>
-    <row r="94" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q94" s="35"/>
-      <c r="S94" s="35"/>
-      <c r="U94" s="35"/>
-      <c r="W94" s="35"/>
-      <c r="Y94" s="35"/>
-      <c r="AF94" s="35"/>
-      <c r="AG94"/>
-      <c r="AH94" s="35"/>
-      <c r="AJ94" s="35"/>
-      <c r="AL94" s="35"/>
-      <c r="AN94" s="35"/>
-      <c r="AU94" s="35"/>
-      <c r="AV94"/>
-      <c r="AW94" s="35"/>
-      <c r="AY94" s="35"/>
-      <c r="BA94" s="35"/>
-      <c r="BC94" s="35"/>
-      <c r="BD94" s="20"/>
-      <c r="BJ94" s="35"/>
-      <c r="BK94"/>
-      <c r="BL94" s="35"/>
-      <c r="BN94" s="35"/>
-      <c r="BP94" s="35"/>
-      <c r="BR94" s="35"/>
-      <c r="BX94"/>
-      <c r="BY94" s="35"/>
-      <c r="CA94" s="35"/>
-      <c r="CC94" s="35"/>
-      <c r="CE94" s="35"/>
-      <c r="CG94" s="38"/>
-      <c r="CH94" s="35"/>
+      <c r="CJ93" s="35"/>
+    </row>
+    <row r="94" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R94" s="35"/>
+      <c r="T94" s="35"/>
+      <c r="V94" s="35"/>
+      <c r="X94" s="35"/>
+      <c r="Z94" s="35"/>
+      <c r="AG94" s="35"/>
+      <c r="AH94"/>
+      <c r="AI94" s="35"/>
+      <c r="AK94" s="35"/>
+      <c r="AM94" s="35"/>
+      <c r="AO94" s="35"/>
+      <c r="AV94" s="35"/>
+      <c r="AW94"/>
+      <c r="AX94" s="35"/>
+      <c r="AZ94" s="35"/>
+      <c r="BB94" s="35"/>
+      <c r="BD94" s="35"/>
+      <c r="BE94" s="20"/>
+      <c r="BK94" s="35"/>
+      <c r="BL94"/>
+      <c r="BM94" s="35"/>
+      <c r="BO94" s="35"/>
+      <c r="BQ94" s="35"/>
+      <c r="BS94" s="35"/>
+      <c r="BY94"/>
+      <c r="BZ94" s="35"/>
+      <c r="CB94" s="35"/>
+      <c r="CD94" s="35"/>
+      <c r="CF94" s="35"/>
+      <c r="CH94" s="38"/>
       <c r="CI94" s="35"/>
-    </row>
-    <row r="95" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q95" s="35"/>
-      <c r="S95" s="35"/>
-      <c r="U95" s="35"/>
-      <c r="W95" s="35"/>
-      <c r="Y95" s="35"/>
-      <c r="AF95" s="35"/>
-      <c r="AG95"/>
-      <c r="AH95" s="35"/>
-      <c r="AJ95" s="35"/>
-      <c r="AL95" s="35"/>
-      <c r="AN95" s="35"/>
-      <c r="AU95" s="35"/>
-      <c r="AV95"/>
-      <c r="AW95" s="35"/>
-      <c r="AY95" s="35"/>
-      <c r="BA95" s="35"/>
-      <c r="BC95" s="35"/>
-      <c r="BD95" s="20"/>
-      <c r="BJ95" s="35"/>
-      <c r="BK95"/>
-      <c r="BL95" s="35"/>
-      <c r="BN95" s="35"/>
-      <c r="BP95" s="35"/>
-      <c r="BR95" s="35"/>
-      <c r="BX95"/>
-      <c r="BY95" s="35"/>
-      <c r="CA95" s="35"/>
-      <c r="CC95" s="35"/>
-      <c r="CE95" s="35"/>
-      <c r="CG95" s="38"/>
-      <c r="CH95" s="35"/>
+      <c r="CJ94" s="35"/>
+    </row>
+    <row r="95" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R95" s="35"/>
+      <c r="T95" s="35"/>
+      <c r="V95" s="35"/>
+      <c r="X95" s="35"/>
+      <c r="Z95" s="35"/>
+      <c r="AG95" s="35"/>
+      <c r="AH95"/>
+      <c r="AI95" s="35"/>
+      <c r="AK95" s="35"/>
+      <c r="AM95" s="35"/>
+      <c r="AO95" s="35"/>
+      <c r="AV95" s="35"/>
+      <c r="AW95"/>
+      <c r="AX95" s="35"/>
+      <c r="AZ95" s="35"/>
+      <c r="BB95" s="35"/>
+      <c r="BD95" s="35"/>
+      <c r="BE95" s="20"/>
+      <c r="BK95" s="35"/>
+      <c r="BL95"/>
+      <c r="BM95" s="35"/>
+      <c r="BO95" s="35"/>
+      <c r="BQ95" s="35"/>
+      <c r="BS95" s="35"/>
+      <c r="BY95"/>
+      <c r="BZ95" s="35"/>
+      <c r="CB95" s="35"/>
+      <c r="CD95" s="35"/>
+      <c r="CF95" s="35"/>
+      <c r="CH95" s="38"/>
       <c r="CI95" s="35"/>
-    </row>
-    <row r="96" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q96" s="35"/>
-      <c r="S96" s="35"/>
-      <c r="U96" s="35"/>
-      <c r="W96" s="35"/>
-      <c r="Y96" s="35"/>
-      <c r="AF96" s="35"/>
-      <c r="AG96"/>
-      <c r="AH96" s="35"/>
-      <c r="AJ96" s="35"/>
-      <c r="AL96" s="35"/>
-      <c r="AN96" s="35"/>
-      <c r="AU96" s="35"/>
-      <c r="AV96"/>
-      <c r="AW96" s="35"/>
-      <c r="AY96" s="35"/>
-      <c r="BA96" s="35"/>
-      <c r="BC96" s="35"/>
-      <c r="BD96" s="20"/>
-      <c r="BJ96" s="35"/>
-      <c r="BK96"/>
-      <c r="BL96" s="35"/>
-      <c r="BN96" s="35"/>
-      <c r="BP96" s="35"/>
-      <c r="BR96" s="35"/>
-      <c r="BX96"/>
-      <c r="BY96" s="35"/>
-      <c r="CA96" s="35"/>
-      <c r="CC96" s="35"/>
-      <c r="CE96" s="35"/>
-      <c r="CG96" s="38"/>
-      <c r="CH96" s="35"/>
+      <c r="CJ95" s="35"/>
+    </row>
+    <row r="96" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R96" s="35"/>
+      <c r="T96" s="35"/>
+      <c r="V96" s="35"/>
+      <c r="X96" s="35"/>
+      <c r="Z96" s="35"/>
+      <c r="AG96" s="35"/>
+      <c r="AH96"/>
+      <c r="AI96" s="35"/>
+      <c r="AK96" s="35"/>
+      <c r="AM96" s="35"/>
+      <c r="AO96" s="35"/>
+      <c r="AV96" s="35"/>
+      <c r="AW96"/>
+      <c r="AX96" s="35"/>
+      <c r="AZ96" s="35"/>
+      <c r="BB96" s="35"/>
+      <c r="BD96" s="35"/>
+      <c r="BE96" s="20"/>
+      <c r="BK96" s="35"/>
+      <c r="BL96"/>
+      <c r="BM96" s="35"/>
+      <c r="BO96" s="35"/>
+      <c r="BQ96" s="35"/>
+      <c r="BS96" s="35"/>
+      <c r="BY96"/>
+      <c r="BZ96" s="35"/>
+      <c r="CB96" s="35"/>
+      <c r="CD96" s="35"/>
+      <c r="CF96" s="35"/>
+      <c r="CH96" s="38"/>
       <c r="CI96" s="35"/>
-    </row>
-    <row r="97" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q97" s="35"/>
-      <c r="S97" s="35"/>
-      <c r="U97" s="35"/>
-      <c r="W97" s="35"/>
-      <c r="Y97" s="35"/>
-      <c r="AF97" s="35"/>
-      <c r="AG97"/>
-      <c r="AH97" s="35"/>
-      <c r="AJ97" s="35"/>
-      <c r="AL97" s="35"/>
-      <c r="AN97" s="35"/>
-      <c r="AU97" s="35"/>
-      <c r="AV97"/>
-      <c r="AW97" s="35"/>
-      <c r="AY97" s="35"/>
-      <c r="BA97" s="35"/>
-      <c r="BC97" s="35"/>
-      <c r="BD97" s="20"/>
-      <c r="BJ97" s="35"/>
-      <c r="BK97"/>
-      <c r="BL97" s="35"/>
-      <c r="BN97" s="35"/>
-      <c r="BP97" s="35"/>
-      <c r="BR97" s="35"/>
-      <c r="BX97"/>
-      <c r="BY97" s="35"/>
-      <c r="CA97" s="35"/>
-      <c r="CC97" s="35"/>
-      <c r="CE97" s="35"/>
-      <c r="CG97" s="38"/>
-      <c r="CH97" s="35"/>
+      <c r="CJ96" s="35"/>
+    </row>
+    <row r="97" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R97" s="35"/>
+      <c r="T97" s="35"/>
+      <c r="V97" s="35"/>
+      <c r="X97" s="35"/>
+      <c r="Z97" s="35"/>
+      <c r="AG97" s="35"/>
+      <c r="AH97"/>
+      <c r="AI97" s="35"/>
+      <c r="AK97" s="35"/>
+      <c r="AM97" s="35"/>
+      <c r="AO97" s="35"/>
+      <c r="AV97" s="35"/>
+      <c r="AW97"/>
+      <c r="AX97" s="35"/>
+      <c r="AZ97" s="35"/>
+      <c r="BB97" s="35"/>
+      <c r="BD97" s="35"/>
+      <c r="BE97" s="20"/>
+      <c r="BK97" s="35"/>
+      <c r="BL97"/>
+      <c r="BM97" s="35"/>
+      <c r="BO97" s="35"/>
+      <c r="BQ97" s="35"/>
+      <c r="BS97" s="35"/>
+      <c r="BY97"/>
+      <c r="BZ97" s="35"/>
+      <c r="CB97" s="35"/>
+      <c r="CD97" s="35"/>
+      <c r="CF97" s="35"/>
+      <c r="CH97" s="38"/>
       <c r="CI97" s="35"/>
-    </row>
-    <row r="98" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q98" s="35"/>
-      <c r="S98" s="35"/>
-      <c r="U98" s="35"/>
-      <c r="W98" s="35"/>
-      <c r="Y98" s="35"/>
-      <c r="AF98" s="35"/>
-      <c r="AG98"/>
-      <c r="AH98" s="35"/>
-      <c r="AJ98" s="35"/>
-      <c r="AL98" s="35"/>
-      <c r="AN98" s="35"/>
-      <c r="AU98" s="35"/>
-      <c r="AV98"/>
-      <c r="AW98" s="35"/>
-      <c r="AY98" s="35"/>
-      <c r="BA98" s="35"/>
-      <c r="BC98" s="35"/>
-      <c r="BD98" s="20"/>
-      <c r="BJ98" s="35"/>
-      <c r="BK98"/>
-      <c r="BL98" s="35"/>
-      <c r="BN98" s="35"/>
-      <c r="BP98" s="35"/>
-      <c r="BR98" s="35"/>
-      <c r="BX98"/>
-      <c r="BY98" s="35"/>
-      <c r="CA98" s="35"/>
-      <c r="CC98" s="35"/>
-      <c r="CE98" s="35"/>
-      <c r="CG98" s="38"/>
-      <c r="CH98" s="35"/>
+      <c r="CJ97" s="35"/>
+    </row>
+    <row r="98" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R98" s="35"/>
+      <c r="T98" s="35"/>
+      <c r="V98" s="35"/>
+      <c r="X98" s="35"/>
+      <c r="Z98" s="35"/>
+      <c r="AG98" s="35"/>
+      <c r="AH98"/>
+      <c r="AI98" s="35"/>
+      <c r="AK98" s="35"/>
+      <c r="AM98" s="35"/>
+      <c r="AO98" s="35"/>
+      <c r="AV98" s="35"/>
+      <c r="AW98"/>
+      <c r="AX98" s="35"/>
+      <c r="AZ98" s="35"/>
+      <c r="BB98" s="35"/>
+      <c r="BD98" s="35"/>
+      <c r="BE98" s="20"/>
+      <c r="BK98" s="35"/>
+      <c r="BL98"/>
+      <c r="BM98" s="35"/>
+      <c r="BO98" s="35"/>
+      <c r="BQ98" s="35"/>
+      <c r="BS98" s="35"/>
+      <c r="BY98"/>
+      <c r="BZ98" s="35"/>
+      <c r="CB98" s="35"/>
+      <c r="CD98" s="35"/>
+      <c r="CF98" s="35"/>
+      <c r="CH98" s="38"/>
       <c r="CI98" s="35"/>
-    </row>
-    <row r="99" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q99" s="35"/>
-      <c r="S99" s="35"/>
-      <c r="U99" s="35"/>
-      <c r="W99" s="35"/>
-      <c r="Y99" s="35"/>
-      <c r="AF99" s="35"/>
-      <c r="AG99"/>
-      <c r="AH99" s="35"/>
-      <c r="AJ99" s="35"/>
-      <c r="AL99" s="35"/>
-      <c r="AN99" s="35"/>
-      <c r="AU99" s="35"/>
-      <c r="AV99"/>
-      <c r="AW99" s="35"/>
-      <c r="AY99" s="35"/>
-      <c r="BA99" s="35"/>
-      <c r="BC99" s="35"/>
-      <c r="BD99" s="20"/>
-      <c r="BJ99" s="35"/>
-      <c r="BK99"/>
-      <c r="BL99" s="35"/>
-      <c r="BN99" s="35"/>
-      <c r="BP99" s="35"/>
-      <c r="BR99" s="35"/>
-      <c r="BX99"/>
-      <c r="BY99" s="35"/>
-      <c r="CA99" s="35"/>
-      <c r="CC99" s="35"/>
-      <c r="CE99" s="35"/>
-      <c r="CG99" s="38"/>
-      <c r="CH99" s="35"/>
+      <c r="CJ98" s="35"/>
+    </row>
+    <row r="99" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R99" s="35"/>
+      <c r="T99" s="35"/>
+      <c r="V99" s="35"/>
+      <c r="X99" s="35"/>
+      <c r="Z99" s="35"/>
+      <c r="AG99" s="35"/>
+      <c r="AH99"/>
+      <c r="AI99" s="35"/>
+      <c r="AK99" s="35"/>
+      <c r="AM99" s="35"/>
+      <c r="AO99" s="35"/>
+      <c r="AV99" s="35"/>
+      <c r="AW99"/>
+      <c r="AX99" s="35"/>
+      <c r="AZ99" s="35"/>
+      <c r="BB99" s="35"/>
+      <c r="BD99" s="35"/>
+      <c r="BE99" s="20"/>
+      <c r="BK99" s="35"/>
+      <c r="BL99"/>
+      <c r="BM99" s="35"/>
+      <c r="BO99" s="35"/>
+      <c r="BQ99" s="35"/>
+      <c r="BS99" s="35"/>
+      <c r="BY99"/>
+      <c r="BZ99" s="35"/>
+      <c r="CB99" s="35"/>
+      <c r="CD99" s="35"/>
+      <c r="CF99" s="35"/>
+      <c r="CH99" s="38"/>
       <c r="CI99" s="35"/>
-    </row>
-    <row r="100" spans="17:87" x14ac:dyDescent="0.3">
-      <c r="Q100" s="35"/>
-      <c r="S100" s="35"/>
-      <c r="U100" s="35"/>
-      <c r="W100" s="35"/>
-      <c r="Y100" s="35"/>
-      <c r="AF100" s="35"/>
-      <c r="AG100"/>
-      <c r="AH100" s="35"/>
-      <c r="AJ100" s="35"/>
-      <c r="AL100" s="35"/>
-      <c r="AN100" s="35"/>
-      <c r="AU100" s="35"/>
-      <c r="AV100"/>
-      <c r="AW100" s="35"/>
-      <c r="AY100" s="35"/>
-      <c r="BA100" s="35"/>
-      <c r="BC100" s="35"/>
-      <c r="BD100" s="20"/>
-      <c r="BJ100" s="35"/>
-      <c r="BK100"/>
-      <c r="BL100" s="35"/>
-      <c r="BN100" s="35"/>
-      <c r="BP100" s="35"/>
-      <c r="BR100" s="35"/>
-      <c r="BX100"/>
-      <c r="BY100" s="35"/>
-      <c r="CA100" s="35"/>
-      <c r="CC100" s="35"/>
-      <c r="CE100" s="35"/>
-      <c r="CG100" s="38"/>
-      <c r="CH100" s="35"/>
+      <c r="CJ99" s="35"/>
+    </row>
+    <row r="100" spans="18:88" x14ac:dyDescent="0.3">
+      <c r="R100" s="35"/>
+      <c r="T100" s="35"/>
+      <c r="V100" s="35"/>
+      <c r="X100" s="35"/>
+      <c r="Z100" s="35"/>
+      <c r="AG100" s="35"/>
+      <c r="AH100"/>
+      <c r="AI100" s="35"/>
+      <c r="AK100" s="35"/>
+      <c r="AM100" s="35"/>
+      <c r="AO100" s="35"/>
+      <c r="AV100" s="35"/>
+      <c r="AW100"/>
+      <c r="AX100" s="35"/>
+      <c r="AZ100" s="35"/>
+      <c r="BB100" s="35"/>
+      <c r="BD100" s="35"/>
+      <c r="BE100" s="20"/>
+      <c r="BK100" s="35"/>
+      <c r="BL100"/>
+      <c r="BM100" s="35"/>
+      <c r="BO100" s="35"/>
+      <c r="BQ100" s="35"/>
+      <c r="BS100" s="35"/>
+      <c r="BY100"/>
+      <c r="BZ100" s="35"/>
+      <c r="CB100" s="35"/>
+      <c r="CD100" s="35"/>
+      <c r="CF100" s="35"/>
+      <c r="CH100" s="38"/>
       <c r="CI100" s="35"/>
+      <c r="CJ100" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="BS1:CG1"/>
-    <mergeCell ref="CH1:CI1"/>
+    <mergeCell ref="BT1:CH1"/>
+    <mergeCell ref="CI1:CJ1"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:Y1"/>
-    <mergeCell ref="Z1:AN1"/>
-    <mergeCell ref="AO1:BC1"/>
-    <mergeCell ref="BD1:BR1"/>
+    <mergeCell ref="G1:Z1"/>
+    <mergeCell ref="AA1:AO1"/>
+    <mergeCell ref="AP1:BD1"/>
+    <mergeCell ref="BE1:BS1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7515,37 +7421,37 @@
           <x14:formula1>
             <xm:f>options!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>BJ100</xm:sqref>
+          <xm:sqref>BK100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="soil moisture" prompt="indicate if measurement is gravimetric (% g/g) or volumetric (% V/V)" xr:uid="{95BC60E9-AF61-486E-9DBD-C211EE4FBBF0}">
           <x14:formula1>
             <xm:f>options!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>Q3:Q99 S3:S99 AF3:AF99 CA3:CA99 AU3:AU99 AW3:AW99 BJ3:BJ99 BL3:BL99 BY3:BY99 AH3:AH99</xm:sqref>
+          <xm:sqref>R3:R99 T3:T99 AG3:AG99 CB3:CB99 AV3:AV99 AX3:AX99 BK3:BK99 BM3:BM99 BZ3:BZ99 AI3:AI99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="measurement units" prompt="select mg N/ha. or kg N/ha." xr:uid="{7A34E804-1F1D-4C2A-861F-919BB0C44744}">
           <x14:formula1>
             <xm:f>options!$I$2:$I$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U3:U100 AJ3:AJ100 BP3:BP100 AY3:AY100 AL3:AL100 BN3:BN100 CC3:CC100 CE3:CE100 W3:W100 BA3:BA100</xm:sqref>
+          <xm:sqref>V3:V100 AK3:AK100 BQ3:BQ100 AZ3:AZ100 AM3:AM100 BO3:BO100 CD3:CD100 CF3:CF100 X3:X100 BB3:BB100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="pebble type" prompt="select pebble parent material" xr:uid="{67722B95-306B-41AB-811A-519E31905398}">
           <x14:formula1>
             <xm:f>options!$K$2:$K$10</xm:f>
           </x14:formula1>
-          <xm:sqref>Y3:Y100 AN3:AN100 BC3:BC100 BR3:BR100 CG3:CG100</xm:sqref>
+          <xm:sqref>Z3:Z100 AO3:AO100 BD3:BD100 BS3:BS100 CH3:CH100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="denitrification model" prompt="option to activate denitirification model (needed to simulate N2O emissions)" xr:uid="{F02AC1DD-C9A5-4A3B-9C6A-CB8872977777}">
           <x14:formula1>
             <xm:f>options!$Q$2:$Q$3</xm:f>
           </x14:formula1>
-          <xm:sqref>CH3</xm:sqref>
+          <xm:sqref>CI3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="nitrification model" prompt="option to activate nitrification model (needed to simulate N2O emissions)" xr:uid="{75783F8E-2B61-4162-B703-3C658A638A13}">
           <x14:formula1>
             <xm:f>options!$Q$2:$Q$3</xm:f>
           </x14:formula1>
-          <xm:sqref>CI3</xm:sqref>
+          <xm:sqref>CJ3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7564,7 +7470,7 @@
     <col min="1" max="1" width="14.88671875" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.109375" style="20" customWidth="1"/>
-    <col min="4" max="5" width="19.6640625" style="79" customWidth="1"/>
+    <col min="4" max="5" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7580,549 +7486,549 @@
       <c r="D1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="67" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C2" s="37"/>
       <c r="D2" s="20"/>
-      <c r="E2" s="80"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C3" s="37"/>
       <c r="D3" s="20"/>
-      <c r="E3" s="80"/>
+      <c r="E3" s="64"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C4" s="37"/>
       <c r="D4" s="20"/>
-      <c r="E4" s="80"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C5" s="37"/>
       <c r="D5" s="20"/>
-      <c r="E5" s="80"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" s="37"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="80"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C7" s="37"/>
       <c r="D7" s="20"/>
-      <c r="E7" s="80"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="37"/>
       <c r="D8" s="20"/>
-      <c r="E8" s="80"/>
+      <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C9" s="37"/>
       <c r="D9" s="20"/>
-      <c r="E9" s="80"/>
+      <c r="E9" s="64"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C10" s="37"/>
       <c r="D10" s="20"/>
-      <c r="E10" s="80"/>
+      <c r="E10" s="64"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" s="37"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="80"/>
+      <c r="E11" s="64"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C12" s="37"/>
       <c r="D12" s="20"/>
-      <c r="E12" s="80"/>
+      <c r="E12" s="64"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C13" s="37"/>
       <c r="D13" s="20"/>
-      <c r="E13" s="80"/>
+      <c r="E13" s="64"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C14" s="37"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="80"/>
+      <c r="E14" s="64"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C15" s="37"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="80"/>
+      <c r="E15" s="64"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C16" s="37"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="80"/>
+      <c r="E16" s="64"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C17" s="37"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="80"/>
+      <c r="E17" s="64"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C18" s="37"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="80"/>
+      <c r="E18" s="64"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C19" s="37"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="80"/>
+      <c r="E19" s="64"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C20" s="37"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="80"/>
+      <c r="E20" s="64"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C21" s="37"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="80"/>
+      <c r="E21" s="64"/>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C22" s="37"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="80"/>
+      <c r="E22" s="64"/>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C23" s="37"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="80"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C24" s="37"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="80"/>
+      <c r="E24" s="64"/>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C25" s="37"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="80"/>
+      <c r="E25" s="64"/>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C26" s="37"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="80"/>
+      <c r="E26" s="64"/>
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C27" s="37"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="80"/>
+      <c r="E27" s="64"/>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C28" s="37"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="80"/>
+      <c r="E28" s="64"/>
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C29" s="37"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="80"/>
+      <c r="E29" s="64"/>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C30" s="37"/>
       <c r="D30" s="20"/>
-      <c r="E30" s="80"/>
+      <c r="E30" s="64"/>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C31" s="37"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="80"/>
+      <c r="E31" s="64"/>
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C32" s="37"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="80"/>
+      <c r="E32" s="64"/>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" s="37"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="80"/>
+      <c r="E33" s="64"/>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" s="37"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="80"/>
+      <c r="E34" s="64"/>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C35" s="37"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="80"/>
+      <c r="E35" s="64"/>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C36" s="37"/>
       <c r="D36" s="20"/>
-      <c r="E36" s="80"/>
+      <c r="E36" s="64"/>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C37" s="37"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="80"/>
+      <c r="E37" s="64"/>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C38" s="37"/>
       <c r="D38" s="20"/>
-      <c r="E38" s="80"/>
+      <c r="E38" s="64"/>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C39" s="37"/>
       <c r="D39" s="20"/>
-      <c r="E39" s="80"/>
+      <c r="E39" s="64"/>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C40" s="37"/>
       <c r="D40" s="20"/>
-      <c r="E40" s="80"/>
+      <c r="E40" s="64"/>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C41" s="37"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="80"/>
+      <c r="E41" s="64"/>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C42" s="37"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="80"/>
+      <c r="E42" s="64"/>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C43" s="37"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="80"/>
+      <c r="E43" s="64"/>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C44" s="37"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="80"/>
+      <c r="E44" s="64"/>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C45" s="37"/>
       <c r="D45" s="20"/>
-      <c r="E45" s="80"/>
+      <c r="E45" s="64"/>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C46" s="37"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="80"/>
+      <c r="E46" s="64"/>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C47" s="37"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="80"/>
+      <c r="E47" s="64"/>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C48" s="37"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="80"/>
+      <c r="E48" s="64"/>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C49" s="37"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="80"/>
+      <c r="E49" s="64"/>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C50" s="37"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="80"/>
+      <c r="E50" s="64"/>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C51" s="37"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="80"/>
+      <c r="E51" s="64"/>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C52" s="37"/>
       <c r="D52" s="20"/>
-      <c r="E52" s="80"/>
+      <c r="E52" s="64"/>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C53" s="37"/>
       <c r="D53" s="20"/>
-      <c r="E53" s="80"/>
+      <c r="E53" s="64"/>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C54" s="37"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="80"/>
+      <c r="E54" s="64"/>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C55" s="37"/>
       <c r="D55" s="20"/>
-      <c r="E55" s="80"/>
+      <c r="E55" s="64"/>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C56" s="37"/>
       <c r="D56" s="20"/>
-      <c r="E56" s="80"/>
+      <c r="E56" s="64"/>
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C57" s="37"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="80"/>
+      <c r="E57" s="64"/>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C58" s="37"/>
       <c r="D58" s="20"/>
-      <c r="E58" s="80"/>
+      <c r="E58" s="64"/>
     </row>
     <row r="59" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C59" s="37"/>
       <c r="D59" s="20"/>
-      <c r="E59" s="80"/>
+      <c r="E59" s="64"/>
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C60" s="37"/>
       <c r="D60" s="20"/>
-      <c r="E60" s="80"/>
+      <c r="E60" s="64"/>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C61" s="37"/>
       <c r="D61" s="20"/>
-      <c r="E61" s="80"/>
+      <c r="E61" s="64"/>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C62" s="37"/>
       <c r="D62" s="20"/>
-      <c r="E62" s="80"/>
+      <c r="E62" s="64"/>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C63" s="37"/>
       <c r="D63" s="20"/>
-      <c r="E63" s="80"/>
+      <c r="E63" s="64"/>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C64" s="37"/>
       <c r="D64" s="20"/>
-      <c r="E64" s="80"/>
+      <c r="E64" s="64"/>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C65" s="37"/>
       <c r="D65" s="20"/>
-      <c r="E65" s="80"/>
+      <c r="E65" s="64"/>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C66" s="37"/>
       <c r="D66" s="20"/>
-      <c r="E66" s="80"/>
+      <c r="E66" s="64"/>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C67" s="37"/>
       <c r="D67" s="20"/>
-      <c r="E67" s="80"/>
+      <c r="E67" s="64"/>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C68" s="37"/>
       <c r="D68" s="20"/>
-      <c r="E68" s="80"/>
+      <c r="E68" s="64"/>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C69" s="37"/>
       <c r="D69" s="20"/>
-      <c r="E69" s="80"/>
+      <c r="E69" s="64"/>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C70" s="37"/>
       <c r="D70" s="20"/>
-      <c r="E70" s="80"/>
+      <c r="E70" s="64"/>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C71" s="37"/>
       <c r="D71" s="20"/>
-      <c r="E71" s="80"/>
+      <c r="E71" s="64"/>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C72" s="37"/>
       <c r="D72" s="20"/>
-      <c r="E72" s="80"/>
+      <c r="E72" s="64"/>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C73" s="37"/>
       <c r="D73" s="20"/>
-      <c r="E73" s="80"/>
+      <c r="E73" s="64"/>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C74" s="37"/>
       <c r="D74" s="20"/>
-      <c r="E74" s="80"/>
+      <c r="E74" s="64"/>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C75" s="37"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="80"/>
+      <c r="E75" s="64"/>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C76" s="37"/>
       <c r="D76" s="20"/>
-      <c r="E76" s="80"/>
+      <c r="E76" s="64"/>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C77" s="37"/>
       <c r="D77" s="20"/>
-      <c r="E77" s="80"/>
+      <c r="E77" s="64"/>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C78" s="37"/>
       <c r="D78" s="20"/>
-      <c r="E78" s="80"/>
+      <c r="E78" s="64"/>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C79" s="37"/>
       <c r="D79" s="20"/>
-      <c r="E79" s="80"/>
+      <c r="E79" s="64"/>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C80" s="37"/>
       <c r="D80" s="20"/>
-      <c r="E80" s="80"/>
+      <c r="E80" s="64"/>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C81" s="37"/>
       <c r="D81" s="20"/>
-      <c r="E81" s="80"/>
+      <c r="E81" s="64"/>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C82" s="37"/>
       <c r="D82" s="20"/>
-      <c r="E82" s="80"/>
+      <c r="E82" s="64"/>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C83" s="37"/>
       <c r="D83" s="20"/>
-      <c r="E83" s="80"/>
+      <c r="E83" s="64"/>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C84" s="37"/>
       <c r="D84" s="20"/>
-      <c r="E84" s="80"/>
+      <c r="E84" s="64"/>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C85" s="37"/>
       <c r="D85" s="20"/>
-      <c r="E85" s="80"/>
+      <c r="E85" s="64"/>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C86" s="37"/>
       <c r="D86" s="20"/>
-      <c r="E86" s="80"/>
+      <c r="E86" s="64"/>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C87" s="37"/>
       <c r="D87" s="20"/>
-      <c r="E87" s="80"/>
+      <c r="E87" s="64"/>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C88" s="37"/>
       <c r="D88" s="20"/>
-      <c r="E88" s="80"/>
+      <c r="E88" s="64"/>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C89" s="37"/>
       <c r="D89" s="20"/>
-      <c r="E89" s="80"/>
+      <c r="E89" s="64"/>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C90" s="37"/>
       <c r="D90" s="20"/>
-      <c r="E90" s="80"/>
+      <c r="E90" s="64"/>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C91" s="37"/>
       <c r="D91" s="20"/>
-      <c r="E91" s="80"/>
+      <c r="E91" s="64"/>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C92" s="37"/>
       <c r="D92" s="20"/>
-      <c r="E92" s="80"/>
+      <c r="E92" s="64"/>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C93" s="37"/>
       <c r="D93" s="20"/>
-      <c r="E93" s="80"/>
+      <c r="E93" s="64"/>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C94" s="37"/>
       <c r="D94" s="20"/>
-      <c r="E94" s="80"/>
+      <c r="E94" s="64"/>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C95" s="37"/>
       <c r="D95" s="20"/>
-      <c r="E95" s="80"/>
+      <c r="E95" s="64"/>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C96" s="37"/>
       <c r="D96" s="20"/>
-      <c r="E96" s="80"/>
+      <c r="E96" s="64"/>
     </row>
     <row r="97" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C97" s="37"/>
       <c r="D97" s="20"/>
-      <c r="E97" s="80"/>
+      <c r="E97" s="64"/>
     </row>
     <row r="98" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C98" s="37"/>
       <c r="D98" s="20"/>
-      <c r="E98" s="80"/>
+      <c r="E98" s="64"/>
     </row>
     <row r="99" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C99" s="37"/>
       <c r="D99" s="20"/>
-      <c r="E99" s="80"/>
+      <c r="E99" s="64"/>
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C100" s="37"/>
       <c r="D100" s="20"/>
-      <c r="E100" s="80"/>
+      <c r="E100" s="64"/>
     </row>
     <row r="101" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C101" s="37"/>
       <c r="D101" s="20"/>
-      <c r="E101" s="80"/>
+      <c r="E101" s="64"/>
     </row>
     <row r="102" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C102" s="37"/>
       <c r="D102" s="20"/>
-      <c r="E102" s="80"/>
+      <c r="E102" s="64"/>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C103" s="37"/>
       <c r="D103" s="20"/>
-      <c r="E103" s="80"/>
+      <c r="E103" s="64"/>
     </row>
     <row r="104" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C104" s="37"/>
       <c r="D104" s="20"/>
-      <c r="E104" s="80"/>
+      <c r="E104" s="64"/>
     </row>
     <row r="105" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C105" s="37"/>
       <c r="D105" s="20"/>
-      <c r="E105" s="80"/>
+      <c r="E105" s="64"/>
     </row>
     <row r="106" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C106" s="37"/>
       <c r="D106" s="20"/>
-      <c r="E106" s="80"/>
+      <c r="E106" s="64"/>
     </row>
     <row r="107" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C107" s="37"/>
       <c r="D107" s="20"/>
-      <c r="E107" s="80"/>
+      <c r="E107" s="64"/>
     </row>
     <row r="108" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C108" s="37"/>
       <c r="D108" s="20"/>
-      <c r="E108" s="80"/>
+      <c r="E108" s="64"/>
     </row>
     <row r="109" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C109" s="37"/>
       <c r="D109" s="20"/>
-      <c r="E109" s="80"/>
+      <c r="E109" s="64"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8173,16 +8079,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C1"/>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
-      <c r="I1" s="69" t="s">
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="79"/>
+      <c r="I1" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="70"/>
+      <c r="J1" s="77"/>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
